--- a/outputs/tables/portfolio_taxes_all_methods_with_costs_taxes.xlsx
+++ b/outputs/tables/portfolio_taxes_all_methods_with_costs_taxes.xlsx
@@ -20,16 +20,13 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -48,21 +45,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -433,54 +421,54 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>symbol</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>sale_value</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>transaction_cost</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>basis_sold</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>realized_gain_after_costs</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>tax_paid</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>loss_carryforward_after</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>strategy</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="1" t="n">
         <v>43467</v>
       </c>
       <c r="B2" t="inlineStr">
@@ -513,7 +501,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n">
+      <c r="A3" s="1" t="n">
         <v>43467</v>
       </c>
       <c r="B3" t="inlineStr">
@@ -546,7 +534,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
+      <c r="A4" s="1" t="n">
         <v>43467</v>
       </c>
       <c r="B4" t="inlineStr">
@@ -579,7 +567,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n">
+      <c r="A5" s="1" t="n">
         <v>43467</v>
       </c>
       <c r="B5" t="inlineStr">
@@ -612,7 +600,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n">
+      <c r="A6" s="1" t="n">
         <v>43467</v>
       </c>
       <c r="B6" t="inlineStr">
@@ -645,7 +633,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n">
+      <c r="A7" s="1" t="n">
         <v>43467</v>
       </c>
       <c r="B7" t="inlineStr">
@@ -678,7 +666,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n">
+      <c r="A8" s="1" t="n">
         <v>43832</v>
       </c>
       <c r="B8" t="inlineStr">
@@ -711,7 +699,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="n">
+      <c r="A9" s="1" t="n">
         <v>43832</v>
       </c>
       <c r="B9" t="inlineStr">
@@ -744,7 +732,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="n">
+      <c r="A10" s="1" t="n">
         <v>43832</v>
       </c>
       <c r="B10" t="inlineStr">
@@ -777,7 +765,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="n">
+      <c r="A11" s="1" t="n">
         <v>43832</v>
       </c>
       <c r="B11" t="inlineStr">
@@ -810,7 +798,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="n">
+      <c r="A12" s="1" t="n">
         <v>43832</v>
       </c>
       <c r="B12" t="inlineStr">
@@ -843,7 +831,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="n">
+      <c r="A13" s="1" t="n">
         <v>43832</v>
       </c>
       <c r="B13" t="inlineStr">
@@ -876,7 +864,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="n">
+      <c r="A14" s="1" t="n">
         <v>44200</v>
       </c>
       <c r="B14" t="inlineStr">
@@ -894,10 +882,10 @@
         <v>15907.70202177101</v>
       </c>
       <c r="F14" t="n">
-        <v>6499.175465066382</v>
+        <v>6499.175465066384</v>
       </c>
       <c r="G14" t="n">
-        <v>1485.208270243099</v>
+        <v>1485.2082702431</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -909,7 +897,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="n">
+      <c r="A15" s="1" t="n">
         <v>44200</v>
       </c>
       <c r="B15" t="inlineStr">
@@ -918,13 +906,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>12377.03010776977</v>
+        <v>12377.03010776976</v>
       </c>
       <c r="D15" t="n">
         <v>5</v>
       </c>
       <c r="E15" t="n">
-        <v>13835.19743782553</v>
+        <v>13835.19743782552</v>
       </c>
       <c r="F15" t="n">
         <v>-1463.16733005576</v>
@@ -942,7 +930,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="n">
+      <c r="A16" s="1" t="n">
         <v>44200</v>
       </c>
       <c r="B16" t="inlineStr">
@@ -975,7 +963,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="n">
+      <c r="A17" s="1" t="n">
         <v>44200</v>
       </c>
       <c r="B17" t="inlineStr">
@@ -1008,7 +996,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="n">
+      <c r="A18" s="1" t="n">
         <v>44200</v>
       </c>
       <c r="B18" t="inlineStr">
@@ -1023,10 +1011,10 @@
         <v>5</v>
       </c>
       <c r="E18" t="n">
-        <v>2902.394133845273</v>
+        <v>2902.394133845272</v>
       </c>
       <c r="F18" t="n">
-        <v>3063.549033101452</v>
+        <v>3063.549033101453</v>
       </c>
       <c r="G18" t="n">
         <v>780.2278282981932</v>
@@ -1041,7 +1029,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="n">
+      <c r="A19" s="1" t="n">
         <v>44200</v>
       </c>
       <c r="B19" t="inlineStr">
@@ -1056,13 +1044,13 @@
         <v>5</v>
       </c>
       <c r="E19" t="n">
-        <v>8778.337745303757</v>
+        <v>8778.337745303759</v>
       </c>
       <c r="F19" t="n">
-        <v>2480.44810981509</v>
+        <v>2480.448109815088</v>
       </c>
       <c r="G19" t="n">
-        <v>644.9165085519235</v>
+        <v>644.9165085519229</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -1074,7 +1062,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="n">
+      <c r="A20" s="1" t="n">
         <v>44200</v>
       </c>
       <c r="B20" t="inlineStr">
@@ -1083,22 +1071,22 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>7821.594406988318</v>
+        <v>7821.594406988322</v>
       </c>
       <c r="D20" t="n">
         <v>5</v>
       </c>
       <c r="E20" t="n">
-        <v>8778.337745303757</v>
+        <v>8778.337745303759</v>
       </c>
       <c r="F20" t="n">
-        <v>-961.7433383154394</v>
+        <v>-961.7433383154375</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>961.7433383154394</v>
+        <v>961.7433383154375</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1107,7 +1095,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="n">
+      <c r="A21" s="1" t="n">
         <v>44200</v>
       </c>
       <c r="B21" t="inlineStr">
@@ -1122,10 +1110,10 @@
         <v>5</v>
       </c>
       <c r="E21" t="n">
-        <v>5853.891830202505</v>
+        <v>5853.891830202507</v>
       </c>
       <c r="F21" t="n">
-        <v>-732.6838481682989</v>
+        <v>-732.6838481683008</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -1140,7 +1128,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="n">
+      <c r="A22" s="1" t="n">
         <v>44564</v>
       </c>
       <c r="B22" t="inlineStr">
@@ -1173,7 +1161,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="n">
+      <c r="A23" s="1" t="n">
         <v>44564</v>
       </c>
       <c r="B23" t="inlineStr">
@@ -1206,7 +1194,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="n">
+      <c r="A24" s="1" t="n">
         <v>44564</v>
       </c>
       <c r="B24" t="inlineStr">
@@ -1215,19 +1203,19 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>9451.658169392351</v>
+        <v>9451.658169392358</v>
       </c>
       <c r="D24" t="n">
         <v>5</v>
       </c>
       <c r="E24" t="n">
-        <v>6871.617288358932</v>
+        <v>6871.617288358935</v>
       </c>
       <c r="F24" t="n">
-        <v>2575.040881033419</v>
+        <v>2575.040881033423</v>
       </c>
       <c r="G24" t="n">
-        <v>669.510629068689</v>
+        <v>669.51062906869</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
@@ -1239,7 +1227,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="n">
+      <c r="A25" s="1" t="n">
         <v>44564</v>
       </c>
       <c r="B25" t="inlineStr">
@@ -1272,7 +1260,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="n">
+      <c r="A26" s="1" t="n">
         <v>44564</v>
       </c>
       <c r="B26" t="inlineStr">
@@ -1305,7 +1293,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="n">
+      <c r="A27" s="1" t="n">
         <v>44564</v>
       </c>
       <c r="B27" t="inlineStr">
@@ -1338,7 +1326,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="n">
+      <c r="A28" s="1" t="n">
         <v>44564</v>
       </c>
       <c r="B28" t="inlineStr">
@@ -1371,7 +1359,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="n">
+      <c r="A29" s="1" t="n">
         <v>44928</v>
       </c>
       <c r="B29" t="inlineStr">
@@ -1380,19 +1368,19 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>5658.515302776081</v>
+        <v>5658.515302776079</v>
       </c>
       <c r="D29" t="n">
         <v>5</v>
       </c>
       <c r="E29" t="n">
-        <v>4535.385945916935</v>
+        <v>4535.385945916934</v>
       </c>
       <c r="F29" t="n">
         <v>1118.129356859145</v>
       </c>
       <c r="G29" t="n">
-        <v>290.7136327833778</v>
+        <v>290.7136327833776</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
@@ -1404,7 +1392,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="n">
+      <c r="A30" s="1" t="n">
         <v>44928</v>
       </c>
       <c r="B30" t="inlineStr">
@@ -1437,7 +1425,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="n">
+      <c r="A31" s="1" t="n">
         <v>44928</v>
       </c>
       <c r="B31" t="inlineStr">
@@ -1446,19 +1434,19 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>2846.049341293059</v>
+        <v>2846.049341293055</v>
       </c>
       <c r="D31" t="n">
         <v>5</v>
       </c>
       <c r="E31" t="n">
-        <v>2605.875581197649</v>
+        <v>2605.875581197646</v>
       </c>
       <c r="F31" t="n">
-        <v>235.1737600954098</v>
+        <v>235.1737600954093</v>
       </c>
       <c r="G31" t="n">
-        <v>61.14517762480654</v>
+        <v>61.14517762480642</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
@@ -1470,7 +1458,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="n">
+      <c r="A32" s="1" t="n">
         <v>44928</v>
       </c>
       <c r="B32" t="inlineStr">
@@ -1488,10 +1476,10 @@
         <v>10764.2671905236</v>
       </c>
       <c r="F32" t="n">
-        <v>3704.93989451846</v>
+        <v>3704.939894518458</v>
       </c>
       <c r="G32" t="n">
-        <v>963.2843725747997</v>
+        <v>963.2843725747992</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -1503,7 +1491,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="n">
+      <c r="A33" s="1" t="n">
         <v>44928</v>
       </c>
       <c r="B33" t="inlineStr">
@@ -1512,7 +1500,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>7583.78540068873</v>
+        <v>7583.785400688734</v>
       </c>
       <c r="D33" t="n">
         <v>5</v>
@@ -1521,13 +1509,13 @@
         <v>10764.2671905236</v>
       </c>
       <c r="F33" t="n">
-        <v>-3185.481789834872</v>
+        <v>-3185.48178983487</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>3185.481789834872</v>
+        <v>3185.48178983487</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -1536,7 +1524,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="n">
+      <c r="A34" s="1" t="n">
         <v>45293</v>
       </c>
       <c r="B34" t="inlineStr">
@@ -1554,13 +1542,13 @@
         <v>1855.340412260958</v>
       </c>
       <c r="F34" t="n">
-        <v>860.2304835817517</v>
+        <v>860.2304835817513</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>2325.25130625312</v>
+        <v>2325.251306253119</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -1569,7 +1557,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="n">
+      <c r="A35" s="1" t="n">
         <v>45293</v>
       </c>
       <c r="B35" t="inlineStr">
@@ -1593,7 +1581,7 @@
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>1676.792373670152</v>
+        <v>1676.79237367015</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -1602,7 +1590,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="n">
+      <c r="A36" s="1" t="n">
         <v>45293</v>
       </c>
       <c r="B36" t="inlineStr">
@@ -1623,7 +1611,7 @@
         <v>5257.732966538011</v>
       </c>
       <c r="G36" t="n">
-        <v>931.0445541456435</v>
+        <v>931.0445541456438</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
@@ -1635,7 +1623,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="n">
+      <c r="A37" s="1" t="n">
         <v>45293</v>
       </c>
       <c r="B37" t="inlineStr">
@@ -1644,19 +1632,19 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>9039.404344762928</v>
+        <v>9039.404344762932</v>
       </c>
       <c r="D37" t="n">
         <v>5</v>
       </c>
       <c r="E37" t="n">
-        <v>5874.681220594085</v>
+        <v>5874.681220594088</v>
       </c>
       <c r="F37" t="n">
-        <v>3159.723124168843</v>
+        <v>3159.723124168844</v>
       </c>
       <c r="G37" t="n">
-        <v>821.5280122838992</v>
+        <v>821.5280122838996</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
@@ -1668,7 +1656,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="n">
+      <c r="A38" s="1" t="n">
         <v>45293</v>
       </c>
       <c r="B38" t="inlineStr">
@@ -1701,7 +1689,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="n">
+      <c r="A39" s="1" t="n">
         <v>45293</v>
       </c>
       <c r="B39" t="inlineStr">
@@ -1710,7 +1698,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>15954.72540140377</v>
+        <v>15954.72540140378</v>
       </c>
       <c r="D39" t="n">
         <v>5</v>
@@ -1734,7 +1722,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="n">
+      <c r="A40" s="1" t="n">
         <v>45293</v>
       </c>
       <c r="B40" t="inlineStr">
@@ -1752,10 +1740,10 @@
         <v>22458.77851705509</v>
       </c>
       <c r="F40" t="n">
-        <v>3358.298149974231</v>
+        <v>3358.298149974235</v>
       </c>
       <c r="G40" t="n">
-        <v>873.1575189933001</v>
+        <v>873.157518993301</v>
       </c>
       <c r="H40" t="n">
         <v>0</v>
@@ -1767,7 +1755,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="n">
+      <c r="A41" s="1" t="n">
         <v>43467</v>
       </c>
       <c r="B41" t="inlineStr">
@@ -1776,19 +1764,19 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>268.2936842226654</v>
+        <v>268.2936842226663</v>
       </c>
       <c r="D41" t="n">
         <v>5</v>
       </c>
       <c r="E41" t="n">
-        <v>250.2840382487073</v>
+        <v>250.2840382487081</v>
       </c>
       <c r="F41" t="n">
-        <v>13.00964597395816</v>
+        <v>13.00964597395821</v>
       </c>
       <c r="G41" t="n">
-        <v>3.382507953229121</v>
+        <v>3.382507953229136</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
@@ -1800,7 +1788,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="n">
+      <c r="A42" s="1" t="n">
         <v>43467</v>
       </c>
       <c r="B42" t="inlineStr">
@@ -1809,22 +1797,22 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>1210.125209119913</v>
+        <v>1210.125209119917</v>
       </c>
       <c r="D42" t="n">
         <v>5</v>
       </c>
       <c r="E42" t="n">
-        <v>1610.795774637359</v>
+        <v>1610.795774637364</v>
       </c>
       <c r="F42" t="n">
-        <v>-405.6705655174455</v>
+        <v>-405.6705655174469</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>405.6705655174455</v>
+        <v>405.6705655174469</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -1833,7 +1821,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="n">
+      <c r="A43" s="1" t="n">
         <v>43467</v>
       </c>
       <c r="B43" t="inlineStr">
@@ -1842,13 +1830,13 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>1817.025931659438</v>
+        <v>1817.025931659442</v>
       </c>
       <c r="D43" t="n">
         <v>5</v>
       </c>
       <c r="E43" t="n">
-        <v>1762.995638010277</v>
+        <v>1762.995638010281</v>
       </c>
       <c r="F43" t="n">
         <v>49.03029364916142</v>
@@ -1857,7 +1845,7 @@
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>356.6402718682841</v>
+        <v>356.6402718682855</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -1866,7 +1854,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="n">
+      <c r="A44" s="1" t="n">
         <v>43467</v>
       </c>
       <c r="B44" t="inlineStr">
@@ -1875,22 +1863,22 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>297.3546760349545</v>
+        <v>297.354676034955</v>
       </c>
       <c r="D44" t="n">
         <v>5</v>
       </c>
       <c r="E44" t="n">
-        <v>359.0384595056398</v>
+        <v>359.0384595056404</v>
       </c>
       <c r="F44" t="n">
-        <v>-66.68378347068528</v>
+        <v>-66.6837834706854</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>423.3240553389694</v>
+        <v>423.3240553389709</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -1899,7 +1887,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="n">
+      <c r="A45" s="1" t="n">
         <v>43467</v>
       </c>
       <c r="B45" t="inlineStr">
@@ -1923,7 +1911,7 @@
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>1063.926099294061</v>
+        <v>1063.926099294062</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -1932,7 +1920,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="n">
+      <c r="A46" s="1" t="n">
         <v>43467</v>
       </c>
       <c r="B46" t="inlineStr">
@@ -1941,22 +1929,22 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>962.5851929420569</v>
+        <v>962.5851929420587</v>
       </c>
       <c r="D46" t="n">
         <v>5</v>
       </c>
       <c r="E46" t="n">
-        <v>949.8422320566267</v>
+        <v>949.8422320566284</v>
       </c>
       <c r="F46" t="n">
-        <v>7.742960885430193</v>
+        <v>7.742960885430307</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>1056.183138408631</v>
+        <v>1056.183138408632</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -1965,7 +1953,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="n">
+      <c r="A47" s="1" t="n">
         <v>43467</v>
       </c>
       <c r="B47" t="inlineStr">
@@ -1989,7 +1977,7 @@
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>1343.425505090166</v>
+        <v>1343.425505090167</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -1998,7 +1986,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="n">
+      <c r="A48" s="1" t="n">
         <v>43467</v>
       </c>
       <c r="B48" t="inlineStr">
@@ -2007,13 +1995,13 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>2143.392435776052</v>
+        <v>2143.392435776055</v>
       </c>
       <c r="D48" t="n">
         <v>5</v>
       </c>
       <c r="E48" t="n">
-        <v>2046.331454696048</v>
+        <v>2046.331454696052</v>
       </c>
       <c r="F48" t="n">
         <v>92.0609810800031</v>
@@ -2022,7 +2010,7 @@
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>1251.364524010163</v>
+        <v>1251.364524010164</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -2031,7 +2019,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="n">
+      <c r="A49" s="1" t="n">
         <v>43467</v>
       </c>
       <c r="B49" t="inlineStr">
@@ -2040,22 +2028,22 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>36.40914398908882</v>
+        <v>36.40914398908888</v>
       </c>
       <c r="D49" t="n">
         <v>5</v>
       </c>
       <c r="E49" t="n">
-        <v>44.83494500634112</v>
+        <v>44.83494500634119</v>
       </c>
       <c r="F49" t="n">
-        <v>-13.4258010172523</v>
+        <v>-13.42580101725231</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>1264.790325027415</v>
+        <v>1264.790325027416</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -2064,7 +2052,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="n">
+      <c r="A50" s="1" t="n">
         <v>43832</v>
       </c>
       <c r="B50" t="inlineStr">
@@ -2088,7 +2076,7 @@
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>1561.668040625313</v>
+        <v>1561.668040625314</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -2097,7 +2085,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="n">
+      <c r="A51" s="1" t="n">
         <v>43832</v>
       </c>
       <c r="B51" t="inlineStr">
@@ -2112,13 +2100,13 @@
         <v>5</v>
       </c>
       <c r="E51" t="n">
-        <v>10618.52851410983</v>
+        <v>10618.52851410982</v>
       </c>
       <c r="F51" t="n">
         <v>3683.182950950732</v>
       </c>
       <c r="G51" t="n">
-        <v>551.5938766846089</v>
+        <v>551.5938766846084</v>
       </c>
       <c r="H51" t="n">
         <v>0</v>
@@ -2130,7 +2118,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="n">
+      <c r="A52" s="1" t="n">
         <v>43832</v>
       </c>
       <c r="B52" t="inlineStr">
@@ -2163,7 +2151,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="n">
+      <c r="A53" s="1" t="n">
         <v>43832</v>
       </c>
       <c r="B53" t="inlineStr">
@@ -2172,19 +2160,19 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>1441.866761808703</v>
+        <v>1441.866761808705</v>
       </c>
       <c r="D53" t="n">
         <v>5</v>
       </c>
       <c r="E53" t="n">
-        <v>1321.705073164138</v>
+        <v>1321.705073164141</v>
       </c>
       <c r="F53" t="n">
-        <v>115.1616886445649</v>
+        <v>115.1616886445645</v>
       </c>
       <c r="G53" t="n">
-        <v>29.94203904758689</v>
+        <v>29.94203904758677</v>
       </c>
       <c r="H53" t="n">
         <v>0</v>
@@ -2196,7 +2184,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="n">
+      <c r="A54" s="1" t="n">
         <v>44200</v>
       </c>
       <c r="B54" t="inlineStr">
@@ -2211,13 +2199,13 @@
         <v>5</v>
       </c>
       <c r="E54" t="n">
-        <v>4518.907017221002</v>
+        <v>4518.907017221001</v>
       </c>
       <c r="F54" t="n">
-        <v>2094.658633483356</v>
+        <v>2094.658633483357</v>
       </c>
       <c r="G54" t="n">
-        <v>544.6112447056727</v>
+        <v>544.6112447056729</v>
       </c>
       <c r="H54" t="n">
         <v>0</v>
@@ -2229,7 +2217,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="n">
+      <c r="A55" s="1" t="n">
         <v>44200</v>
       </c>
       <c r="B55" t="inlineStr">
@@ -2244,16 +2232,16 @@
         <v>5</v>
       </c>
       <c r="E55" t="n">
-        <v>523.9827746987681</v>
+        <v>523.982774698768</v>
       </c>
       <c r="F55" t="n">
-        <v>-102.3009481541336</v>
+        <v>-102.3009481541335</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>102.3009481541336</v>
+        <v>102.3009481541335</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
@@ -2262,7 +2250,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="n">
+      <c r="A56" s="1" t="n">
         <v>44200</v>
       </c>
       <c r="B56" t="inlineStr">
@@ -2271,19 +2259,19 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>6307.420189327073</v>
+        <v>6307.42018932708</v>
       </c>
       <c r="D56" t="n">
         <v>5</v>
       </c>
       <c r="E56" t="n">
-        <v>3467.663791438691</v>
+        <v>3467.663791438696</v>
       </c>
       <c r="F56" t="n">
-        <v>2834.756397888382</v>
+        <v>2834.756397888384</v>
       </c>
       <c r="G56" t="n">
-        <v>710.4384169309047</v>
+        <v>710.4384169309052</v>
       </c>
       <c r="H56" t="n">
         <v>0</v>
@@ -2295,7 +2283,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="n">
+      <c r="A57" s="1" t="n">
         <v>44200</v>
       </c>
       <c r="B57" t="inlineStr">
@@ -2304,22 +2292,22 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>478.194732745178</v>
+        <v>478.1947327451785</v>
       </c>
       <c r="D57" t="n">
         <v>5</v>
       </c>
       <c r="E57" t="n">
-        <v>544.0318142230658</v>
+        <v>544.0318142230664</v>
       </c>
       <c r="F57" t="n">
-        <v>-70.83708147788775</v>
+        <v>-70.83708147788786</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>70.83708147788775</v>
+        <v>70.83708147788786</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
@@ -2328,7 +2316,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="n">
+      <c r="A58" s="1" t="n">
         <v>44200</v>
       </c>
       <c r="B58" t="inlineStr">
@@ -2337,22 +2325,22 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>3433.932346792895</v>
+        <v>3433.932346792908</v>
       </c>
       <c r="D58" t="n">
         <v>5</v>
       </c>
       <c r="E58" t="n">
-        <v>4676.99229323328</v>
+        <v>4676.992293233295</v>
       </c>
       <c r="F58" t="n">
-        <v>-1248.059946440385</v>
+        <v>-1248.059946440387</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>1318.897027918273</v>
+        <v>1318.897027918274</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
@@ -2361,7 +2349,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="n">
+      <c r="A59" s="1" t="n">
         <v>44200</v>
       </c>
       <c r="B59" t="inlineStr">
@@ -2376,13 +2364,13 @@
         <v>5</v>
       </c>
       <c r="E59" t="n">
-        <v>1749.776579561959</v>
+        <v>1749.776579561958</v>
       </c>
       <c r="F59" t="n">
         <v>1400.726774962242</v>
       </c>
       <c r="G59" t="n">
-        <v>21.27573423143196</v>
+        <v>21.27573423143166</v>
       </c>
       <c r="H59" t="n">
         <v>0</v>
@@ -2394,7 +2382,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="n">
+      <c r="A60" s="1" t="n">
         <v>44200</v>
       </c>
       <c r="B60" t="inlineStr">
@@ -2409,16 +2397,16 @@
         <v>5</v>
       </c>
       <c r="E60" t="n">
-        <v>1575.7754327425</v>
+        <v>1575.775432742499</v>
       </c>
       <c r="F60" t="n">
-        <v>-180.3998064935404</v>
+        <v>-180.3998064935397</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>180.3998064935404</v>
+        <v>180.3998064935397</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
@@ -2427,7 +2415,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="n">
+      <c r="A61" s="1" t="n">
         <v>44200</v>
       </c>
       <c r="B61" t="inlineStr">
@@ -2436,22 +2424,22 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>910.7717147793719</v>
+        <v>910.7717147793674</v>
       </c>
       <c r="D61" t="n">
         <v>5</v>
       </c>
       <c r="E61" t="n">
-        <v>1048.035239811616</v>
+        <v>1048.035239811611</v>
       </c>
       <c r="F61" t="n">
-        <v>-142.2635250322437</v>
+        <v>-142.2635250322435</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>322.6633315257841</v>
+        <v>322.6633315257832</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
@@ -2460,7 +2448,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="n">
+      <c r="A62" s="1" t="n">
         <v>44200</v>
       </c>
       <c r="B62" t="inlineStr">
@@ -2478,13 +2466,13 @@
         <v>2178.737988385124</v>
       </c>
       <c r="F62" t="n">
-        <v>-278.585123466268</v>
+        <v>-278.5851234662675</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>601.2484549920521</v>
+        <v>601.2484549920507</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -2493,7 +2481,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="n">
+      <c r="A63" s="1" t="n">
         <v>44564</v>
       </c>
       <c r="B63" t="inlineStr">
@@ -2514,7 +2502,7 @@
         <v>13915.73974257826</v>
       </c>
       <c r="G63" t="n">
-        <v>3461.767734772414</v>
+        <v>3461.767734772416</v>
       </c>
       <c r="H63" t="n">
         <v>0</v>
@@ -2526,7 +2514,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="n">
+      <c r="A64" s="1" t="n">
         <v>44564</v>
       </c>
       <c r="B64" t="inlineStr">
@@ -2535,19 +2523,19 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>13107.67151853135</v>
+        <v>13107.67151853136</v>
       </c>
       <c r="D64" t="n">
         <v>5</v>
       </c>
       <c r="E64" t="n">
-        <v>7305.048920480013</v>
+        <v>7305.048920480019</v>
       </c>
       <c r="F64" t="n">
-        <v>5797.622598051335</v>
+        <v>5797.622598051338</v>
       </c>
       <c r="G64" t="n">
-        <v>1507.381875493347</v>
+        <v>1507.381875493348</v>
       </c>
       <c r="H64" t="n">
         <v>0</v>
@@ -2559,7 +2547,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="n">
+      <c r="A65" s="1" t="n">
         <v>44928</v>
       </c>
       <c r="B65" t="inlineStr">
@@ -2568,13 +2556,13 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>1440.168391608437</v>
+        <v>1440.168391608433</v>
       </c>
       <c r="D65" t="n">
         <v>5</v>
       </c>
       <c r="E65" t="n">
-        <v>1402.294941173977</v>
+        <v>1402.294941173973</v>
       </c>
       <c r="F65" t="n">
         <v>32.87345043445976</v>
@@ -2592,7 +2580,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="n">
+      <c r="A66" s="1" t="n">
         <v>44928</v>
       </c>
       <c r="B66" t="inlineStr">
@@ -2601,19 +2589,19 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>612.2816651918947</v>
+        <v>612.2816651918874</v>
       </c>
       <c r="D66" t="n">
         <v>5</v>
       </c>
       <c r="E66" t="n">
-        <v>546.3572658823442</v>
+        <v>546.357265882338</v>
       </c>
       <c r="F66" t="n">
-        <v>60.92439930955049</v>
+        <v>60.92439930954947</v>
       </c>
       <c r="G66" t="n">
-        <v>15.84034382048313</v>
+        <v>15.84034382048286</v>
       </c>
       <c r="H66" t="n">
         <v>0</v>
@@ -2625,7 +2613,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="n">
+      <c r="A67" s="1" t="n">
         <v>44928</v>
       </c>
       <c r="B67" t="inlineStr">
@@ -2634,19 +2622,19 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>300.2446410899292</v>
+        <v>300.244641089932</v>
       </c>
       <c r="D67" t="n">
         <v>5</v>
       </c>
       <c r="E67" t="n">
-        <v>260.5514234018981</v>
+        <v>260.5514234019008</v>
       </c>
       <c r="F67" t="n">
-        <v>34.69321768803115</v>
+        <v>34.69321768803121</v>
       </c>
       <c r="G67" t="n">
-        <v>9.020236598888101</v>
+        <v>9.020236598888115</v>
       </c>
       <c r="H67" t="n">
         <v>0</v>
@@ -2658,7 +2646,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="n">
+      <c r="A68" s="1" t="n">
         <v>44928</v>
       </c>
       <c r="B68" t="inlineStr">
@@ -2667,19 +2655,19 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>183.2555453804925</v>
+        <v>183.2555453804853</v>
       </c>
       <c r="D68" t="n">
         <v>5</v>
       </c>
       <c r="E68" t="n">
-        <v>143.8121628416781</v>
+        <v>143.8121628416724</v>
       </c>
       <c r="F68" t="n">
-        <v>34.4433825388144</v>
+        <v>34.44338253881284</v>
       </c>
       <c r="G68" t="n">
-        <v>8.955279460091745</v>
+        <v>8.955279460091338</v>
       </c>
       <c r="H68" t="n">
         <v>0</v>
@@ -2691,7 +2679,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="n">
+      <c r="A69" s="1" t="n">
         <v>44928</v>
       </c>
       <c r="B69" t="inlineStr">
@@ -2700,22 +2688,22 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>232.7648594727298</v>
+        <v>232.7648594727289</v>
       </c>
       <c r="D69" t="n">
         <v>5</v>
       </c>
       <c r="E69" t="n">
-        <v>228.6736891956008</v>
+        <v>228.6736891956</v>
       </c>
       <c r="F69" t="n">
-        <v>-0.9088297228710758</v>
+        <v>-0.9088297228711895</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
       </c>
       <c r="H69" t="n">
-        <v>0.9088297228710758</v>
+        <v>0.9088297228711895</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
@@ -2724,7 +2712,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="2" t="n">
+      <c r="A70" s="1" t="n">
         <v>44928</v>
       </c>
       <c r="B70" t="inlineStr">
@@ -2733,19 +2721,19 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>330.2931424958551</v>
+        <v>330.2931424958515</v>
       </c>
       <c r="D70" t="n">
         <v>5</v>
       </c>
       <c r="E70" t="n">
-        <v>266.688582526909</v>
+        <v>266.6885825269061</v>
       </c>
       <c r="F70" t="n">
-        <v>58.60455996894609</v>
+        <v>58.60455996894541</v>
       </c>
       <c r="G70" t="n">
-        <v>15.0008898639795</v>
+        <v>15.0008898639793</v>
       </c>
       <c r="H70" t="n">
         <v>0</v>
@@ -2757,7 +2745,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="2" t="n">
+      <c r="A71" s="1" t="n">
         <v>44928</v>
       </c>
       <c r="B71" t="inlineStr">
@@ -2772,13 +2760,13 @@
         <v>5</v>
       </c>
       <c r="E71" t="n">
-        <v>2337.39012459009</v>
+        <v>2337.390124590089</v>
       </c>
       <c r="F71" t="n">
-        <v>795.3233524168036</v>
+        <v>795.323352416804</v>
       </c>
       <c r="G71" t="n">
-        <v>206.7840716283689</v>
+        <v>206.784071628369</v>
       </c>
       <c r="H71" t="n">
         <v>0</v>
@@ -2790,7 +2778,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="2" t="n">
+      <c r="A72" s="1" t="n">
         <v>44928</v>
       </c>
       <c r="B72" t="inlineStr">
@@ -2799,22 +2787,22 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>45.72284262730432</v>
+        <v>45.72284262730409</v>
       </c>
       <c r="D72" t="n">
         <v>5</v>
       </c>
       <c r="E72" t="n">
-        <v>50.67595477987773</v>
+        <v>50.67595477987746</v>
       </c>
       <c r="F72" t="n">
-        <v>-9.953112152573411</v>
+        <v>-9.953112152573375</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
       </c>
       <c r="H72" t="n">
-        <v>9.953112152573411</v>
+        <v>9.953112152573375</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
@@ -2823,7 +2811,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="2" t="n">
+      <c r="A73" s="1" t="n">
         <v>44928</v>
       </c>
       <c r="B73" t="inlineStr">
@@ -2838,16 +2826,16 @@
         <v>5</v>
       </c>
       <c r="E73" t="n">
-        <v>6500.533793261225</v>
+        <v>6500.533793261224</v>
       </c>
       <c r="F73" t="n">
-        <v>-1927.086815533789</v>
+        <v>-1927.086815533788</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
       </c>
       <c r="H73" t="n">
-        <v>1937.039927686363</v>
+        <v>1937.039927686362</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
@@ -2856,7 +2844,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="2" t="n">
+      <c r="A74" s="1" t="n">
         <v>45293</v>
       </c>
       <c r="B74" t="inlineStr">
@@ -2865,22 +2853,22 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>1017.0290739993</v>
+        <v>1017.029073999296</v>
       </c>
       <c r="D74" t="n">
         <v>5</v>
       </c>
       <c r="E74" t="n">
-        <v>709.7086890853335</v>
+        <v>709.708689085331</v>
       </c>
       <c r="F74" t="n">
-        <v>302.3203849139662</v>
+        <v>302.3203849139651</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
       </c>
       <c r="H74" t="n">
-        <v>1634.719542772396</v>
+        <v>1634.719542772397</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
@@ -2889,7 +2877,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="2" t="n">
+      <c r="A75" s="1" t="n">
         <v>45293</v>
       </c>
       <c r="B75" t="inlineStr">
@@ -2898,19 +2886,19 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>6044.779731599218</v>
+        <v>6044.77973159922</v>
       </c>
       <c r="D75" t="n">
         <v>5</v>
       </c>
       <c r="E75" t="n">
-        <v>3901.103245137075</v>
+        <v>3901.103245137081</v>
       </c>
       <c r="F75" t="n">
-        <v>2138.676486462144</v>
+        <v>2138.67648646214</v>
       </c>
       <c r="G75" t="n">
-        <v>131.0288053593343</v>
+        <v>131.0288053593331</v>
       </c>
       <c r="H75" t="n">
         <v>0</v>
@@ -2922,7 +2910,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="2" t="n">
+      <c r="A76" s="1" t="n">
         <v>45293</v>
       </c>
       <c r="B76" t="inlineStr">
@@ -2931,7 +2919,7 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>35578.65568058491</v>
+        <v>35578.65568058493</v>
       </c>
       <c r="D76" t="n">
         <v>5</v>
@@ -2940,10 +2928,10 @@
         <v>22639.18370773104</v>
       </c>
       <c r="F76" t="n">
-        <v>12934.47197285387</v>
+        <v>12934.47197285389</v>
       </c>
       <c r="G76" t="n">
-        <v>3362.962712942006</v>
+        <v>3362.962712942011</v>
       </c>
       <c r="H76" t="n">
         <v>0</v>
@@ -2955,7 +2943,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="2" t="n">
+      <c r="A77" s="1" t="n">
         <v>45293</v>
       </c>
       <c r="B77" t="inlineStr">
@@ -2970,13 +2958,13 @@
         <v>5</v>
       </c>
       <c r="E77" t="n">
-        <v>8853.06552767585</v>
+        <v>8853.065527675844</v>
       </c>
       <c r="F77" t="n">
-        <v>1186.719161581377</v>
+        <v>1186.719161581383</v>
       </c>
       <c r="G77" t="n">
-        <v>308.5469820111581</v>
+        <v>308.5469820111595</v>
       </c>
       <c r="H77" t="n">
         <v>0</v>
@@ -2988,7 +2976,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="2" t="n">
+      <c r="A78" s="1" t="n">
         <v>45293</v>
       </c>
       <c r="B78" t="inlineStr">
@@ -3006,10 +2994,10 @@
         <v>1937.258303926226</v>
       </c>
       <c r="F78" t="n">
-        <v>164.70677996623</v>
+        <v>164.7067799662302</v>
       </c>
       <c r="G78" t="n">
-        <v>42.8237627912198</v>
+        <v>42.82376279121986</v>
       </c>
       <c r="H78" t="n">
         <v>0</v>
@@ -3021,7 +3009,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="2" t="n">
+      <c r="A79" s="1" t="n">
         <v>43467</v>
       </c>
       <c r="B79" t="inlineStr">
@@ -3054,7 +3042,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="2" t="n">
+      <c r="A80" s="1" t="n">
         <v>43467</v>
       </c>
       <c r="B80" t="inlineStr">
@@ -3087,7 +3075,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="2" t="n">
+      <c r="A81" s="1" t="n">
         <v>43467</v>
       </c>
       <c r="B81" t="inlineStr">
@@ -3120,7 +3108,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="2" t="n">
+      <c r="A82" s="1" t="n">
         <v>43467</v>
       </c>
       <c r="B82" t="inlineStr">
@@ -3153,7 +3141,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="2" t="n">
+      <c r="A83" s="1" t="n">
         <v>43467</v>
       </c>
       <c r="B83" t="inlineStr">
@@ -3186,7 +3174,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="2" t="n">
+      <c r="A84" s="1" t="n">
         <v>43467</v>
       </c>
       <c r="B84" t="inlineStr">
@@ -3219,7 +3207,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="2" t="n">
+      <c r="A85" s="1" t="n">
         <v>43467</v>
       </c>
       <c r="B85" t="inlineStr">
@@ -3252,7 +3240,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="2" t="n">
+      <c r="A86" s="1" t="n">
         <v>43832</v>
       </c>
       <c r="B86" t="inlineStr">
@@ -3285,7 +3273,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="2" t="n">
+      <c r="A87" s="1" t="n">
         <v>43832</v>
       </c>
       <c r="B87" t="inlineStr">
@@ -3318,7 +3306,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="2" t="n">
+      <c r="A88" s="1" t="n">
         <v>43832</v>
       </c>
       <c r="B88" t="inlineStr">
@@ -3333,16 +3321,16 @@
         <v>5</v>
       </c>
       <c r="E88" t="n">
-        <v>8954.671812270219</v>
+        <v>8954.671812270217</v>
       </c>
       <c r="F88" t="n">
-        <v>2721.236433250111</v>
+        <v>2721.236433250113</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
       </c>
       <c r="H88" t="n">
-        <v>117.6552209432252</v>
+        <v>117.6552209432234</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
@@ -3351,7 +3339,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="2" t="n">
+      <c r="A89" s="1" t="n">
         <v>43832</v>
       </c>
       <c r="B89" t="inlineStr">
@@ -3372,7 +3360,7 @@
         <v>1408.309736767316</v>
       </c>
       <c r="G89" t="n">
-        <v>335.5701741142636</v>
+        <v>335.570174114264</v>
       </c>
       <c r="H89" t="n">
         <v>0</v>
@@ -3384,7 +3372,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="2" t="n">
+      <c r="A90" s="1" t="n">
         <v>43832</v>
       </c>
       <c r="B90" t="inlineStr">
@@ -3399,13 +3387,13 @@
         <v>5</v>
       </c>
       <c r="E90" t="n">
-        <v>4479.835906135109</v>
+        <v>4479.835906135108</v>
       </c>
       <c r="F90" t="n">
-        <v>1532.664553179204</v>
+        <v>1532.664553179205</v>
       </c>
       <c r="G90" t="n">
-        <v>398.492783826593</v>
+        <v>398.4927838265932</v>
       </c>
       <c r="H90" t="n">
         <v>0</v>
@@ -3417,7 +3405,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="2" t="n">
+      <c r="A91" s="1" t="n">
         <v>44200</v>
       </c>
       <c r="B91" t="inlineStr">
@@ -3450,7 +3438,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="2" t="n">
+      <c r="A92" s="1" t="n">
         <v>44200</v>
       </c>
       <c r="B92" t="inlineStr">
@@ -3483,7 +3471,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="2" t="n">
+      <c r="A93" s="1" t="n">
         <v>44200</v>
       </c>
       <c r="B93" t="inlineStr">
@@ -3516,7 +3504,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="2" t="n">
+      <c r="A94" s="1" t="n">
         <v>44200</v>
       </c>
       <c r="B94" t="inlineStr">
@@ -3549,7 +3537,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="2" t="n">
+      <c r="A95" s="1" t="n">
         <v>44200</v>
       </c>
       <c r="B95" t="inlineStr">
@@ -3564,10 +3552,10 @@
         <v>5</v>
       </c>
       <c r="E95" t="n">
-        <v>7138.74712853256</v>
+        <v>7138.747128532559</v>
       </c>
       <c r="F95" t="n">
-        <v>6980.390809893178</v>
+        <v>6980.390809893179</v>
       </c>
       <c r="G95" t="n">
         <v>1814.901610572226</v>
@@ -3582,7 +3570,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="2" t="n">
+      <c r="A96" s="1" t="n">
         <v>44200</v>
       </c>
       <c r="B96" t="inlineStr">
@@ -3597,13 +3585,13 @@
         <v>5</v>
       </c>
       <c r="E96" t="n">
-        <v>5026.287092382425</v>
+        <v>5026.287092382426</v>
       </c>
       <c r="F96" t="n">
-        <v>2367.19141070957</v>
+        <v>2367.191410709569</v>
       </c>
       <c r="G96" t="n">
-        <v>615.4697667844882</v>
+        <v>615.469766784488</v>
       </c>
       <c r="H96" t="n">
         <v>0</v>
@@ -3615,7 +3603,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="2" t="n">
+      <c r="A97" s="1" t="n">
         <v>44200</v>
       </c>
       <c r="B97" t="inlineStr">
@@ -3624,22 +3612,22 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>8141.136328895011</v>
+        <v>8141.136328895012</v>
       </c>
       <c r="D97" t="n">
         <v>5</v>
       </c>
       <c r="E97" t="n">
-        <v>9136.762007518902</v>
+        <v>9136.762007518906</v>
       </c>
       <c r="F97" t="n">
-        <v>-1000.625678623892</v>
+        <v>-1000.625678623894</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
       </c>
       <c r="H97" t="n">
-        <v>1000.625678623892</v>
+        <v>1000.625678623894</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
@@ -3648,7 +3636,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="2" t="n">
+      <c r="A98" s="1" t="n">
         <v>44200</v>
       </c>
       <c r="B98" t="inlineStr">
@@ -3672,7 +3660,7 @@
         <v>0</v>
       </c>
       <c r="H98" t="n">
-        <v>4060.96625054018</v>
+        <v>4060.966250540182</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
@@ -3681,7 +3669,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="2" t="n">
+      <c r="A99" s="1" t="n">
         <v>44564</v>
       </c>
       <c r="B99" t="inlineStr">
@@ -3696,13 +3684,13 @@
         <v>5</v>
       </c>
       <c r="E99" t="n">
-        <v>4768.905446205948</v>
+        <v>4768.905446205947</v>
       </c>
       <c r="F99" t="n">
         <v>6660.872677347626</v>
       </c>
       <c r="G99" t="n">
-        <v>675.9756709699359</v>
+        <v>675.9756709699357</v>
       </c>
       <c r="H99" t="n">
         <v>0</v>
@@ -3714,7 +3702,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="2" t="n">
+      <c r="A100" s="1" t="n">
         <v>44564</v>
       </c>
       <c r="B100" t="inlineStr">
@@ -3747,7 +3735,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="2" t="n">
+      <c r="A101" s="1" t="n">
         <v>44564</v>
       </c>
       <c r="B101" t="inlineStr">
@@ -3780,7 +3768,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="2" t="n">
+      <c r="A102" s="1" t="n">
         <v>44564</v>
       </c>
       <c r="B102" t="inlineStr">
@@ -3813,7 +3801,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="2" t="n">
+      <c r="A103" s="1" t="n">
         <v>44564</v>
       </c>
       <c r="B103" t="inlineStr">
@@ -3846,7 +3834,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="2" t="n">
+      <c r="A104" s="1" t="n">
         <v>44564</v>
       </c>
       <c r="B104" t="inlineStr">
@@ -3879,7 +3867,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="2" t="n">
+      <c r="A105" s="1" t="n">
         <v>44928</v>
       </c>
       <c r="B105" t="inlineStr">
@@ -3888,13 +3876,13 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>5591.193739557897</v>
+        <v>5591.193739557893</v>
       </c>
       <c r="D105" t="n">
         <v>5</v>
       </c>
       <c r="E105" t="n">
-        <v>5225.853474746881</v>
+        <v>5225.853474746878</v>
       </c>
       <c r="F105" t="n">
         <v>360.3402648110159</v>
@@ -3912,7 +3900,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="2" t="n">
+      <c r="A106" s="1" t="n">
         <v>44928</v>
       </c>
       <c r="B106" t="inlineStr">
@@ -3945,7 +3933,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="2" t="n">
+      <c r="A107" s="1" t="n">
         <v>44928</v>
       </c>
       <c r="B107" t="inlineStr">
@@ -3978,7 +3966,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="2" t="n">
+      <c r="A108" s="1" t="n">
         <v>44928</v>
       </c>
       <c r="B108" t="inlineStr">
@@ -4011,7 +3999,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="2" t="n">
+      <c r="A109" s="1" t="n">
         <v>44928</v>
       </c>
       <c r="B109" t="inlineStr">
@@ -4020,19 +4008,19 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>3585.609760083709</v>
+        <v>3585.609760083707</v>
       </c>
       <c r="D109" t="n">
         <v>5</v>
       </c>
       <c r="E109" t="n">
-        <v>3524.657479429261</v>
+        <v>3524.657479429258</v>
       </c>
       <c r="F109" t="n">
-        <v>55.95228065444871</v>
+        <v>55.95228065444917</v>
       </c>
       <c r="G109" t="n">
-        <v>14.54759297015667</v>
+        <v>14.54759297015678</v>
       </c>
       <c r="H109" t="n">
         <v>0</v>
@@ -4044,7 +4032,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="2" t="n">
+      <c r="A110" s="1" t="n">
         <v>44928</v>
       </c>
       <c r="B110" t="inlineStr">
@@ -4077,7 +4065,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="2" t="n">
+      <c r="A111" s="1" t="n">
         <v>44928</v>
       </c>
       <c r="B111" t="inlineStr">
@@ -4110,7 +4098,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="2" t="n">
+      <c r="A112" s="1" t="n">
         <v>45293</v>
       </c>
       <c r="B112" t="inlineStr">
@@ -4128,10 +4116,10 @@
         <v>3436.996086351303</v>
       </c>
       <c r="F112" t="n">
-        <v>1689.04731937447</v>
+        <v>1689.047319374471</v>
       </c>
       <c r="G112" t="n">
-        <v>377.0391719056481</v>
+        <v>377.0391719056482</v>
       </c>
       <c r="H112" t="n">
         <v>0</v>
@@ -4143,7 +4131,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="2" t="n">
+      <c r="A113" s="1" t="n">
         <v>45293</v>
       </c>
       <c r="B113" t="inlineStr">
@@ -4152,19 +4140,19 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>2022.446564473077</v>
+        <v>2022.446564473072</v>
       </c>
       <c r="D113" t="n">
         <v>5</v>
       </c>
       <c r="E113" t="n">
-        <v>1481.223911266514</v>
+        <v>1481.22391126651</v>
       </c>
       <c r="F113" t="n">
-        <v>536.2226532065629</v>
+        <v>536.2226532065615</v>
       </c>
       <c r="G113" t="n">
-        <v>139.4178898337063</v>
+        <v>139.417889833706</v>
       </c>
       <c r="H113" t="n">
         <v>0</v>
@@ -4176,7 +4164,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="2" t="n">
+      <c r="A114" s="1" t="n">
         <v>45293</v>
       </c>
       <c r="B114" t="inlineStr">
@@ -4185,19 +4173,19 @@
         </is>
       </c>
       <c r="C114" t="n">
-        <v>9502.722133110987</v>
+        <v>9502.722133110983</v>
       </c>
       <c r="D114" t="n">
         <v>5</v>
       </c>
       <c r="E114" t="n">
-        <v>6742.376775747302</v>
+        <v>6742.3767757473</v>
       </c>
       <c r="F114" t="n">
-        <v>2755.345357363684</v>
+        <v>2755.345357363683</v>
       </c>
       <c r="G114" t="n">
-        <v>716.3897929145579</v>
+        <v>716.3897929145577</v>
       </c>
       <c r="H114" t="n">
         <v>0</v>
@@ -4209,7 +4197,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="2" t="n">
+      <c r="A115" s="1" t="n">
         <v>45293</v>
       </c>
       <c r="B115" t="inlineStr">
@@ -4224,13 +4212,13 @@
         <v>5</v>
       </c>
       <c r="E115" t="n">
-        <v>8108.121080593044</v>
+        <v>8108.121080593047</v>
       </c>
       <c r="F115" t="n">
-        <v>3239.023409925318</v>
+        <v>3239.023409925317</v>
       </c>
       <c r="G115" t="n">
-        <v>842.1460865805826</v>
+        <v>842.1460865805824</v>
       </c>
       <c r="H115" t="n">
         <v>0</v>
@@ -4242,7 +4230,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="2" t="n">
+      <c r="A116" s="1" t="n">
         <v>45293</v>
       </c>
       <c r="B116" t="inlineStr">
@@ -4275,7 +4263,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="2" t="n">
+      <c r="A117" s="1" t="n">
         <v>45293</v>
       </c>
       <c r="B117" t="inlineStr">
@@ -4308,7 +4296,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="2" t="n">
+      <c r="A118" s="1" t="n">
         <v>45293</v>
       </c>
       <c r="B118" t="inlineStr">
@@ -4341,7 +4329,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="2" t="n">
+      <c r="A119" s="1" t="n">
         <v>43467</v>
       </c>
       <c r="B119" t="inlineStr">
@@ -4350,22 +4338,22 @@
         </is>
       </c>
       <c r="C119" t="n">
-        <v>1689.514503034668</v>
+        <v>1689.514503034663</v>
       </c>
       <c r="D119" t="n">
         <v>5</v>
       </c>
       <c r="E119" t="n">
-        <v>2248.887489002815</v>
+        <v>2248.887489002808</v>
       </c>
       <c r="F119" t="n">
-        <v>-564.3729859681462</v>
+        <v>-564.3729859681448</v>
       </c>
       <c r="G119" t="n">
         <v>0</v>
       </c>
       <c r="H119" t="n">
-        <v>564.3729859681462</v>
+        <v>564.3729859681448</v>
       </c>
       <c r="I119" t="inlineStr">
         <is>
@@ -4374,7 +4362,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="2" t="n">
+      <c r="A120" s="1" t="n">
         <v>43467</v>
       </c>
       <c r="B120" t="inlineStr">
@@ -4383,22 +4371,22 @@
         </is>
       </c>
       <c r="C120" t="n">
-        <v>409.8390923199695</v>
+        <v>409.8390923199722</v>
       </c>
       <c r="D120" t="n">
         <v>5</v>
       </c>
       <c r="E120" t="n">
-        <v>382.3096514754063</v>
+        <v>382.3096514754087</v>
       </c>
       <c r="F120" t="n">
-        <v>22.52944084456323</v>
+        <v>22.52944084456357</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
       </c>
       <c r="H120" t="n">
-        <v>541.843545123583</v>
+        <v>541.8435451235812</v>
       </c>
       <c r="I120" t="inlineStr">
         <is>
@@ -4407,7 +4395,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="2" t="n">
+      <c r="A121" s="1" t="n">
         <v>43467</v>
       </c>
       <c r="B121" t="inlineStr">
@@ -4416,22 +4404,22 @@
         </is>
       </c>
       <c r="C121" t="n">
-        <v>2872.888498862769</v>
+        <v>2872.888498862776</v>
       </c>
       <c r="D121" t="n">
         <v>5</v>
       </c>
       <c r="E121" t="n">
-        <v>2742.767636604648</v>
+        <v>2742.767636604654</v>
       </c>
       <c r="F121" t="n">
-        <v>125.1208622581207</v>
+        <v>125.1208622581221</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
       </c>
       <c r="H121" t="n">
-        <v>416.7226828654623</v>
+        <v>416.7226828654591</v>
       </c>
       <c r="I121" t="inlineStr">
         <is>
@@ -4440,7 +4428,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="2" t="n">
+      <c r="A122" s="1" t="n">
         <v>43467</v>
       </c>
       <c r="B122" t="inlineStr">
@@ -4449,22 +4437,22 @@
         </is>
       </c>
       <c r="C122" t="n">
-        <v>392.6312336782944</v>
+        <v>392.6312336782935</v>
       </c>
       <c r="D122" t="n">
         <v>5</v>
       </c>
       <c r="E122" t="n">
-        <v>474.0525428923219</v>
+        <v>474.052542892321</v>
       </c>
       <c r="F122" t="n">
-        <v>-86.42130921402753</v>
+        <v>-86.42130921402747</v>
       </c>
       <c r="G122" t="n">
         <v>0</v>
       </c>
       <c r="H122" t="n">
-        <v>503.1439920794898</v>
+        <v>503.1439920794866</v>
       </c>
       <c r="I122" t="inlineStr">
         <is>
@@ -4473,7 +4461,7 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="2" t="n">
+      <c r="A123" s="1" t="n">
         <v>43467</v>
       </c>
       <c r="B123" t="inlineStr">
@@ -4482,22 +4470,22 @@
         </is>
       </c>
       <c r="C123" t="n">
-        <v>2557.007887305812</v>
+        <v>2557.007887305805</v>
       </c>
       <c r="D123" t="n">
         <v>5</v>
       </c>
       <c r="E123" t="n">
-        <v>2480.951661899838</v>
+        <v>2480.951661899832</v>
       </c>
       <c r="F123" t="n">
-        <v>71.05622540597369</v>
+        <v>71.05622540597278</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
       </c>
       <c r="H123" t="n">
-        <v>432.0877666735161</v>
+        <v>432.0877666735138</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
@@ -4506,7 +4494,7 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="2" t="n">
+      <c r="A124" s="1" t="n">
         <v>43467</v>
       </c>
       <c r="B124" t="inlineStr">
@@ -4524,13 +4512,13 @@
         <v>1480.491143836333</v>
       </c>
       <c r="F124" t="n">
-        <v>-98.71900725697651</v>
+        <v>-98.71900725697674</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
       </c>
       <c r="H124" t="n">
-        <v>530.8067739304927</v>
+        <v>530.8067739304905</v>
       </c>
       <c r="I124" t="inlineStr">
         <is>
@@ -4539,7 +4527,7 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="2" t="n">
+      <c r="A125" s="1" t="n">
         <v>43467</v>
       </c>
       <c r="B125" t="inlineStr">
@@ -4557,13 +4545,13 @@
         <v>1010.194541679133</v>
       </c>
       <c r="F125" t="n">
-        <v>-300.4890688458414</v>
+        <v>-300.4890688458416</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
       </c>
       <c r="H125" t="n">
-        <v>831.2958427763341</v>
+        <v>831.2958427763322</v>
       </c>
       <c r="I125" t="inlineStr">
         <is>
@@ -4572,7 +4560,7 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="2" t="n">
+      <c r="A126" s="1" t="n">
         <v>43467</v>
       </c>
       <c r="B126" t="inlineStr">
@@ -4581,7 +4569,7 @@
         </is>
       </c>
       <c r="C126" t="n">
-        <v>12283.72533226162</v>
+        <v>12283.72533226163</v>
       </c>
       <c r="D126" t="n">
         <v>5</v>
@@ -4590,13 +4578,13 @@
         <v>12120.87118151976</v>
       </c>
       <c r="F126" t="n">
-        <v>157.8541507418631</v>
+        <v>157.8541507418704</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
       </c>
       <c r="H126" t="n">
-        <v>673.441692034471</v>
+        <v>673.4416920344618</v>
       </c>
       <c r="I126" t="inlineStr">
         <is>
@@ -4605,7 +4593,7 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="2" t="n">
+      <c r="A127" s="1" t="n">
         <v>43832</v>
       </c>
       <c r="B127" t="inlineStr">
@@ -4614,22 +4602,22 @@
         </is>
       </c>
       <c r="C127" t="n">
-        <v>604.7595642266569</v>
+        <v>604.7595642266642</v>
       </c>
       <c r="D127" t="n">
         <v>5</v>
       </c>
       <c r="E127" t="n">
-        <v>604.6749395868046</v>
+        <v>604.6749395868121</v>
       </c>
       <c r="F127" t="n">
-        <v>-4.915375360147664</v>
+        <v>-4.915375360147891</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
       </c>
       <c r="H127" t="n">
-        <v>678.3570673946186</v>
+        <v>678.3570673946097</v>
       </c>
       <c r="I127" t="inlineStr">
         <is>
@@ -4638,7 +4626,7 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="2" t="n">
+      <c r="A128" s="1" t="n">
         <v>43832</v>
       </c>
       <c r="B128" t="inlineStr">
@@ -4647,22 +4635,22 @@
         </is>
       </c>
       <c r="C128" t="n">
-        <v>199.5955895660836</v>
+        <v>199.5955895660845</v>
       </c>
       <c r="D128" t="n">
         <v>5</v>
       </c>
       <c r="E128" t="n">
-        <v>148.7903999142228</v>
+        <v>148.7903999142235</v>
       </c>
       <c r="F128" t="n">
-        <v>45.80518965186079</v>
+        <v>45.80518965186107</v>
       </c>
       <c r="G128" t="n">
         <v>0</v>
       </c>
       <c r="H128" t="n">
-        <v>632.5518777427578</v>
+        <v>632.5518777427486</v>
       </c>
       <c r="I128" t="inlineStr">
         <is>
@@ -4671,7 +4659,7 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="2" t="n">
+      <c r="A129" s="1" t="n">
         <v>43832</v>
       </c>
       <c r="B129" t="inlineStr">
@@ -4680,22 +4668,22 @@
         </is>
       </c>
       <c r="C129" t="n">
-        <v>109.5419485570928</v>
+        <v>109.5419485571001</v>
       </c>
       <c r="D129" t="n">
         <v>5</v>
       </c>
       <c r="E129" t="n">
-        <v>97.98882577182565</v>
+        <v>97.98882577183214</v>
       </c>
       <c r="F129" t="n">
-        <v>6.553122785267192</v>
+        <v>6.553122785267973</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
       </c>
       <c r="H129" t="n">
-        <v>625.9987549574906</v>
+        <v>625.9987549574806</v>
       </c>
       <c r="I129" t="inlineStr">
         <is>
@@ -4704,7 +4692,7 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="2" t="n">
+      <c r="A130" s="1" t="n">
         <v>43832</v>
       </c>
       <c r="B130" t="inlineStr">
@@ -4713,13 +4701,13 @@
         </is>
       </c>
       <c r="C130" t="n">
-        <v>4320.565218854006</v>
+        <v>4320.565218854008</v>
       </c>
       <c r="D130" t="n">
         <v>5</v>
       </c>
       <c r="E130" t="n">
-        <v>3749.703694791673</v>
+        <v>3749.703694791675</v>
       </c>
       <c r="F130" t="n">
         <v>565.861524062333</v>
@@ -4728,7 +4716,7 @@
         <v>0</v>
       </c>
       <c r="H130" t="n">
-        <v>60.13723089515759</v>
+        <v>60.13723089514758</v>
       </c>
       <c r="I130" t="inlineStr">
         <is>
@@ -4737,7 +4725,7 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="2" t="n">
+      <c r="A131" s="1" t="n">
         <v>43832</v>
       </c>
       <c r="B131" t="inlineStr">
@@ -4746,22 +4734,22 @@
         </is>
       </c>
       <c r="C131" t="n">
-        <v>68.02297079237906</v>
+        <v>68.02297079238633</v>
       </c>
       <c r="D131" t="n">
         <v>5</v>
       </c>
       <c r="E131" t="n">
-        <v>44.83529839971969</v>
+        <v>44.8352983997245</v>
       </c>
       <c r="F131" t="n">
-        <v>18.18767239265937</v>
+        <v>18.18767239266183</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
       </c>
       <c r="H131" t="n">
-        <v>41.94955850249822</v>
+        <v>41.94955850248575</v>
       </c>
       <c r="I131" t="inlineStr">
         <is>
@@ -4770,7 +4758,7 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="2" t="n">
+      <c r="A132" s="1" t="n">
         <v>43832</v>
       </c>
       <c r="B132" t="inlineStr">
@@ -4779,19 +4767,19 @@
         </is>
       </c>
       <c r="C132" t="n">
-        <v>2891.805008875635</v>
+        <v>2891.805008875633</v>
       </c>
       <c r="D132" t="n">
         <v>5</v>
       </c>
       <c r="E132" t="n">
-        <v>2220.641560615927</v>
+        <v>2220.641560615925</v>
       </c>
       <c r="F132" t="n">
-        <v>666.1634482597083</v>
+        <v>666.1634482597078</v>
       </c>
       <c r="G132" t="n">
-        <v>162.2956113368746</v>
+        <v>162.2956113368778</v>
       </c>
       <c r="H132" t="n">
         <v>0</v>
@@ -4803,7 +4791,7 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="2" t="n">
+      <c r="A133" s="1" t="n">
         <v>43832</v>
       </c>
       <c r="B133" t="inlineStr">
@@ -4821,10 +4809,10 @@
         <v>10481.16581678655</v>
       </c>
       <c r="F133" t="n">
-        <v>3601.575932120071</v>
+        <v>3601.575932120073</v>
       </c>
       <c r="G133" t="n">
-        <v>936.4097423512186</v>
+        <v>936.4097423512191</v>
       </c>
       <c r="H133" t="n">
         <v>0</v>
@@ -4836,7 +4824,7 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="2" t="n">
+      <c r="A134" s="1" t="n">
         <v>44200</v>
       </c>
       <c r="B134" t="inlineStr">
@@ -4851,13 +4839,13 @@
         <v>5</v>
       </c>
       <c r="E134" t="n">
-        <v>228.4269069872459</v>
+        <v>228.4269069872458</v>
       </c>
       <c r="F134" t="n">
-        <v>101.6875310626795</v>
+        <v>101.6875310626796</v>
       </c>
       <c r="G134" t="n">
-        <v>26.43875807629668</v>
+        <v>26.4387580762967</v>
       </c>
       <c r="H134" t="n">
         <v>0</v>
@@ -4869,7 +4857,7 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="2" t="n">
+      <c r="A135" s="1" t="n">
         <v>44200</v>
       </c>
       <c r="B135" t="inlineStr">
@@ -4884,16 +4872,16 @@
         <v>5</v>
       </c>
       <c r="E135" t="n">
-        <v>22836.93409756123</v>
+        <v>22836.93409756122</v>
       </c>
       <c r="F135" t="n">
-        <v>-6012.495059622168</v>
+        <v>-6012.495059622161</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
       </c>
       <c r="H135" t="n">
-        <v>6012.495059622168</v>
+        <v>6012.495059622161</v>
       </c>
       <c r="I135" t="inlineStr">
         <is>
@@ -4902,7 +4890,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="2" t="n">
+      <c r="A136" s="1" t="n">
         <v>44200</v>
       </c>
       <c r="B136" t="inlineStr">
@@ -4926,7 +4914,7 @@
         <v>0</v>
       </c>
       <c r="H136" t="n">
-        <v>4975.489909785366</v>
+        <v>4975.489909785359</v>
       </c>
       <c r="I136" t="inlineStr">
         <is>
@@ -4935,7 +4923,7 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="2" t="n">
+      <c r="A137" s="1" t="n">
         <v>44200</v>
       </c>
       <c r="B137" t="inlineStr">
@@ -4950,16 +4938,16 @@
         <v>5</v>
       </c>
       <c r="E137" t="n">
-        <v>284.867843923315</v>
+        <v>284.8678439233154</v>
       </c>
       <c r="F137" t="n">
-        <v>236.3044798146333</v>
+        <v>236.3044798146329</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
       </c>
       <c r="H137" t="n">
-        <v>4739.185429970733</v>
+        <v>4739.185429970727</v>
       </c>
       <c r="I137" t="inlineStr">
         <is>
@@ -4968,7 +4956,7 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="2" t="n">
+      <c r="A138" s="1" t="n">
         <v>44200</v>
       </c>
       <c r="B138" t="inlineStr">
@@ -4977,13 +4965,13 @@
         </is>
       </c>
       <c r="C138" t="n">
-        <v>2627.780054142848</v>
+        <v>2627.780054142847</v>
       </c>
       <c r="D138" t="n">
         <v>5</v>
       </c>
       <c r="E138" t="n">
-        <v>1788.899970894606</v>
+        <v>1788.899970894605</v>
       </c>
       <c r="F138" t="n">
         <v>833.8800832482423</v>
@@ -4992,7 +4980,7 @@
         <v>0</v>
       </c>
       <c r="H138" t="n">
-        <v>3905.305346722491</v>
+        <v>3905.305346722485</v>
       </c>
       <c r="I138" t="inlineStr">
         <is>
@@ -5001,7 +4989,7 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="2" t="n">
+      <c r="A139" s="1" t="n">
         <v>44200</v>
       </c>
       <c r="B139" t="inlineStr">
@@ -5019,13 +5007,13 @@
         <v>341.5334287201753</v>
       </c>
       <c r="F139" t="n">
-        <v>-71.20921470209976</v>
+        <v>-71.20921470209981</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
       </c>
       <c r="H139" t="n">
-        <v>3976.514561424591</v>
+        <v>3976.514561424584</v>
       </c>
       <c r="I139" t="inlineStr">
         <is>
@@ -5034,7 +5022,7 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="2" t="n">
+      <c r="A140" s="1" t="n">
         <v>44200</v>
       </c>
       <c r="B140" t="inlineStr">
@@ -5049,16 +5037,16 @@
         <v>5</v>
       </c>
       <c r="E140" t="n">
-        <v>1486.976969459853</v>
+        <v>1486.976969459854</v>
       </c>
       <c r="F140" t="n">
-        <v>-170.7668311840973</v>
+        <v>-170.7668311840976</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
       </c>
       <c r="H140" t="n">
-        <v>4147.281392608688</v>
+        <v>4147.281392608682</v>
       </c>
       <c r="I140" t="inlineStr">
         <is>
@@ -5067,7 +5055,7 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="2" t="n">
+      <c r="A141" s="1" t="n">
         <v>44200</v>
       </c>
       <c r="B141" t="inlineStr">
@@ -5076,22 +5064,22 @@
         </is>
       </c>
       <c r="C141" t="n">
-        <v>386.1575180795418</v>
+        <v>386.1575180795426</v>
       </c>
       <c r="D141" t="n">
         <v>5</v>
       </c>
       <c r="E141" t="n">
-        <v>778.9473608235378</v>
+        <v>778.9473608235394</v>
       </c>
       <c r="F141" t="n">
-        <v>-397.789842743996</v>
+        <v>-397.7898427439968</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
       </c>
       <c r="H141" t="n">
-        <v>4545.071235352684</v>
+        <v>4545.071235352679</v>
       </c>
       <c r="I141" t="inlineStr">
         <is>
@@ -5100,7 +5088,7 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="2" t="n">
+      <c r="A142" s="1" t="n">
         <v>44564</v>
       </c>
       <c r="B142" t="inlineStr">
@@ -5115,13 +5103,13 @@
         <v>5</v>
       </c>
       <c r="E142" t="n">
-        <v>12471.87075545512</v>
+        <v>12471.87075545514</v>
       </c>
       <c r="F142" t="n">
-        <v>15441.19028849659</v>
+        <v>15441.19028849657</v>
       </c>
       <c r="G142" t="n">
-        <v>2832.990953817416</v>
+        <v>2832.990953817413</v>
       </c>
       <c r="H142" t="n">
         <v>0</v>
@@ -5133,7 +5121,7 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="2" t="n">
+      <c r="A143" s="1" t="n">
         <v>44564</v>
       </c>
       <c r="B143" t="inlineStr">
@@ -5151,7 +5139,7 @@
         <v>2046.412774294338</v>
       </c>
       <c r="F143" t="n">
-        <v>765.3719250716435</v>
+        <v>765.3719250716433</v>
       </c>
       <c r="G143" t="n">
         <v>198.9967005186273</v>
@@ -5166,7 +5154,7 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="2" t="n">
+      <c r="A144" s="1" t="n">
         <v>44928</v>
       </c>
       <c r="B144" t="inlineStr">
@@ -5199,7 +5187,7 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="2" t="n">
+      <c r="A145" s="1" t="n">
         <v>44928</v>
       </c>
       <c r="B145" t="inlineStr">
@@ -5214,13 +5202,13 @@
         <v>5</v>
       </c>
       <c r="E145" t="n">
-        <v>7654.142286008716</v>
+        <v>7654.142286008719</v>
       </c>
       <c r="F145" t="n">
-        <v>654.1254026621164</v>
+        <v>654.1254026621136</v>
       </c>
       <c r="G145" t="n">
-        <v>170.0726046921503</v>
+        <v>170.0726046921496</v>
       </c>
       <c r="H145" t="n">
         <v>0</v>
@@ -5232,7 +5220,7 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="2" t="n">
+      <c r="A146" s="1" t="n">
         <v>44928</v>
       </c>
       <c r="B146" t="inlineStr">
@@ -5241,16 +5229,16 @@
         </is>
       </c>
       <c r="C146" t="n">
-        <v>16611.41378593623</v>
+        <v>16611.41378593624</v>
       </c>
       <c r="D146" t="n">
         <v>5</v>
       </c>
       <c r="E146" t="n">
-        <v>9375.795168808791</v>
+        <v>9375.795168808796</v>
       </c>
       <c r="F146" t="n">
-        <v>7230.61861712744</v>
+        <v>7230.618617127442</v>
       </c>
       <c r="G146" t="n">
         <v>1879.960840453135</v>
@@ -5265,7 +5253,7 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="2" t="n">
+      <c r="A147" s="1" t="n">
         <v>44928</v>
       </c>
       <c r="B147" t="inlineStr">
@@ -5280,13 +5268,13 @@
         <v>5</v>
       </c>
       <c r="E147" t="n">
-        <v>5622.068346074855</v>
+        <v>5622.068346074856</v>
       </c>
       <c r="F147" t="n">
-        <v>1149.444526520331</v>
+        <v>1149.44452652033</v>
       </c>
       <c r="G147" t="n">
-        <v>298.8555768952861</v>
+        <v>298.8555768952859</v>
       </c>
       <c r="H147" t="n">
         <v>0</v>
@@ -5298,7 +5286,7 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="2" t="n">
+      <c r="A148" s="1" t="n">
         <v>44928</v>
       </c>
       <c r="B148" t="inlineStr">
@@ -5313,16 +5301,16 @@
         <v>5</v>
       </c>
       <c r="E148" t="n">
-        <v>1953.041010639025</v>
+        <v>1953.041010639024</v>
       </c>
       <c r="F148" t="n">
-        <v>-68.42972246004274</v>
+        <v>-68.42972246004138</v>
       </c>
       <c r="G148" t="n">
         <v>0</v>
       </c>
       <c r="H148" t="n">
-        <v>68.42972246004274</v>
+        <v>68.42972246004138</v>
       </c>
       <c r="I148" t="inlineStr">
         <is>
@@ -5331,7 +5319,7 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="2" t="n">
+      <c r="A149" s="1" t="n">
         <v>45293</v>
       </c>
       <c r="B149" t="inlineStr">
@@ -5346,13 +5334,13 @@
         <v>5</v>
       </c>
       <c r="E149" t="n">
-        <v>24040.38658829579</v>
+        <v>24040.3865882958</v>
       </c>
       <c r="F149" t="n">
-        <v>10201.51542026386</v>
+        <v>10201.51542026385</v>
       </c>
       <c r="G149" t="n">
-        <v>2634.602281428993</v>
+        <v>2634.60228142899</v>
       </c>
       <c r="H149" t="n">
         <v>0</v>
@@ -5364,7 +5352,7 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="2" t="n">
+      <c r="A150" s="1" t="n">
         <v>45293</v>
       </c>
       <c r="B150" t="inlineStr">
@@ -5373,19 +5361,19 @@
         </is>
       </c>
       <c r="C150" t="n">
-        <v>31944.51175832204</v>
+        <v>31944.51175832203</v>
       </c>
       <c r="D150" t="n">
         <v>5</v>
       </c>
       <c r="E150" t="n">
-        <v>20811.45112687072</v>
+        <v>20811.45112687071</v>
       </c>
       <c r="F150" t="n">
-        <v>11128.06063145132</v>
+        <v>11128.06063145131</v>
       </c>
       <c r="G150" t="n">
-        <v>2893.295764177345</v>
+        <v>2893.295764177341</v>
       </c>
       <c r="H150" t="n">
         <v>0</v>
@@ -5397,7 +5385,7 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="2" t="n">
+      <c r="A151" s="1" t="n">
         <v>45293</v>
       </c>
       <c r="B151" t="inlineStr">
@@ -5412,13 +5400,13 @@
         <v>5</v>
       </c>
       <c r="E151" t="n">
-        <v>3396.06195588735</v>
+        <v>3396.061955887349</v>
       </c>
       <c r="F151" t="n">
-        <v>451.6946630509638</v>
+        <v>451.6946630509647</v>
       </c>
       <c r="G151" t="n">
-        <v>117.4406123932506</v>
+        <v>117.4406123932508</v>
       </c>
       <c r="H151" t="n">
         <v>0</v>
@@ -5430,7 +5418,7 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="2" t="n">
+      <c r="A152" s="1" t="n">
         <v>43467</v>
       </c>
       <c r="B152" t="inlineStr">
@@ -5439,22 +5427,22 @@
         </is>
       </c>
       <c r="C152" t="n">
-        <v>274.4119784489558</v>
+        <v>274.411978448954</v>
       </c>
       <c r="D152" t="n">
         <v>5</v>
       </c>
       <c r="E152" t="n">
-        <v>365.2953357909274</v>
+        <v>365.2953357909249</v>
       </c>
       <c r="F152" t="n">
-        <v>-95.88335734197159</v>
+        <v>-95.88335734197096</v>
       </c>
       <c r="G152" t="n">
         <v>0</v>
       </c>
       <c r="H152" t="n">
-        <v>95.88335734197159</v>
+        <v>95.88335734197096</v>
       </c>
       <c r="I152" t="inlineStr">
         <is>
@@ -5463,7 +5451,7 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="2" t="n">
+      <c r="A153" s="1" t="n">
         <v>43467</v>
       </c>
       <c r="B153" t="inlineStr">
@@ -5472,19 +5460,19 @@
         </is>
       </c>
       <c r="C153" t="n">
-        <v>5785.827603339607</v>
+        <v>5785.827603339605</v>
       </c>
       <c r="D153" t="n">
         <v>5</v>
       </c>
       <c r="E153" t="n">
-        <v>5393.34299199399</v>
+        <v>5393.342991993987</v>
       </c>
       <c r="F153" t="n">
-        <v>387.4846113456169</v>
+        <v>387.4846113456179</v>
       </c>
       <c r="G153" t="n">
-        <v>75.8163260409478</v>
+        <v>75.8163260409482</v>
       </c>
       <c r="H153" t="n">
         <v>0</v>
@@ -5496,7 +5484,7 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="2" t="n">
+      <c r="A154" s="1" t="n">
         <v>43467</v>
       </c>
       <c r="B154" t="inlineStr">
@@ -5505,13 +5493,13 @@
         </is>
       </c>
       <c r="C154" t="n">
-        <v>1886.529037081576</v>
+        <v>1886.529037081575</v>
       </c>
       <c r="D154" t="n">
         <v>5</v>
       </c>
       <c r="E154" t="n">
-        <v>1801.520557789828</v>
+        <v>1801.520557789826</v>
       </c>
       <c r="F154" t="n">
         <v>80.0084792917487</v>
@@ -5529,7 +5517,7 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="2" t="n">
+      <c r="A155" s="1" t="n">
         <v>43467</v>
       </c>
       <c r="B155" t="inlineStr">
@@ -5538,19 +5526,19 @@
         </is>
       </c>
       <c r="C155" t="n">
-        <v>1694.662080295055</v>
+        <v>1694.662080295053</v>
       </c>
       <c r="D155" t="n">
         <v>5</v>
       </c>
       <c r="E155" t="n">
-        <v>1644.668015553174</v>
+        <v>1644.668015553172</v>
       </c>
       <c r="F155" t="n">
-        <v>44.99406474188027</v>
+        <v>44.99406474188049</v>
       </c>
       <c r="G155" t="n">
-        <v>11.69845683288887</v>
+        <v>11.69845683288893</v>
       </c>
       <c r="H155" t="n">
         <v>0</v>
@@ -5562,7 +5550,7 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="2" t="n">
+      <c r="A156" s="1" t="n">
         <v>43467</v>
       </c>
       <c r="B156" t="inlineStr">
@@ -5571,22 +5559,22 @@
         </is>
       </c>
       <c r="C156" t="n">
-        <v>2063.807821522604</v>
+        <v>2063.807821522603</v>
       </c>
       <c r="D156" t="n">
         <v>5</v>
       </c>
       <c r="E156" t="n">
-        <v>2490.289671581119</v>
+        <v>2490.289671581117</v>
       </c>
       <c r="F156" t="n">
-        <v>-431.4818500585147</v>
+        <v>-431.4818500585138</v>
       </c>
       <c r="G156" t="n">
         <v>0</v>
       </c>
       <c r="H156" t="n">
-        <v>431.4818500585147</v>
+        <v>431.4818500585138</v>
       </c>
       <c r="I156" t="inlineStr">
         <is>
@@ -5595,7 +5583,7 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="2" t="n">
+      <c r="A157" s="1" t="n">
         <v>43467</v>
       </c>
       <c r="B157" t="inlineStr">
@@ -5613,13 +5601,13 @@
         <v>5716.428571428572</v>
       </c>
       <c r="F157" t="n">
-        <v>-1048.531185704555</v>
+        <v>-1048.531185704554</v>
       </c>
       <c r="G157" t="n">
         <v>0</v>
       </c>
       <c r="H157" t="n">
-        <v>1480.01303576307</v>
+        <v>1480.013035763068</v>
       </c>
       <c r="I157" t="inlineStr">
         <is>
@@ -5628,7 +5616,7 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="2" t="n">
+      <c r="A158" s="1" t="n">
         <v>43832</v>
       </c>
       <c r="B158" t="inlineStr">
@@ -5652,7 +5640,7 @@
         <v>0</v>
       </c>
       <c r="H158" t="n">
-        <v>1448.719819827481</v>
+        <v>1448.719819827479</v>
       </c>
       <c r="I158" t="inlineStr">
         <is>
@@ -5661,7 +5649,7 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="2" t="n">
+      <c r="A159" s="1" t="n">
         <v>43832</v>
       </c>
       <c r="B159" t="inlineStr">
@@ -5682,7 +5670,7 @@
         <v>5050.89442434081</v>
       </c>
       <c r="G159" t="n">
-        <v>936.5653971734655</v>
+        <v>936.565397173466</v>
       </c>
       <c r="H159" t="n">
         <v>0</v>
@@ -5694,7 +5682,7 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="2" t="n">
+      <c r="A160" s="1" t="n">
         <v>43832</v>
       </c>
       <c r="B160" t="inlineStr">
@@ -5709,13 +5697,13 @@
         <v>5</v>
       </c>
       <c r="E160" t="n">
-        <v>2398.845078929113</v>
+        <v>2398.845078929112</v>
       </c>
       <c r="F160" t="n">
-        <v>1038.443479145562</v>
+        <v>1038.443479145563</v>
       </c>
       <c r="G160" t="n">
-        <v>269.9953045778462</v>
+        <v>269.9953045778464</v>
       </c>
       <c r="H160" t="n">
         <v>0</v>
@@ -5727,7 +5715,7 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="2" t="n">
+      <c r="A161" s="1" t="n">
         <v>43832</v>
       </c>
       <c r="B161" t="inlineStr">
@@ -5760,7 +5748,7 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="2" t="n">
+      <c r="A162" s="1" t="n">
         <v>43832</v>
       </c>
       <c r="B162" t="inlineStr">
@@ -5775,13 +5763,13 @@
         <v>5</v>
       </c>
       <c r="E162" t="n">
-        <v>4482.108903155586</v>
+        <v>4482.108903155585</v>
       </c>
       <c r="F162" t="n">
-        <v>3206.245748854344</v>
+        <v>3206.245748854345</v>
       </c>
       <c r="G162" t="n">
-        <v>833.6238947021295</v>
+        <v>833.6238947021297</v>
       </c>
       <c r="H162" t="n">
         <v>0</v>
@@ -5793,7 +5781,7 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="2" t="n">
+      <c r="A163" s="1" t="n">
         <v>43832</v>
       </c>
       <c r="B163" t="inlineStr">
@@ -5826,7 +5814,7 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="2" t="n">
+      <c r="A164" s="1" t="n">
         <v>43832</v>
       </c>
       <c r="B164" t="inlineStr">
@@ -5841,13 +5829,13 @@
         <v>5</v>
       </c>
       <c r="E164" t="n">
-        <v>5894.971903267023</v>
+        <v>5894.971903267022</v>
       </c>
       <c r="F164" t="n">
-        <v>219.4792889493774</v>
+        <v>219.4792889493783</v>
       </c>
       <c r="G164" t="n">
-        <v>57.06461512683813</v>
+        <v>57.06461512683836</v>
       </c>
       <c r="H164" t="n">
         <v>0</v>
@@ -5859,7 +5847,7 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="2" t="n">
+      <c r="A165" s="1" t="n">
         <v>44200</v>
       </c>
       <c r="B165" t="inlineStr">
@@ -5892,7 +5880,7 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="2" t="n">
+      <c r="A166" s="1" t="n">
         <v>44200</v>
       </c>
       <c r="B166" t="inlineStr">
@@ -5925,7 +5913,7 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="2" t="n">
+      <c r="A167" s="1" t="n">
         <v>44200</v>
       </c>
       <c r="B167" t="inlineStr">
@@ -5940,16 +5928,16 @@
         <v>5</v>
       </c>
       <c r="E167" t="n">
-        <v>7257.162267544541</v>
+        <v>7257.16226754454</v>
       </c>
       <c r="F167" t="n">
-        <v>1087.746022213691</v>
+        <v>1087.746022213692</v>
       </c>
       <c r="G167" t="n">
         <v>0</v>
       </c>
       <c r="H167" t="n">
-        <v>1370.067132108046</v>
+        <v>1370.067132108044</v>
       </c>
       <c r="I167" t="inlineStr">
         <is>
@@ -5958,7 +5946,7 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="2" t="n">
+      <c r="A168" s="1" t="n">
         <v>44200</v>
       </c>
       <c r="B168" t="inlineStr">
@@ -5967,19 +5955,19 @@
         </is>
       </c>
       <c r="C168" t="n">
-        <v>7133.256544355601</v>
+        <v>7133.2565443556</v>
       </c>
       <c r="D168" t="n">
         <v>5</v>
       </c>
       <c r="E168" t="n">
-        <v>3233.01941731631</v>
+        <v>3233.019417316309</v>
       </c>
       <c r="F168" t="n">
-        <v>3895.237127039292</v>
+        <v>3895.237127039291</v>
       </c>
       <c r="G168" t="n">
-        <v>656.5441986821239</v>
+        <v>656.5441986821241</v>
       </c>
       <c r="H168" t="n">
         <v>0</v>
@@ -5991,7 +5979,7 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="2" t="n">
+      <c r="A169" s="1" t="n">
         <v>44200</v>
       </c>
       <c r="B169" t="inlineStr">
@@ -6024,7 +6012,7 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="2" t="n">
+      <c r="A170" s="1" t="n">
         <v>44200</v>
       </c>
       <c r="B170" t="inlineStr">
@@ -6057,7 +6045,7 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="2" t="n">
+      <c r="A171" s="1" t="n">
         <v>44564</v>
       </c>
       <c r="B171" t="inlineStr">
@@ -6066,22 +6054,22 @@
         </is>
       </c>
       <c r="C171" t="n">
-        <v>2.910260180993646</v>
+        <v>2.910260180995465</v>
       </c>
       <c r="D171" t="n">
         <v>5</v>
       </c>
       <c r="E171" t="n">
-        <v>1.088386654772878</v>
+        <v>1.088386654773558</v>
       </c>
       <c r="F171" t="n">
-        <v>-3.178126473779232</v>
+        <v>-3.178126473778093</v>
       </c>
       <c r="G171" t="n">
         <v>0</v>
       </c>
       <c r="H171" t="n">
-        <v>1076.955665144103</v>
+        <v>1076.955665144101</v>
       </c>
       <c r="I171" t="inlineStr">
         <is>
@@ -6090,7 +6078,7 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="2" t="n">
+      <c r="A172" s="1" t="n">
         <v>44564</v>
       </c>
       <c r="B172" t="inlineStr">
@@ -6099,13 +6087,13 @@
         </is>
       </c>
       <c r="C172" t="n">
-        <v>1488.849669918509</v>
+        <v>1488.849669918514</v>
       </c>
       <c r="D172" t="n">
         <v>5</v>
       </c>
       <c r="E172" t="n">
-        <v>1154.514159614134</v>
+        <v>1154.51415961414</v>
       </c>
       <c r="F172" t="n">
         <v>329.3355103043746</v>
@@ -6114,7 +6102,7 @@
         <v>0</v>
       </c>
       <c r="H172" t="n">
-        <v>747.620154839728</v>
+        <v>747.6201548397269</v>
       </c>
       <c r="I172" t="inlineStr">
         <is>
@@ -6123,7 +6111,7 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="2" t="n">
+      <c r="A173" s="1" t="n">
         <v>44564</v>
       </c>
       <c r="B173" t="inlineStr">
@@ -6144,7 +6132,7 @@
         <v>3955.808718177559</v>
       </c>
       <c r="G173" t="n">
-        <v>834.1290264678361</v>
+        <v>834.1290264678364</v>
       </c>
       <c r="H173" t="n">
         <v>0</v>
@@ -6156,7 +6144,7 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="2" t="n">
+      <c r="A174" s="1" t="n">
         <v>44564</v>
       </c>
       <c r="B174" t="inlineStr">
@@ -6171,13 +6159,13 @@
         <v>5</v>
       </c>
       <c r="E174" t="n">
-        <v>3212.32962744118</v>
+        <v>3212.329627441179</v>
       </c>
       <c r="F174" t="n">
-        <v>2547.83829189257</v>
+        <v>2547.838291892571</v>
       </c>
       <c r="G174" t="n">
-        <v>662.4379558920682</v>
+        <v>662.4379558920684</v>
       </c>
       <c r="H174" t="n">
         <v>0</v>
@@ -6189,7 +6177,7 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="2" t="n">
+      <c r="A175" s="1" t="n">
         <v>44564</v>
       </c>
       <c r="B175" t="inlineStr">
@@ -6222,7 +6210,7 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="2" t="n">
+      <c r="A176" s="1" t="n">
         <v>44928</v>
       </c>
       <c r="B176" t="inlineStr">
@@ -6231,19 +6219,19 @@
         </is>
       </c>
       <c r="C176" t="n">
-        <v>2456.769854875507</v>
+        <v>2456.7698548755</v>
       </c>
       <c r="D176" t="n">
         <v>5</v>
       </c>
       <c r="E176" t="n">
-        <v>2244.49961403626</v>
+        <v>2244.499614036252</v>
       </c>
       <c r="F176" t="n">
-        <v>207.2702408392474</v>
+        <v>207.2702408392479</v>
       </c>
       <c r="G176" t="n">
-        <v>53.89026261820433</v>
+        <v>53.89026261820445</v>
       </c>
       <c r="H176" t="n">
         <v>0</v>
@@ -6255,7 +6243,7 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="2" t="n">
+      <c r="A177" s="1" t="n">
         <v>44928</v>
       </c>
       <c r="B177" t="inlineStr">
@@ -6288,7 +6276,7 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="2" t="n">
+      <c r="A178" s="1" t="n">
         <v>44928</v>
       </c>
       <c r="B178" t="inlineStr">
@@ -6297,19 +6285,19 @@
         </is>
       </c>
       <c r="C178" t="n">
-        <v>8525.150133794144</v>
+        <v>8525.150133794141</v>
       </c>
       <c r="D178" t="n">
         <v>5</v>
       </c>
       <c r="E178" t="n">
-        <v>6842.218244561035</v>
+        <v>6842.218244561033</v>
       </c>
       <c r="F178" t="n">
-        <v>1677.931889233109</v>
+        <v>1677.931889233108</v>
       </c>
       <c r="G178" t="n">
-        <v>436.2622912006084</v>
+        <v>436.262291200608</v>
       </c>
       <c r="H178" t="n">
         <v>0</v>
@@ -6321,7 +6309,7 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="2" t="n">
+      <c r="A179" s="1" t="n">
         <v>44928</v>
       </c>
       <c r="B179" t="inlineStr">
@@ -6336,10 +6324,10 @@
         <v>5</v>
       </c>
       <c r="E179" t="n">
-        <v>7233.920972324148</v>
+        <v>7233.920972324147</v>
       </c>
       <c r="F179" t="n">
-        <v>6219.980675438896</v>
+        <v>6219.980675438897</v>
       </c>
       <c r="G179" t="n">
         <v>1617.194975614113</v>
@@ -6354,7 +6342,7 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="2" t="n">
+      <c r="A180" s="1" t="n">
         <v>44928</v>
       </c>
       <c r="B180" t="inlineStr">
@@ -6387,7 +6375,7 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="2" t="n">
+      <c r="A181" s="1" t="n">
         <v>45293</v>
       </c>
       <c r="B181" t="inlineStr">
@@ -6396,7 +6384,7 @@
         </is>
       </c>
       <c r="C181" t="n">
-        <v>21204.12945274452</v>
+        <v>21204.12945274454</v>
       </c>
       <c r="D181" t="n">
         <v>5</v>
@@ -6405,10 +6393,10 @@
         <v>13883.41063370549</v>
       </c>
       <c r="F181" t="n">
-        <v>7315.718819039039</v>
+        <v>7315.718819039046</v>
       </c>
       <c r="G181" t="n">
-        <v>1108.752057034307</v>
+        <v>1108.752057034309</v>
       </c>
       <c r="H181" t="n">
         <v>0</v>
@@ -6420,7 +6408,7 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="2" t="n">
+      <c r="A182" s="1" t="n">
         <v>45293</v>
       </c>
       <c r="B182" t="inlineStr">
@@ -6435,7 +6423,7 @@
         <v>5</v>
       </c>
       <c r="E182" t="n">
-        <v>8458.837315033694</v>
+        <v>8458.837315033692</v>
       </c>
       <c r="F182" t="n">
         <v>14717.92704706195</v>
@@ -6453,7 +6441,7 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="2" t="n">
+      <c r="A183" s="1" t="n">
         <v>45293</v>
       </c>
       <c r="B183" t="inlineStr">
@@ -6462,19 +6450,19 @@
         </is>
       </c>
       <c r="C183" t="n">
-        <v>5966.149913649788</v>
+        <v>5966.149913649784</v>
       </c>
       <c r="D183" t="n">
         <v>5</v>
       </c>
       <c r="E183" t="n">
-        <v>4790.513940478068</v>
+        <v>4790.513940478066</v>
       </c>
       <c r="F183" t="n">
-        <v>1170.63597317172</v>
+        <v>1170.635973171718</v>
       </c>
       <c r="G183" t="n">
-        <v>304.3653530246473</v>
+        <v>304.3653530246468</v>
       </c>
       <c r="H183" t="n">
         <v>0</v>
@@ -6486,7 +6474,7 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="2" t="n">
+      <c r="A184" s="1" t="n">
         <v>45293</v>
       </c>
       <c r="B184" t="inlineStr">
@@ -6501,13 +6489,13 @@
         <v>5</v>
       </c>
       <c r="E184" t="n">
-        <v>15539.53873074934</v>
+        <v>15539.53873074935</v>
       </c>
       <c r="F184" t="n">
-        <v>701.1443647932356</v>
+        <v>701.1443647932338</v>
       </c>
       <c r="G184" t="n">
-        <v>182.2975348462413</v>
+        <v>182.2975348462408</v>
       </c>
       <c r="H184" t="n">
         <v>0</v>
@@ -6519,7 +6507,7 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="2" t="n">
+      <c r="A185" s="1" t="n">
         <v>45293</v>
       </c>
       <c r="B185" t="inlineStr">
@@ -6534,13 +6522,13 @@
         <v>5</v>
       </c>
       <c r="E185" t="n">
-        <v>9997.087885100766</v>
+        <v>9997.087885100767</v>
       </c>
       <c r="F185" t="n">
-        <v>3993.273534994891</v>
+        <v>3993.273534994889</v>
       </c>
       <c r="G185" t="n">
-        <v>1038.251119098672</v>
+        <v>1038.251119098671</v>
       </c>
       <c r="H185" t="n">
         <v>0</v>
@@ -6552,7 +6540,7 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="2" t="n">
+      <c r="A186" s="1" t="n">
         <v>45293</v>
       </c>
       <c r="B186" t="inlineStr">
@@ -6561,13 +6549,13 @@
         </is>
       </c>
       <c r="C186" t="n">
-        <v>6762.618151967888</v>
+        <v>6762.618151967887</v>
       </c>
       <c r="D186" t="n">
         <v>5</v>
       </c>
       <c r="E186" t="n">
-        <v>7434.527652032685</v>
+        <v>7434.527652032684</v>
       </c>
       <c r="F186" t="n">
         <v>-676.9095000647976</v>
@@ -6585,7 +6573,7 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="2" t="n">
+      <c r="A187" s="1" t="n">
         <v>45293</v>
       </c>
       <c r="B187" t="inlineStr">
@@ -6594,19 +6582,19 @@
         </is>
       </c>
       <c r="C187" t="n">
-        <v>8966.855853222398</v>
+        <v>8966.855853222387</v>
       </c>
       <c r="D187" t="n">
         <v>5</v>
       </c>
       <c r="E187" t="n">
-        <v>7434.527652032685</v>
+        <v>7434.527652032684</v>
       </c>
       <c r="F187" t="n">
-        <v>1527.328201189713</v>
+        <v>1527.328201189703</v>
       </c>
       <c r="G187" t="n">
-        <v>221.1088622924779</v>
+        <v>221.1088622924753</v>
       </c>
       <c r="H187" t="n">
         <v>0</v>
@@ -6618,7 +6606,7 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="2" t="n">
+      <c r="A188" s="1" t="n">
         <v>43467</v>
       </c>
       <c r="B188" t="inlineStr">
@@ -6651,7 +6639,7 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="2" t="n">
+      <c r="A189" s="1" t="n">
         <v>43467</v>
       </c>
       <c r="B189" t="inlineStr">
@@ -6684,7 +6672,7 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="2" t="n">
+      <c r="A190" s="1" t="n">
         <v>43467</v>
       </c>
       <c r="B190" t="inlineStr">
@@ -6717,7 +6705,7 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="2" t="n">
+      <c r="A191" s="1" t="n">
         <v>43467</v>
       </c>
       <c r="B191" t="inlineStr">
@@ -6750,7 +6738,7 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="2" t="n">
+      <c r="A192" s="1" t="n">
         <v>43467</v>
       </c>
       <c r="B192" t="inlineStr">
@@ -6783,7 +6771,7 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="2" t="n">
+      <c r="A193" s="1" t="n">
         <v>43467</v>
       </c>
       <c r="B193" t="inlineStr">
@@ -6816,7 +6804,7 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="2" t="n">
+      <c r="A194" s="1" t="n">
         <v>43467</v>
       </c>
       <c r="B194" t="inlineStr">
@@ -6849,7 +6837,7 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="2" t="n">
+      <c r="A195" s="1" t="n">
         <v>43467</v>
       </c>
       <c r="B195" t="inlineStr">
@@ -6882,7 +6870,7 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="2" t="n">
+      <c r="A196" s="1" t="n">
         <v>43467</v>
       </c>
       <c r="B196" t="inlineStr">
@@ -6915,7 +6903,7 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="2" t="n">
+      <c r="A197" s="1" t="n">
         <v>43832</v>
       </c>
       <c r="B197" t="inlineStr">
@@ -6948,7 +6936,7 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="2" t="n">
+      <c r="A198" s="1" t="n">
         <v>43832</v>
       </c>
       <c r="B198" t="inlineStr">
@@ -6981,7 +6969,7 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="2" t="n">
+      <c r="A199" s="1" t="n">
         <v>43832</v>
       </c>
       <c r="B199" t="inlineStr">
@@ -7014,7 +7002,7 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="2" t="n">
+      <c r="A200" s="1" t="n">
         <v>44200</v>
       </c>
       <c r="B200" t="inlineStr">
@@ -7047,7 +7035,7 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="2" t="n">
+      <c r="A201" s="1" t="n">
         <v>44200</v>
       </c>
       <c r="B201" t="inlineStr">
@@ -7056,22 +7044,22 @@
         </is>
       </c>
       <c r="C201" t="n">
-        <v>1978.851338746947</v>
+        <v>1978.851338746954</v>
       </c>
       <c r="D201" t="n">
         <v>5</v>
       </c>
       <c r="E201" t="n">
-        <v>1394.830166946518</v>
+        <v>1394.830166946521</v>
       </c>
       <c r="F201" t="n">
-        <v>579.0211718004298</v>
+        <v>579.0211718004327</v>
       </c>
       <c r="G201" t="n">
         <v>0</v>
       </c>
       <c r="H201" t="n">
-        <v>165.1407606785392</v>
+        <v>165.1407606785363</v>
       </c>
       <c r="I201" t="inlineStr">
         <is>
@@ -7080,7 +7068,7 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="2" t="n">
+      <c r="A202" s="1" t="n">
         <v>44200</v>
       </c>
       <c r="B202" t="inlineStr">
@@ -7089,7 +7077,7 @@
         </is>
       </c>
       <c r="C202" t="n">
-        <v>19288.86350380226</v>
+        <v>19288.86350380227</v>
       </c>
       <c r="D202" t="n">
         <v>5</v>
@@ -7098,13 +7086,13 @@
         <v>26556.96985444887</v>
       </c>
       <c r="F202" t="n">
-        <v>-7273.106350646609</v>
+        <v>-7273.106350646602</v>
       </c>
       <c r="G202" t="n">
         <v>0</v>
       </c>
       <c r="H202" t="n">
-        <v>7438.247111325149</v>
+        <v>7438.247111325138</v>
       </c>
       <c r="I202" t="inlineStr">
         <is>
@@ -7113,7 +7101,7 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="2" t="n">
+      <c r="A203" s="1" t="n">
         <v>44200</v>
       </c>
       <c r="B203" t="inlineStr">
@@ -7128,16 +7116,16 @@
         <v>5</v>
       </c>
       <c r="E203" t="n">
-        <v>2864.550235683181</v>
+        <v>2864.550235683182</v>
       </c>
       <c r="F203" t="n">
-        <v>154.7207572575053</v>
+        <v>154.7207572575044</v>
       </c>
       <c r="G203" t="n">
         <v>0</v>
       </c>
       <c r="H203" t="n">
-        <v>7283.526354067643</v>
+        <v>7283.526354067633</v>
       </c>
       <c r="I203" t="inlineStr">
         <is>
@@ -7146,7 +7134,7 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="2" t="n">
+      <c r="A204" s="1" t="n">
         <v>44200</v>
       </c>
       <c r="B204" t="inlineStr">
@@ -7170,7 +7158,7 @@
         <v>0</v>
       </c>
       <c r="H204" t="n">
-        <v>4289.157465101511</v>
+        <v>4289.157465101501</v>
       </c>
       <c r="I204" t="inlineStr">
         <is>
@@ -7179,7 +7167,7 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="2" t="n">
+      <c r="A205" s="1" t="n">
         <v>44200</v>
       </c>
       <c r="B205" t="inlineStr">
@@ -7197,13 +7185,13 @@
         <v>3647.281682584791</v>
       </c>
       <c r="F205" t="n">
-        <v>97.37905686919339</v>
+        <v>97.37905686919294</v>
       </c>
       <c r="G205" t="n">
         <v>0</v>
       </c>
       <c r="H205" t="n">
-        <v>4191.778408232318</v>
+        <v>4191.778408232308</v>
       </c>
       <c r="I205" t="inlineStr">
         <is>
@@ -7212,7 +7200,7 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="2" t="n">
+      <c r="A206" s="1" t="n">
         <v>44200</v>
       </c>
       <c r="B206" t="inlineStr">
@@ -7221,22 +7209,22 @@
         </is>
       </c>
       <c r="C206" t="n">
-        <v>2483.546838585092</v>
+        <v>2483.546838585081</v>
       </c>
       <c r="D206" t="n">
         <v>5</v>
       </c>
       <c r="E206" t="n">
-        <v>2403.392079421886</v>
+        <v>2403.392079421877</v>
       </c>
       <c r="F206" t="n">
-        <v>75.15475916320611</v>
+        <v>75.15475916320429</v>
       </c>
       <c r="G206" t="n">
         <v>0</v>
       </c>
       <c r="H206" t="n">
-        <v>4116.623649069112</v>
+        <v>4116.623649069104</v>
       </c>
       <c r="I206" t="inlineStr">
         <is>
@@ -7245,7 +7233,7 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="2" t="n">
+      <c r="A207" s="1" t="n">
         <v>44200</v>
       </c>
       <c r="B207" t="inlineStr">
@@ -7254,22 +7242,22 @@
         </is>
       </c>
       <c r="C207" t="n">
-        <v>4811.668062193704</v>
+        <v>4811.668062193692</v>
       </c>
       <c r="D207" t="n">
         <v>5</v>
       </c>
       <c r="E207" t="n">
-        <v>3843.562017170863</v>
+        <v>3843.56201717086</v>
       </c>
       <c r="F207" t="n">
-        <v>963.106045022841</v>
+        <v>963.1060450228319</v>
       </c>
       <c r="G207" t="n">
         <v>0</v>
       </c>
       <c r="H207" t="n">
-        <v>3153.517604046271</v>
+        <v>3153.517604046272</v>
       </c>
       <c r="I207" t="inlineStr">
         <is>
@@ -7278,7 +7266,7 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="2" t="n">
+      <c r="A208" s="1" t="n">
         <v>44200</v>
       </c>
       <c r="B208" t="inlineStr">
@@ -7293,16 +7281,16 @@
         <v>5</v>
       </c>
       <c r="E208" t="n">
-        <v>1783.633996685432</v>
+        <v>1783.63399668543</v>
       </c>
       <c r="F208" t="n">
-        <v>-202.9485797526559</v>
+        <v>-202.9485797526547</v>
       </c>
       <c r="G208" t="n">
         <v>0</v>
       </c>
       <c r="H208" t="n">
-        <v>3356.466183798927</v>
+        <v>3356.466183798926</v>
       </c>
       <c r="I208" t="inlineStr">
         <is>
@@ -7311,7 +7299,7 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="2" t="n">
+      <c r="A209" s="1" t="n">
         <v>44200</v>
       </c>
       <c r="B209" t="inlineStr">
@@ -7320,13 +7308,13 @@
         </is>
       </c>
       <c r="C209" t="n">
-        <v>1848.274759873234</v>
+        <v>1848.274759873235</v>
       </c>
       <c r="D209" t="n">
         <v>5</v>
       </c>
       <c r="E209" t="n">
-        <v>2126.645846364567</v>
+        <v>2126.645846364568</v>
       </c>
       <c r="F209" t="n">
         <v>-283.3710864913328</v>
@@ -7344,7 +7332,7 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="2" t="n">
+      <c r="A210" s="1" t="n">
         <v>44564</v>
       </c>
       <c r="B210" t="inlineStr">
@@ -7368,7 +7356,7 @@
         <v>0</v>
       </c>
       <c r="H210" t="n">
-        <v>3516.96313351706</v>
+        <v>3516.963133517059</v>
       </c>
       <c r="I210" t="inlineStr">
         <is>
@@ -7377,7 +7365,7 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="2" t="n">
+      <c r="A211" s="1" t="n">
         <v>44564</v>
       </c>
       <c r="B211" t="inlineStr">
@@ -7392,16 +7380,16 @@
         <v>5</v>
       </c>
       <c r="E211" t="n">
-        <v>385.93158491135</v>
+        <v>385.9315849113498</v>
       </c>
       <c r="F211" t="n">
-        <v>259.4323796360623</v>
+        <v>259.4323796360625</v>
       </c>
       <c r="G211" t="n">
         <v>0</v>
       </c>
       <c r="H211" t="n">
-        <v>3257.530753880998</v>
+        <v>3257.530753880997</v>
       </c>
       <c r="I211" t="inlineStr">
         <is>
@@ -7410,7 +7398,7 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="2" t="n">
+      <c r="A212" s="1" t="n">
         <v>44564</v>
       </c>
       <c r="B212" t="inlineStr">
@@ -7434,7 +7422,7 @@
         <v>0</v>
       </c>
       <c r="H212" t="n">
-        <v>2322.842114941843</v>
+        <v>2322.842114941842</v>
       </c>
       <c r="I212" t="inlineStr">
         <is>
@@ -7443,7 +7431,7 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="2" t="n">
+      <c r="A213" s="1" t="n">
         <v>44564</v>
       </c>
       <c r="B213" t="inlineStr">
@@ -7461,13 +7449,13 @@
         <v>1158.679657644755</v>
       </c>
       <c r="F213" t="n">
-        <v>526.79717912712</v>
+        <v>526.7971791271198</v>
       </c>
       <c r="G213" t="n">
         <v>0</v>
       </c>
       <c r="H213" t="n">
-        <v>1796.044935814723</v>
+        <v>1796.044935814722</v>
       </c>
       <c r="I213" t="inlineStr">
         <is>
@@ -7476,7 +7464,7 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="2" t="n">
+      <c r="A214" s="1" t="n">
         <v>44564</v>
       </c>
       <c r="B214" t="inlineStr">
@@ -7491,10 +7479,10 @@
         <v>5</v>
       </c>
       <c r="E214" t="n">
-        <v>714.5607784532798</v>
+        <v>714.5607784532801</v>
       </c>
       <c r="F214" t="n">
-        <v>176.7330325140389</v>
+        <v>176.7330325140385</v>
       </c>
       <c r="G214" t="n">
         <v>0</v>
@@ -7509,7 +7497,7 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="2" t="n">
+      <c r="A215" s="1" t="n">
         <v>44564</v>
       </c>
       <c r="B215" t="inlineStr">
@@ -7542,7 +7530,7 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="2" t="n">
+      <c r="A216" s="1" t="n">
         <v>44564</v>
       </c>
       <c r="B216" t="inlineStr">
@@ -7575,7 +7563,7 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="2" t="n">
+      <c r="A217" s="1" t="n">
         <v>44564</v>
       </c>
       <c r="B217" t="inlineStr">
@@ -7608,7 +7596,7 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="2" t="n">
+      <c r="A218" s="1" t="n">
         <v>44564</v>
       </c>
       <c r="B218" t="inlineStr">
@@ -7641,7 +7629,7 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="2" t="n">
+      <c r="A219" s="1" t="n">
         <v>44564</v>
       </c>
       <c r="B219" t="inlineStr">
@@ -7674,7 +7662,7 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="2" t="n">
+      <c r="A220" s="1" t="n">
         <v>44928</v>
       </c>
       <c r="B220" t="inlineStr">
@@ -7689,13 +7677,13 @@
         <v>5</v>
       </c>
       <c r="E220" t="n">
-        <v>3495.130385247215</v>
+        <v>3495.130385247213</v>
       </c>
       <c r="F220" t="n">
-        <v>2450.55817534453</v>
+        <v>2450.558175344532</v>
       </c>
       <c r="G220" t="n">
-        <v>549.1841674323256</v>
+        <v>549.1841674323261</v>
       </c>
       <c r="H220" t="n">
         <v>0</v>
@@ -7707,7 +7695,7 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="2" t="n">
+      <c r="A221" s="1" t="n">
         <v>44928</v>
       </c>
       <c r="B221" t="inlineStr">
@@ -7716,19 +7704,19 @@
         </is>
       </c>
       <c r="C221" t="n">
-        <v>3103.307772208133</v>
+        <v>3103.307772208129</v>
       </c>
       <c r="D221" t="n">
         <v>5</v>
       </c>
       <c r="E221" t="n">
-        <v>1661.451214553193</v>
+        <v>1661.451214553191</v>
       </c>
       <c r="F221" t="n">
-        <v>1436.85655765494</v>
+        <v>1436.856557654938</v>
       </c>
       <c r="G221" t="n">
-        <v>373.5827049902844</v>
+        <v>373.5827049902838</v>
       </c>
       <c r="H221" t="n">
         <v>0</v>
@@ -7740,7 +7728,7 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="2" t="n">
+      <c r="A222" s="1" t="n">
         <v>44928</v>
       </c>
       <c r="B222" t="inlineStr">
@@ -7773,7 +7761,7 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="2" t="n">
+      <c r="A223" s="1" t="n">
         <v>45293</v>
       </c>
       <c r="B223" t="inlineStr">
@@ -7788,13 +7776,13 @@
         <v>5</v>
       </c>
       <c r="E223" t="n">
-        <v>9258.340446593256</v>
+        <v>9258.340446593258</v>
       </c>
       <c r="F223" t="n">
         <v>17286.91147354405</v>
       </c>
       <c r="G223" t="n">
-        <v>4494.596983121453</v>
+        <v>4494.596983121452</v>
       </c>
       <c r="H223" t="n">
         <v>0</v>
@@ -7806,7 +7794,7 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="2" t="n">
+      <c r="A224" s="1" t="n">
         <v>45293</v>
       </c>
       <c r="B224" t="inlineStr">
@@ -7815,22 +7803,22 @@
         </is>
       </c>
       <c r="C224" t="n">
-        <v>34472.50360869655</v>
+        <v>34472.50360869653</v>
       </c>
       <c r="D224" t="n">
         <v>5</v>
       </c>
       <c r="E224" t="n">
-        <v>34873.06058570604</v>
+        <v>34873.06058570603</v>
       </c>
       <c r="F224" t="n">
-        <v>-405.556977009488</v>
+        <v>-405.5569770094953</v>
       </c>
       <c r="G224" t="n">
         <v>0</v>
       </c>
       <c r="H224" t="n">
-        <v>405.556977009488</v>
+        <v>405.5569770094953</v>
       </c>
       <c r="I224" t="inlineStr">
         <is>
@@ -7839,7 +7827,7 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="2" t="n">
+      <c r="A225" s="1" t="n">
         <v>45293</v>
       </c>
       <c r="B225" t="inlineStr">
@@ -7857,7 +7845,7 @@
         <v>19437.79102451042</v>
       </c>
       <c r="F225" t="n">
-        <v>8088.597307816493</v>
+        <v>8088.597307816497</v>
       </c>
       <c r="G225" t="n">
         <v>1997.590486009821</v>
@@ -7872,7 +7860,7 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="2" t="n">
+      <c r="A226" s="1" t="n">
         <v>45293</v>
       </c>
       <c r="B226" t="inlineStr">
@@ -7905,7 +7893,7 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="2" t="n">
+      <c r="A227" s="1" t="n">
         <v>45293</v>
       </c>
       <c r="B227" t="inlineStr">
@@ -7914,13 +7902,13 @@
         </is>
       </c>
       <c r="C227" t="n">
-        <v>5083.636647335371</v>
+        <v>5083.636647335374</v>
       </c>
       <c r="D227" t="n">
         <v>5</v>
       </c>
       <c r="E227" t="n">
-        <v>4217.069387810213</v>
+        <v>4217.069387810216</v>
       </c>
       <c r="F227" t="n">
         <v>861.5672595251581</v>
@@ -7938,7 +7926,7 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="2" t="n">
+      <c r="A228" s="1" t="n">
         <v>43467</v>
       </c>
       <c r="B228" t="inlineStr">
@@ -7947,13 +7935,13 @@
         </is>
       </c>
       <c r="C228" t="n">
-        <v>5035.358348532151</v>
+        <v>5035.358348532152</v>
       </c>
       <c r="D228" t="n">
         <v>5</v>
       </c>
       <c r="E228" t="n">
-        <v>4886.103834685249</v>
+        <v>4886.103834685251</v>
       </c>
       <c r="F228" t="n">
         <v>144.2545138469013</v>
@@ -7971,7 +7959,7 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="2" t="n">
+      <c r="A229" s="1" t="n">
         <v>43467</v>
       </c>
       <c r="B229" t="inlineStr">
@@ -7980,19 +7968,19 @@
         </is>
       </c>
       <c r="C229" t="n">
-        <v>5651.274588367256</v>
+        <v>5651.274588367258</v>
       </c>
       <c r="D229" t="n">
         <v>5</v>
       </c>
       <c r="E229" t="n">
-        <v>5268.180901221274</v>
+        <v>5268.180901221275</v>
       </c>
       <c r="F229" t="n">
-        <v>378.0936871459817</v>
+        <v>378.0936871459826</v>
       </c>
       <c r="G229" t="n">
-        <v>98.30435865795523</v>
+        <v>98.30435865795548</v>
       </c>
       <c r="H229" t="n">
         <v>0</v>
@@ -8004,7 +7992,7 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="2" t="n">
+      <c r="A230" s="1" t="n">
         <v>43467</v>
       </c>
       <c r="B230" t="inlineStr">
@@ -8037,7 +8025,7 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="2" t="n">
+      <c r="A231" s="1" t="n">
         <v>43467</v>
       </c>
       <c r="B231" t="inlineStr">
@@ -8052,7 +8040,7 @@
         <v>5</v>
       </c>
       <c r="E231" t="n">
-        <v>7318.414634146343</v>
+        <v>7318.414634146342</v>
       </c>
       <c r="F231" t="n">
         <v>-1805.993867185111</v>
@@ -8061,7 +8049,7 @@
         <v>0</v>
       </c>
       <c r="H231" t="n">
-        <v>4633.978405259907</v>
+        <v>4633.978405259906</v>
       </c>
       <c r="I231" t="inlineStr">
         <is>
@@ -8070,7 +8058,7 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="2" t="n">
+      <c r="A232" s="1" t="n">
         <v>43467</v>
       </c>
       <c r="B232" t="inlineStr">
@@ -8079,22 +8067,22 @@
         </is>
       </c>
       <c r="C232" t="n">
-        <v>961.3091676460554</v>
+        <v>961.3091676460544</v>
       </c>
       <c r="D232" t="n">
         <v>5</v>
       </c>
       <c r="E232" t="n">
-        <v>1175.759250839007</v>
+        <v>1175.759250839006</v>
       </c>
       <c r="F232" t="n">
-        <v>-219.4500831929513</v>
+        <v>-219.4500831929511</v>
       </c>
       <c r="G232" t="n">
         <v>0</v>
       </c>
       <c r="H232" t="n">
-        <v>4853.428488452859</v>
+        <v>4853.428488452857</v>
       </c>
       <c r="I232" t="inlineStr">
         <is>
@@ -8103,7 +8091,7 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="2" t="n">
+      <c r="A233" s="1" t="n">
         <v>43467</v>
       </c>
       <c r="B233" t="inlineStr">
@@ -8118,16 +8106,16 @@
         <v>5</v>
       </c>
       <c r="E233" t="n">
-        <v>4880.609756097539</v>
+        <v>4880.60975609754</v>
       </c>
       <c r="F233" t="n">
-        <v>-1306.149370104031</v>
+        <v>-1306.149370104032</v>
       </c>
       <c r="G233" t="n">
         <v>0</v>
       </c>
       <c r="H233" t="n">
-        <v>6159.57785855689</v>
+        <v>6159.577858556889</v>
       </c>
       <c r="I233" t="inlineStr">
         <is>
@@ -8136,7 +8124,7 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="2" t="n">
+      <c r="A234" s="1" t="n">
         <v>43832</v>
       </c>
       <c r="B234" t="inlineStr">
@@ -8151,16 +8139,16 @@
         <v>5</v>
       </c>
       <c r="E234" t="n">
-        <v>785.5902326873476</v>
+        <v>785.5902326873477</v>
       </c>
       <c r="F234" t="n">
-        <v>401.1607866517296</v>
+        <v>401.1607866517295</v>
       </c>
       <c r="G234" t="n">
         <v>0</v>
       </c>
       <c r="H234" t="n">
-        <v>5758.41707190516</v>
+        <v>5758.417071905159</v>
       </c>
       <c r="I234" t="inlineStr">
         <is>
@@ -8169,7 +8157,7 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="2" t="n">
+      <c r="A235" s="1" t="n">
         <v>43832</v>
       </c>
       <c r="B235" t="inlineStr">
@@ -8178,13 +8166,13 @@
         </is>
       </c>
       <c r="C235" t="n">
-        <v>3923.817127338938</v>
+        <v>3923.817127338936</v>
       </c>
       <c r="D235" t="n">
         <v>5</v>
       </c>
       <c r="E235" t="n">
-        <v>2923.109726390217</v>
+        <v>2923.109726390216</v>
       </c>
       <c r="F235" t="n">
         <v>995.7074009487205</v>
@@ -8193,7 +8181,7 @@
         <v>0</v>
       </c>
       <c r="H235" t="n">
-        <v>4762.709670956439</v>
+        <v>4762.709670956438</v>
       </c>
       <c r="I235" t="inlineStr">
         <is>
@@ -8202,7 +8190,7 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="2" t="n">
+      <c r="A236" s="1" t="n">
         <v>43832</v>
       </c>
       <c r="B236" t="inlineStr">
@@ -8211,22 +8199,22 @@
         </is>
       </c>
       <c r="C236" t="n">
-        <v>7595.969771589893</v>
+        <v>7595.969771589892</v>
       </c>
       <c r="D236" t="n">
         <v>5</v>
       </c>
       <c r="E236" t="n">
-        <v>6924.762514837353</v>
+        <v>6924.76251483735</v>
       </c>
       <c r="F236" t="n">
-        <v>666.2072567525402</v>
+        <v>666.207256752542</v>
       </c>
       <c r="G236" t="n">
         <v>0</v>
       </c>
       <c r="H236" t="n">
-        <v>4096.502414203899</v>
+        <v>4096.502414203896</v>
       </c>
       <c r="I236" t="inlineStr">
         <is>
@@ -8235,7 +8223,7 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="2" t="n">
+      <c r="A237" s="1" t="n">
         <v>43832</v>
       </c>
       <c r="B237" t="inlineStr">
@@ -8250,16 +8238,16 @@
         <v>5</v>
       </c>
       <c r="E237" t="n">
-        <v>7535.638855418797</v>
+        <v>7535.638855418796</v>
       </c>
       <c r="F237" t="n">
-        <v>693.0262168014551</v>
+        <v>693.026216801456</v>
       </c>
       <c r="G237" t="n">
         <v>0</v>
       </c>
       <c r="H237" t="n">
-        <v>3403.476197402444</v>
+        <v>3403.47619740244</v>
       </c>
       <c r="I237" t="inlineStr">
         <is>
@@ -8268,7 +8256,7 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="2" t="n">
+      <c r="A238" s="1" t="n">
         <v>43832</v>
       </c>
       <c r="B238" t="inlineStr">
@@ -8277,16 +8265,16 @@
         </is>
       </c>
       <c r="C238" t="n">
-        <v>6926.715559435535</v>
+        <v>6926.715559435533</v>
       </c>
       <c r="D238" t="n">
         <v>5</v>
       </c>
       <c r="E238" t="n">
-        <v>6142.655383307336</v>
+        <v>6142.655383307337</v>
       </c>
       <c r="F238" t="n">
-        <v>779.0601761281996</v>
+        <v>779.060176128196</v>
       </c>
       <c r="G238" t="n">
         <v>0</v>
@@ -8301,7 +8289,7 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="2" t="n">
+      <c r="A239" s="1" t="n">
         <v>44200</v>
       </c>
       <c r="B239" t="inlineStr">
@@ -8310,7 +8298,7 @@
         </is>
       </c>
       <c r="C239" t="n">
-        <v>6209.974662173348</v>
+        <v>6209.97466217335</v>
       </c>
       <c r="D239" t="n">
         <v>5</v>
@@ -8319,13 +8307,13 @@
         <v>7386.078694117654</v>
       </c>
       <c r="F239" t="n">
-        <v>-1181.104031944305</v>
+        <v>-1181.104031944304</v>
       </c>
       <c r="G239" t="n">
         <v>0</v>
       </c>
       <c r="H239" t="n">
-        <v>3805.52005321855</v>
+        <v>3805.520053218548</v>
       </c>
       <c r="I239" t="inlineStr">
         <is>
@@ -8334,7 +8322,7 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="2" t="n">
+      <c r="A240" s="1" t="n">
         <v>44200</v>
       </c>
       <c r="B240" t="inlineStr">
@@ -8343,19 +8331,19 @@
         </is>
       </c>
       <c r="C240" t="n">
-        <v>8518.293181146893</v>
+        <v>8518.293181146892</v>
       </c>
       <c r="D240" t="n">
         <v>5</v>
       </c>
       <c r="E240" t="n">
-        <v>4606.709528065735</v>
+        <v>4606.709528065734</v>
       </c>
       <c r="F240" t="n">
         <v>3906.583653081158</v>
       </c>
       <c r="G240" t="n">
-        <v>26.27653596427821</v>
+        <v>26.27653596427845</v>
       </c>
       <c r="H240" t="n">
         <v>0</v>
@@ -8367,7 +8355,7 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="2" t="n">
+      <c r="A241" s="1" t="n">
         <v>44200</v>
       </c>
       <c r="B241" t="inlineStr">
@@ -8382,13 +8370,13 @@
         <v>5</v>
       </c>
       <c r="E241" t="n">
-        <v>5121.19445250555</v>
+        <v>5121.194452505547</v>
       </c>
       <c r="F241" t="n">
-        <v>5095.881191553684</v>
+        <v>5095.881191553682</v>
       </c>
       <c r="G241" t="n">
-        <v>1324.929109803958</v>
+        <v>1324.929109803957</v>
       </c>
       <c r="H241" t="n">
         <v>0</v>
@@ -8400,7 +8388,7 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="2" t="n">
+      <c r="A242" s="1" t="n">
         <v>44200</v>
       </c>
       <c r="B242" t="inlineStr">
@@ -8415,16 +8403,16 @@
         <v>5</v>
       </c>
       <c r="E242" t="n">
-        <v>5619.110533834323</v>
+        <v>5619.110533834324</v>
       </c>
       <c r="F242" t="n">
-        <v>-487.6497004993871</v>
+        <v>-487.649700499388</v>
       </c>
       <c r="G242" t="n">
         <v>0</v>
       </c>
       <c r="H242" t="n">
-        <v>487.6497004993871</v>
+        <v>487.649700499388</v>
       </c>
       <c r="I242" t="inlineStr">
         <is>
@@ -8433,7 +8421,7 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="2" t="n">
+      <c r="A243" s="1" t="n">
         <v>44200</v>
       </c>
       <c r="B243" t="inlineStr">
@@ -8448,13 +8436,13 @@
         <v>5</v>
       </c>
       <c r="E243" t="n">
-        <v>7409.043102068892</v>
+        <v>7409.04310206889</v>
       </c>
       <c r="F243" t="n">
-        <v>3416.245682523408</v>
+        <v>3416.245682523409</v>
       </c>
       <c r="G243" t="n">
-        <v>761.4349553262454</v>
+        <v>761.4349553262456</v>
       </c>
       <c r="H243" t="n">
         <v>0</v>
@@ -8466,7 +8454,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="2" t="n">
+      <c r="A244" s="1" t="n">
         <v>44200</v>
       </c>
       <c r="B244" t="inlineStr">
@@ -8481,13 +8469,13 @@
         <v>5</v>
       </c>
       <c r="E244" t="n">
-        <v>5758.76183656345</v>
+        <v>5758.761836563449</v>
       </c>
       <c r="F244" t="n">
-        <v>4.971775885588613</v>
+        <v>4.971775885589523</v>
       </c>
       <c r="G244" t="n">
-        <v>1.292661730253039</v>
+        <v>1.292661730253276</v>
       </c>
       <c r="H244" t="n">
         <v>0</v>
@@ -8499,7 +8487,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="2" t="n">
+      <c r="A245" s="1" t="n">
         <v>44200</v>
       </c>
       <c r="B245" t="inlineStr">
@@ -8532,7 +8520,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="2" t="n">
+      <c r="A246" s="1" t="n">
         <v>44564</v>
       </c>
       <c r="B246" t="inlineStr">
@@ -8547,16 +8535,16 @@
         <v>5</v>
       </c>
       <c r="E246" t="n">
-        <v>1866.949036530928</v>
+        <v>1866.949036530927</v>
       </c>
       <c r="F246" t="n">
-        <v>582.2321906725183</v>
+        <v>582.2321906725188</v>
       </c>
       <c r="G246" t="n">
         <v>0</v>
       </c>
       <c r="H246" t="n">
-        <v>568.1235925054216</v>
+        <v>568.1235925054211</v>
       </c>
       <c r="I246" t="inlineStr">
         <is>
@@ -8565,7 +8553,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="2" t="n">
+      <c r="A247" s="1" t="n">
         <v>44564</v>
       </c>
       <c r="B247" t="inlineStr">
@@ -8574,19 +8562,19 @@
         </is>
       </c>
       <c r="C247" t="n">
-        <v>19023.45171007855</v>
+        <v>19023.45171007853</v>
       </c>
       <c r="D247" t="n">
         <v>5</v>
       </c>
       <c r="E247" t="n">
-        <v>7864.161390521496</v>
+        <v>7864.161390521495</v>
       </c>
       <c r="F247" t="n">
-        <v>11154.29031955705</v>
+        <v>11154.29031955703</v>
       </c>
       <c r="G247" t="n">
-        <v>2752.403349033423</v>
+        <v>2752.403349033419</v>
       </c>
       <c r="H247" t="n">
         <v>0</v>
@@ -8598,7 +8586,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="2" t="n">
+      <c r="A248" s="1" t="n">
         <v>44564</v>
       </c>
       <c r="B248" t="inlineStr">
@@ -8607,19 +8595,19 @@
         </is>
       </c>
       <c r="C248" t="n">
-        <v>8373.876831014753</v>
+        <v>8373.87683101475</v>
       </c>
       <c r="D248" t="n">
         <v>5</v>
       </c>
       <c r="E248" t="n">
-        <v>6091.255026328552</v>
+        <v>6091.255026328549</v>
       </c>
       <c r="F248" t="n">
-        <v>2277.621804686201</v>
+        <v>2277.6218046862</v>
       </c>
       <c r="G248" t="n">
-        <v>592.1816692184124</v>
+        <v>592.1816692184121</v>
       </c>
       <c r="H248" t="n">
         <v>0</v>
@@ -8631,7 +8619,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="2" t="n">
+      <c r="A249" s="1" t="n">
         <v>44564</v>
       </c>
       <c r="B249" t="inlineStr">
@@ -8664,7 +8652,7 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="2" t="n">
+      <c r="A250" s="1" t="n">
         <v>44564</v>
       </c>
       <c r="B250" t="inlineStr">
@@ -8697,7 +8685,7 @@
       </c>
     </row>
     <row r="251">
-      <c r="A251" s="2" t="n">
+      <c r="A251" s="1" t="n">
         <v>44928</v>
       </c>
       <c r="B251" t="inlineStr">
@@ -8706,19 +8694,19 @@
         </is>
       </c>
       <c r="C251" t="n">
-        <v>1909.879810256982</v>
+        <v>1909.879810256985</v>
       </c>
       <c r="D251" t="n">
         <v>5</v>
       </c>
       <c r="E251" t="n">
-        <v>1844.121212260693</v>
+        <v>1844.121212260695</v>
       </c>
       <c r="F251" t="n">
-        <v>60.75859799628915</v>
+        <v>60.75859799629029</v>
       </c>
       <c r="G251" t="n">
-        <v>15.79723547903518</v>
+        <v>15.79723547903548</v>
       </c>
       <c r="H251" t="n">
         <v>0</v>
@@ -8730,7 +8718,7 @@
       </c>
     </row>
     <row r="252">
-      <c r="A252" s="2" t="n">
+      <c r="A252" s="1" t="n">
         <v>44928</v>
       </c>
       <c r="B252" t="inlineStr">
@@ -8763,7 +8751,7 @@
       </c>
     </row>
     <row r="253">
-      <c r="A253" s="2" t="n">
+      <c r="A253" s="1" t="n">
         <v>44928</v>
       </c>
       <c r="B253" t="inlineStr">
@@ -8772,7 +8760,7 @@
         </is>
       </c>
       <c r="C253" t="n">
-        <v>17339.35464027094</v>
+        <v>17339.35464027095</v>
       </c>
       <c r="D253" t="n">
         <v>5</v>
@@ -8796,7 +8784,7 @@
       </c>
     </row>
     <row r="254">
-      <c r="A254" s="2" t="n">
+      <c r="A254" s="1" t="n">
         <v>44928</v>
       </c>
       <c r="B254" t="inlineStr">
@@ -8811,13 +8799,13 @@
         <v>5</v>
       </c>
       <c r="E254" t="n">
-        <v>9960.329021468102</v>
+        <v>9960.3290214681</v>
       </c>
       <c r="F254" t="n">
-        <v>5356.589195732331</v>
+        <v>5356.589195732333</v>
       </c>
       <c r="G254" t="n">
-        <v>1392.713190890406</v>
+        <v>1392.713190890407</v>
       </c>
       <c r="H254" t="n">
         <v>0</v>
@@ -8829,7 +8817,7 @@
       </c>
     </row>
     <row r="255">
-      <c r="A255" s="2" t="n">
+      <c r="A255" s="1" t="n">
         <v>44928</v>
       </c>
       <c r="B255" t="inlineStr">
@@ -8847,13 +8835,13 @@
         <v>10861.21154250264</v>
       </c>
       <c r="F255" t="n">
-        <v>-3214.093870833094</v>
+        <v>-3214.093870833092</v>
       </c>
       <c r="G255" t="n">
         <v>0</v>
       </c>
       <c r="H255" t="n">
-        <v>3214.093870833094</v>
+        <v>3214.093870833092</v>
       </c>
       <c r="I255" t="inlineStr">
         <is>
@@ -8862,7 +8850,7 @@
       </c>
     </row>
     <row r="256">
-      <c r="A256" s="2" t="n">
+      <c r="A256" s="1" t="n">
         <v>44928</v>
       </c>
       <c r="B256" t="inlineStr">
@@ -8877,16 +8865,16 @@
         <v>5</v>
       </c>
       <c r="E256" t="n">
-        <v>7242.474361668428</v>
+        <v>7242.474361668426</v>
       </c>
       <c r="F256" t="n">
-        <v>-1718.090145380004</v>
+        <v>-1718.090145380002</v>
       </c>
       <c r="G256" t="n">
         <v>0</v>
       </c>
       <c r="H256" t="n">
-        <v>4932.184016213098</v>
+        <v>4932.184016213095</v>
       </c>
       <c r="I256" t="inlineStr">
         <is>
@@ -8895,7 +8883,7 @@
       </c>
     </row>
     <row r="257">
-      <c r="A257" s="2" t="n">
+      <c r="A257" s="1" t="n">
         <v>44928</v>
       </c>
       <c r="B257" t="inlineStr">
@@ -8910,16 +8898,16 @@
         <v>5</v>
       </c>
       <c r="E257" t="n">
-        <v>7242.474361668428</v>
+        <v>7242.474361668426</v>
       </c>
       <c r="F257" t="n">
-        <v>-761.7390576690941</v>
+        <v>-761.7390576690923</v>
       </c>
       <c r="G257" t="n">
         <v>0</v>
       </c>
       <c r="H257" t="n">
-        <v>5693.923073882193</v>
+        <v>5693.923073882187</v>
       </c>
       <c r="I257" t="inlineStr">
         <is>
@@ -8928,7 +8916,7 @@
       </c>
     </row>
     <row r="258">
-      <c r="A258" s="2" t="n">
+      <c r="A258" s="1" t="n">
         <v>45293</v>
       </c>
       <c r="B258" t="inlineStr">
@@ -8937,22 +8925,22 @@
         </is>
       </c>
       <c r="C258" t="n">
-        <v>2640.117017583721</v>
+        <v>2640.117017583729</v>
       </c>
       <c r="D258" t="n">
         <v>5</v>
       </c>
       <c r="E258" t="n">
-        <v>1826.952532770595</v>
+        <v>1826.952532770598</v>
       </c>
       <c r="F258" t="n">
-        <v>808.1644848131266</v>
+        <v>808.1644848131305</v>
       </c>
       <c r="G258" t="n">
         <v>0</v>
       </c>
       <c r="H258" t="n">
-        <v>4885.758589069066</v>
+        <v>4885.758589069057</v>
       </c>
       <c r="I258" t="inlineStr">
         <is>
@@ -8961,7 +8949,7 @@
       </c>
     </row>
     <row r="259">
-      <c r="A259" s="2" t="n">
+      <c r="A259" s="1" t="n">
         <v>45293</v>
       </c>
       <c r="B259" t="inlineStr">
@@ -8976,13 +8964,13 @@
         <v>5</v>
       </c>
       <c r="E259" t="n">
-        <v>9627.521683036895</v>
+        <v>9627.521683036894</v>
       </c>
       <c r="F259" t="n">
-        <v>6619.428960980971</v>
+        <v>6619.428960980973</v>
       </c>
       <c r="G259" t="n">
-        <v>450.7542966970953</v>
+        <v>450.7542966970981</v>
       </c>
       <c r="H259" t="n">
         <v>0</v>
@@ -8994,7 +8982,7 @@
       </c>
     </row>
     <row r="260">
-      <c r="A260" s="2" t="n">
+      <c r="A260" s="1" t="n">
         <v>45293</v>
       </c>
       <c r="B260" t="inlineStr">
@@ -9003,19 +8991,19 @@
         </is>
       </c>
       <c r="C260" t="n">
-        <v>18702.50761765054</v>
+        <v>18702.50761765053</v>
       </c>
       <c r="D260" t="n">
         <v>5</v>
       </c>
       <c r="E260" t="n">
-        <v>10550.01628192055</v>
+        <v>10550.01628192056</v>
       </c>
       <c r="F260" t="n">
-        <v>8147.491335729981</v>
+        <v>8147.49133572997</v>
       </c>
       <c r="G260" t="n">
-        <v>2118.347747289795</v>
+        <v>2118.347747289792</v>
       </c>
       <c r="H260" t="n">
         <v>0</v>
@@ -9027,7 +9015,7 @@
       </c>
     </row>
     <row r="261">
-      <c r="A261" s="2" t="n">
+      <c r="A261" s="1" t="n">
         <v>45293</v>
       </c>
       <c r="B261" t="inlineStr">
@@ -9042,13 +9030,13 @@
         <v>5</v>
       </c>
       <c r="E261" t="n">
-        <v>9250.254463952708</v>
+        <v>9250.254463952706</v>
       </c>
       <c r="F261" t="n">
-        <v>6050.222601501062</v>
+        <v>6050.222601501064</v>
       </c>
       <c r="G261" t="n">
-        <v>1573.057876390276</v>
+        <v>1573.057876390277</v>
       </c>
       <c r="H261" t="n">
         <v>0</v>
@@ -9060,7 +9048,7 @@
       </c>
     </row>
     <row r="262">
-      <c r="A262" s="2" t="n">
+      <c r="A262" s="1" t="n">
         <v>45293</v>
       </c>
       <c r="B262" t="inlineStr">
@@ -9069,19 +9057,19 @@
         </is>
       </c>
       <c r="C262" t="n">
-        <v>874.8796951242475</v>
+        <v>874.8796951242512</v>
       </c>
       <c r="D262" t="n">
         <v>5</v>
       </c>
       <c r="E262" t="n">
-        <v>782.8220758727002</v>
+        <v>782.8220758727034</v>
       </c>
       <c r="F262" t="n">
-        <v>87.05761925154729</v>
+        <v>87.05761925154775</v>
       </c>
       <c r="G262" t="n">
-        <v>22.6349810054023</v>
+        <v>22.63498100540242</v>
       </c>
       <c r="H262" t="n">
         <v>0</v>
@@ -9093,7 +9081,7 @@
       </c>
     </row>
     <row r="263">
-      <c r="A263" s="2" t="n">
+      <c r="A263" s="1" t="n">
         <v>45293</v>
       </c>
       <c r="B263" t="inlineStr">
@@ -9111,10 +9099,10 @@
         <v>11232.44743865074</v>
       </c>
       <c r="F263" t="n">
-        <v>6000.250837377329</v>
+        <v>6000.250837377331</v>
       </c>
       <c r="G263" t="n">
-        <v>1560.065217718105</v>
+        <v>1560.065217718106</v>
       </c>
       <c r="H263" t="n">
         <v>0</v>
@@ -9126,7 +9114,7 @@
       </c>
     </row>
     <row r="264">
-      <c r="A264" s="2" t="n">
+      <c r="A264" s="1" t="n">
         <v>45293</v>
       </c>
       <c r="B264" t="inlineStr">
@@ -9144,10 +9132,10 @@
         <v>11232.44743865074</v>
       </c>
       <c r="F264" t="n">
-        <v>2296.34635192415</v>
+        <v>2296.346351924152</v>
       </c>
       <c r="G264" t="n">
-        <v>597.0500515002791</v>
+        <v>597.0500515002796</v>
       </c>
       <c r="H264" t="n">
         <v>0</v>
@@ -9159,7 +9147,7 @@
       </c>
     </row>
     <row r="265">
-      <c r="A265" s="2" t="n">
+      <c r="A265" s="1" t="n">
         <v>43467</v>
       </c>
       <c r="B265" t="inlineStr">
@@ -9168,22 +9156,22 @@
         </is>
       </c>
       <c r="C265" t="n">
-        <v>2430.299700246789</v>
+        <v>2430.299700246793</v>
       </c>
       <c r="D265" t="n">
         <v>5</v>
       </c>
       <c r="E265" t="n">
-        <v>3234.906254042525</v>
+        <v>3234.90625404253</v>
       </c>
       <c r="F265" t="n">
-        <v>-809.6065537957356</v>
+        <v>-809.606553795737</v>
       </c>
       <c r="G265" t="n">
         <v>0</v>
       </c>
       <c r="H265" t="n">
-        <v>809.6065537957356</v>
+        <v>809.606553795737</v>
       </c>
       <c r="I265" t="inlineStr">
         <is>
@@ -9192,7 +9180,7 @@
       </c>
     </row>
     <row r="266">
-      <c r="A266" s="2" t="n">
+      <c r="A266" s="1" t="n">
         <v>43467</v>
       </c>
       <c r="B266" t="inlineStr">
@@ -9201,22 +9189,22 @@
         </is>
       </c>
       <c r="C266" t="n">
-        <v>3702.023574057635</v>
+        <v>3702.023574057639</v>
       </c>
       <c r="D266" t="n">
         <v>5</v>
       </c>
       <c r="E266" t="n">
-        <v>3591.880838662818</v>
+        <v>3591.880838662821</v>
       </c>
       <c r="F266" t="n">
-        <v>105.142735394817</v>
+        <v>105.1427353948179</v>
       </c>
       <c r="G266" t="n">
         <v>0</v>
       </c>
       <c r="H266" t="n">
-        <v>704.4638184009186</v>
+        <v>704.4638184009191</v>
       </c>
       <c r="I266" t="inlineStr">
         <is>
@@ -9225,7 +9213,7 @@
       </c>
     </row>
     <row r="267">
-      <c r="A267" s="2" t="n">
+      <c r="A267" s="1" t="n">
         <v>43467</v>
       </c>
       <c r="B267" t="inlineStr">
@@ -9234,13 +9222,13 @@
         </is>
       </c>
       <c r="C267" t="n">
-        <v>631.2654850995477</v>
+        <v>631.2654850995486</v>
       </c>
       <c r="D267" t="n">
         <v>5</v>
       </c>
       <c r="E267" t="n">
-        <v>588.8370892367515</v>
+        <v>588.8370892367524</v>
       </c>
       <c r="F267" t="n">
         <v>37.42839586279626</v>
@@ -9249,7 +9237,7 @@
         <v>0</v>
       </c>
       <c r="H267" t="n">
-        <v>667.0354225381224</v>
+        <v>667.0354225381228</v>
       </c>
       <c r="I267" t="inlineStr">
         <is>
@@ -9258,7 +9246,7 @@
       </c>
     </row>
     <row r="268">
-      <c r="A268" s="2" t="n">
+      <c r="A268" s="1" t="n">
         <v>43467</v>
       </c>
       <c r="B268" t="inlineStr">
@@ -9282,7 +9270,7 @@
         <v>0</v>
       </c>
       <c r="H268" t="n">
-        <v>980.5967746648272</v>
+        <v>980.5967746648276</v>
       </c>
       <c r="I268" t="inlineStr">
         <is>
@@ -9291,7 +9279,7 @@
       </c>
     </row>
     <row r="269">
-      <c r="A269" s="2" t="n">
+      <c r="A269" s="1" t="n">
         <v>43467</v>
       </c>
       <c r="B269" t="inlineStr">
@@ -9300,13 +9288,13 @@
         </is>
       </c>
       <c r="C269" t="n">
-        <v>3990.995001000218</v>
+        <v>3990.995001000221</v>
       </c>
       <c r="D269" t="n">
         <v>5</v>
       </c>
       <c r="E269" t="n">
-        <v>3810.200132106802</v>
+        <v>3810.200132106806</v>
       </c>
       <c r="F269" t="n">
         <v>175.7948688934152</v>
@@ -9315,7 +9303,7 @@
         <v>0</v>
       </c>
       <c r="H269" t="n">
-        <v>804.801905771412</v>
+        <v>804.8019057714124</v>
       </c>
       <c r="I269" t="inlineStr">
         <is>
@@ -9324,7 +9312,7 @@
       </c>
     </row>
     <row r="270">
-      <c r="A270" s="2" t="n">
+      <c r="A270" s="1" t="n">
         <v>43467</v>
       </c>
       <c r="B270" t="inlineStr">
@@ -9357,7 +9345,7 @@
       </c>
     </row>
     <row r="271">
-      <c r="A271" s="2" t="n">
+      <c r="A271" s="1" t="n">
         <v>43467</v>
       </c>
       <c r="B271" t="inlineStr">
@@ -9366,22 +9354,22 @@
         </is>
       </c>
       <c r="C271" t="n">
-        <v>180.451755114012</v>
+        <v>180.4517551140123</v>
       </c>
       <c r="D271" t="n">
         <v>5</v>
       </c>
       <c r="E271" t="n">
-        <v>181.2033969102927</v>
+        <v>181.2033969102929</v>
       </c>
       <c r="F271" t="n">
-        <v>-5.751641796280694</v>
+        <v>-5.751641796280666</v>
       </c>
       <c r="G271" t="n">
         <v>0</v>
       </c>
       <c r="H271" t="n">
-        <v>1511.019479626195</v>
+        <v>1511.019479626196</v>
       </c>
       <c r="I271" t="inlineStr">
         <is>
@@ -9390,7 +9378,7 @@
       </c>
     </row>
     <row r="272">
-      <c r="A272" s="2" t="n">
+      <c r="A272" s="1" t="n">
         <v>43467</v>
       </c>
       <c r="B272" t="inlineStr">
@@ -9414,7 +9402,7 @@
         <v>0</v>
       </c>
       <c r="H272" t="n">
-        <v>1533.410625534009</v>
+        <v>1533.41062553401</v>
       </c>
       <c r="I272" t="inlineStr">
         <is>
@@ -9423,7 +9411,7 @@
       </c>
     </row>
     <row r="273">
-      <c r="A273" s="2" t="n">
+      <c r="A273" s="1" t="n">
         <v>43467</v>
       </c>
       <c r="B273" t="inlineStr">
@@ -9432,13 +9420,13 @@
         </is>
       </c>
       <c r="C273" t="n">
-        <v>1199.049708608283</v>
+        <v>1199.049708608285</v>
       </c>
       <c r="D273" t="n">
         <v>5</v>
       </c>
       <c r="E273" t="n">
-        <v>1200.429470749345</v>
+        <v>1200.429470749347</v>
       </c>
       <c r="F273" t="n">
         <v>-6.379762141061747</v>
@@ -9447,7 +9435,7 @@
         <v>0</v>
       </c>
       <c r="H273" t="n">
-        <v>1539.790387675071</v>
+        <v>1539.790387675072</v>
       </c>
       <c r="I273" t="inlineStr">
         <is>
@@ -9456,7 +9444,7 @@
       </c>
     </row>
     <row r="274">
-      <c r="A274" s="2" t="n">
+      <c r="A274" s="1" t="n">
         <v>43832</v>
       </c>
       <c r="B274" t="inlineStr">
@@ -9465,22 +9453,22 @@
         </is>
       </c>
       <c r="C274" t="n">
-        <v>1853.465033166576</v>
+        <v>1853.46503316658</v>
       </c>
       <c r="D274" t="n">
         <v>5</v>
       </c>
       <c r="E274" t="n">
-        <v>1853.188871886528</v>
+        <v>1853.188871886532</v>
       </c>
       <c r="F274" t="n">
-        <v>-4.723838719952028</v>
+        <v>-4.723838719952255</v>
       </c>
       <c r="G274" t="n">
         <v>0</v>
       </c>
       <c r="H274" t="n">
-        <v>1544.514226395023</v>
+        <v>1544.514226395024</v>
       </c>
       <c r="I274" t="inlineStr">
         <is>
@@ -9489,7 +9477,7 @@
       </c>
     </row>
     <row r="275">
-      <c r="A275" s="2" t="n">
+      <c r="A275" s="1" t="n">
         <v>43832</v>
       </c>
       <c r="B275" t="inlineStr">
@@ -9498,22 +9486,22 @@
         </is>
       </c>
       <c r="C275" t="n">
-        <v>2261.334568685808</v>
+        <v>2261.334568685779</v>
       </c>
       <c r="D275" t="n">
         <v>5</v>
       </c>
       <c r="E275" t="n">
-        <v>1490.478777517898</v>
+        <v>1490.478777517881</v>
       </c>
       <c r="F275" t="n">
-        <v>765.85579116791</v>
+        <v>765.8557911678981</v>
       </c>
       <c r="G275" t="n">
         <v>0</v>
       </c>
       <c r="H275" t="n">
-        <v>778.6584352271132</v>
+        <v>778.6584352271257</v>
       </c>
       <c r="I275" t="inlineStr">
         <is>
@@ -9522,7 +9510,7 @@
       </c>
     </row>
     <row r="276">
-      <c r="A276" s="2" t="n">
+      <c r="A276" s="1" t="n">
         <v>43832</v>
       </c>
       <c r="B276" t="inlineStr">
@@ -9531,22 +9519,22 @@
         </is>
       </c>
       <c r="C276" t="n">
-        <v>556.5448426003304</v>
+        <v>556.5448426003331</v>
       </c>
       <c r="D276" t="n">
         <v>5</v>
       </c>
       <c r="E276" t="n">
-        <v>414.8636316259824</v>
+        <v>414.8636316259843</v>
       </c>
       <c r="F276" t="n">
-        <v>136.6812109743481</v>
+        <v>136.6812109743488</v>
       </c>
       <c r="G276" t="n">
         <v>0</v>
       </c>
       <c r="H276" t="n">
-        <v>641.9772242527652</v>
+        <v>641.9772242527769</v>
       </c>
       <c r="I276" t="inlineStr">
         <is>
@@ -9555,7 +9543,7 @@
       </c>
     </row>
     <row r="277">
-      <c r="A277" s="2" t="n">
+      <c r="A277" s="1" t="n">
         <v>43832</v>
       </c>
       <c r="B277" t="inlineStr">
@@ -9564,22 +9552,22 @@
         </is>
       </c>
       <c r="C277" t="n">
-        <v>1632.780340782254</v>
+        <v>1632.780340782261</v>
       </c>
       <c r="D277" t="n">
         <v>5</v>
       </c>
       <c r="E277" t="n">
-        <v>1460.562723624689</v>
+        <v>1460.562723624696</v>
       </c>
       <c r="F277" t="n">
-        <v>167.2176171575645</v>
+        <v>167.2176171575654</v>
       </c>
       <c r="G277" t="n">
         <v>0</v>
       </c>
       <c r="H277" t="n">
-        <v>474.7596070952006</v>
+        <v>474.7596070952114</v>
       </c>
       <c r="I277" t="inlineStr">
         <is>
@@ -9588,7 +9576,7 @@
       </c>
     </row>
     <row r="278">
-      <c r="A278" s="2" t="n">
+      <c r="A278" s="1" t="n">
         <v>43832</v>
       </c>
       <c r="B278" t="inlineStr">
@@ -9603,16 +9591,16 @@
         <v>5</v>
       </c>
       <c r="E278" t="n">
-        <v>1364.417075438771</v>
+        <v>1364.41707543877</v>
       </c>
       <c r="F278" t="n">
-        <v>118.4993672632579</v>
+        <v>118.4993672632581</v>
       </c>
       <c r="G278" t="n">
         <v>0</v>
       </c>
       <c r="H278" t="n">
-        <v>356.2602398319427</v>
+        <v>356.2602398319533</v>
       </c>
       <c r="I278" t="inlineStr">
         <is>
@@ -9621,7 +9609,7 @@
       </c>
     </row>
     <row r="279">
-      <c r="A279" s="2" t="n">
+      <c r="A279" s="1" t="n">
         <v>43832</v>
       </c>
       <c r="B279" t="inlineStr">
@@ -9645,7 +9633,7 @@
         <v>0</v>
       </c>
       <c r="H279" t="n">
-        <v>283.8041835274291</v>
+        <v>283.8041835274397</v>
       </c>
       <c r="I279" t="inlineStr">
         <is>
@@ -9654,7 +9642,7 @@
       </c>
     </row>
     <row r="280">
-      <c r="A280" s="2" t="n">
+      <c r="A280" s="1" t="n">
         <v>43832</v>
       </c>
       <c r="B280" t="inlineStr">
@@ -9663,22 +9651,22 @@
         </is>
       </c>
       <c r="C280" t="n">
-        <v>851.2518258599666</v>
+        <v>851.2518258599903</v>
       </c>
       <c r="D280" t="n">
         <v>5</v>
       </c>
       <c r="E280" t="n">
-        <v>640.5718937595319</v>
+        <v>640.5718937595495</v>
       </c>
       <c r="F280" t="n">
-        <v>205.6799321004347</v>
+        <v>205.6799321004407</v>
       </c>
       <c r="G280" t="n">
         <v>0</v>
       </c>
       <c r="H280" t="n">
-        <v>78.12425142699442</v>
+        <v>78.12425142699897</v>
       </c>
       <c r="I280" t="inlineStr">
         <is>
@@ -9687,7 +9675,7 @@
       </c>
     </row>
     <row r="281">
-      <c r="A281" s="2" t="n">
+      <c r="A281" s="1" t="n">
         <v>43832</v>
       </c>
       <c r="B281" t="inlineStr">
@@ -9696,22 +9684,22 @@
         </is>
       </c>
       <c r="C281" t="n">
-        <v>30.80596001675053</v>
+        <v>30.80596001675303</v>
       </c>
       <c r="D281" t="n">
         <v>5</v>
       </c>
       <c r="E281" t="n">
-        <v>29.99738572936699</v>
+        <v>29.99738572936942</v>
       </c>
       <c r="F281" t="n">
-        <v>-4.191425712616461</v>
+        <v>-4.191425712616383</v>
       </c>
       <c r="G281" t="n">
         <v>0</v>
       </c>
       <c r="H281" t="n">
-        <v>82.31567713961088</v>
+        <v>82.31567713961535</v>
       </c>
       <c r="I281" t="inlineStr">
         <is>
@@ -9720,7 +9708,7 @@
       </c>
     </row>
     <row r="282">
-      <c r="A282" s="2" t="n">
+      <c r="A282" s="1" t="n">
         <v>43832</v>
       </c>
       <c r="B282" t="inlineStr">
@@ -9729,22 +9717,22 @@
         </is>
       </c>
       <c r="C282" t="n">
-        <v>51.84342319498046</v>
+        <v>51.8434231949841</v>
       </c>
       <c r="D282" t="n">
         <v>5</v>
       </c>
       <c r="E282" t="n">
-        <v>41.61135145613223</v>
+        <v>41.61135145613516</v>
       </c>
       <c r="F282" t="n">
-        <v>5.232071738848234</v>
+        <v>5.232071738848937</v>
       </c>
       <c r="G282" t="n">
         <v>0</v>
       </c>
       <c r="H282" t="n">
-        <v>77.08360540076265</v>
+        <v>77.0836054007664</v>
       </c>
       <c r="I282" t="inlineStr">
         <is>
@@ -9753,7 +9741,7 @@
       </c>
     </row>
     <row r="283">
-      <c r="A283" s="2" t="n">
+      <c r="A283" s="1" t="n">
         <v>44200</v>
       </c>
       <c r="B283" t="inlineStr">
@@ -9762,19 +9750,19 @@
         </is>
       </c>
       <c r="C283" t="n">
-        <v>4673.088994641876</v>
+        <v>4673.088994641817</v>
       </c>
       <c r="D283" t="n">
         <v>5</v>
       </c>
       <c r="E283" t="n">
-        <v>2526.927193855638</v>
+        <v>2526.927193855613</v>
       </c>
       <c r="F283" t="n">
-        <v>2141.161800786238</v>
+        <v>2141.161800786204</v>
       </c>
       <c r="G283" t="n">
-        <v>536.6603308002235</v>
+        <v>536.6603308002138</v>
       </c>
       <c r="H283" t="n">
         <v>0</v>
@@ -9786,7 +9774,7 @@
       </c>
     </row>
     <row r="284">
-      <c r="A284" s="2" t="n">
+      <c r="A284" s="1" t="n">
         <v>44200</v>
       </c>
       <c r="B284" t="inlineStr">
@@ -9795,19 +9783,19 @@
         </is>
       </c>
       <c r="C284" t="n">
-        <v>684.9375681159381</v>
+        <v>684.9375681159408</v>
       </c>
       <c r="D284" t="n">
         <v>5</v>
       </c>
       <c r="E284" t="n">
-        <v>466.8596487838501</v>
+        <v>466.8596487838518</v>
       </c>
       <c r="F284" t="n">
-        <v>213.077919332088</v>
+        <v>213.0779193320891</v>
       </c>
       <c r="G284" t="n">
-        <v>55.40025902634289</v>
+        <v>55.40025902634316</v>
       </c>
       <c r="H284" t="n">
         <v>0</v>
@@ -9819,7 +9807,7 @@
       </c>
     </row>
     <row r="285">
-      <c r="A285" s="2" t="n">
+      <c r="A285" s="1" t="n">
         <v>44200</v>
       </c>
       <c r="B285" t="inlineStr">
@@ -9828,22 +9816,22 @@
         </is>
       </c>
       <c r="C285" t="n">
-        <v>2780.077836990386</v>
+        <v>2780.077836990396</v>
       </c>
       <c r="D285" t="n">
         <v>5</v>
       </c>
       <c r="E285" t="n">
-        <v>3772.432452209366</v>
+        <v>3772.43245220938</v>
       </c>
       <c r="F285" t="n">
-        <v>-997.3546152189806</v>
+        <v>-997.3546152189833</v>
       </c>
       <c r="G285" t="n">
         <v>0</v>
       </c>
       <c r="H285" t="n">
-        <v>997.3546152189806</v>
+        <v>997.3546152189833</v>
       </c>
       <c r="I285" t="inlineStr">
         <is>
@@ -9852,7 +9840,7 @@
       </c>
     </row>
     <row r="286">
-      <c r="A286" s="2" t="n">
+      <c r="A286" s="1" t="n">
         <v>44200</v>
       </c>
       <c r="B286" t="inlineStr">
@@ -9861,19 +9849,19 @@
         </is>
       </c>
       <c r="C286" t="n">
-        <v>2265.905621318194</v>
+        <v>2265.905621318208</v>
       </c>
       <c r="D286" t="n">
         <v>5</v>
       </c>
       <c r="E286" t="n">
-        <v>1201.808904342362</v>
+        <v>1201.80890434237</v>
       </c>
       <c r="F286" t="n">
-        <v>1059.096716975832</v>
+        <v>1059.096716975838</v>
       </c>
       <c r="G286" t="n">
-        <v>16.05294645678134</v>
+        <v>16.05294645678222</v>
       </c>
       <c r="H286" t="n">
         <v>0</v>
@@ -9885,7 +9873,7 @@
       </c>
     </row>
     <row r="287">
-      <c r="A287" s="2" t="n">
+      <c r="A287" s="1" t="n">
         <v>44200</v>
       </c>
       <c r="B287" t="inlineStr">
@@ -9894,19 +9882,19 @@
         </is>
       </c>
       <c r="C287" t="n">
-        <v>1421.492582619363</v>
+        <v>1421.492582619367</v>
       </c>
       <c r="D287" t="n">
         <v>5</v>
       </c>
       <c r="E287" t="n">
-        <v>1326.438150951246</v>
+        <v>1326.438150951249</v>
       </c>
       <c r="F287" t="n">
-        <v>90.05443166811665</v>
+        <v>90.05443166811733</v>
       </c>
       <c r="G287" t="n">
-        <v>23.41415223371033</v>
+        <v>23.41415223371051</v>
       </c>
       <c r="H287" t="n">
         <v>0</v>
@@ -9918,7 +9906,7 @@
       </c>
     </row>
     <row r="288">
-      <c r="A288" s="2" t="n">
+      <c r="A288" s="1" t="n">
         <v>44200</v>
       </c>
       <c r="B288" t="inlineStr">
@@ -9927,22 +9915,22 @@
         </is>
       </c>
       <c r="C288" t="n">
-        <v>1307.746424100663</v>
+        <v>1307.746424100661</v>
       </c>
       <c r="D288" t="n">
         <v>5</v>
       </c>
       <c r="E288" t="n">
-        <v>1428.373414704363</v>
+        <v>1428.373414704362</v>
       </c>
       <c r="F288" t="n">
-        <v>-125.6269906037003</v>
+        <v>-125.626990603701</v>
       </c>
       <c r="G288" t="n">
         <v>0</v>
       </c>
       <c r="H288" t="n">
-        <v>125.6269906037003</v>
+        <v>125.626990603701</v>
       </c>
       <c r="I288" t="inlineStr">
         <is>
@@ -9951,7 +9939,7 @@
       </c>
     </row>
     <row r="289">
-      <c r="A289" s="2" t="n">
+      <c r="A289" s="1" t="n">
         <v>44200</v>
       </c>
       <c r="B289" t="inlineStr">
@@ -9960,19 +9948,19 @@
         </is>
       </c>
       <c r="C289" t="n">
-        <v>3968.278723572282</v>
+        <v>3968.278723572281</v>
       </c>
       <c r="D289" t="n">
         <v>5</v>
       </c>
       <c r="E289" t="n">
-        <v>2540.933047099226</v>
+        <v>2540.933047099225</v>
       </c>
       <c r="F289" t="n">
-        <v>1422.345676473056</v>
+        <v>1422.345676473055</v>
       </c>
       <c r="G289" t="n">
-        <v>337.1468583260325</v>
+        <v>337.1468583260321</v>
       </c>
       <c r="H289" t="n">
         <v>0</v>
@@ -9984,7 +9972,7 @@
       </c>
     </row>
     <row r="290">
-      <c r="A290" s="2" t="n">
+      <c r="A290" s="1" t="n">
         <v>44200</v>
       </c>
       <c r="B290" t="inlineStr">
@@ -9993,22 +9981,22 @@
         </is>
       </c>
       <c r="C290" t="n">
-        <v>2126.278946278369</v>
+        <v>2126.278946278373</v>
       </c>
       <c r="D290" t="n">
         <v>5</v>
       </c>
       <c r="E290" t="n">
-        <v>2125.760547615409</v>
+        <v>2125.76054761541</v>
       </c>
       <c r="F290" t="n">
-        <v>-4.481601337039137</v>
+        <v>-4.481601337037773</v>
       </c>
       <c r="G290" t="n">
         <v>0</v>
       </c>
       <c r="H290" t="n">
-        <v>4.481601337039137</v>
+        <v>4.481601337037773</v>
       </c>
       <c r="I290" t="inlineStr">
         <is>
@@ -10017,7 +10005,7 @@
       </c>
     </row>
     <row r="291">
-      <c r="A291" s="2" t="n">
+      <c r="A291" s="1" t="n">
         <v>44200</v>
       </c>
       <c r="B291" t="inlineStr">
@@ -10032,16 +10020,16 @@
         <v>5</v>
       </c>
       <c r="E291" t="n">
-        <v>3094.087362647728</v>
+        <v>3094.087362647731</v>
       </c>
       <c r="F291" t="n">
-        <v>-622.2357405118464</v>
+        <v>-622.2357405118501</v>
       </c>
       <c r="G291" t="n">
         <v>0</v>
       </c>
       <c r="H291" t="n">
-        <v>626.7173418488856</v>
+        <v>626.7173418488878</v>
       </c>
       <c r="I291" t="inlineStr">
         <is>
@@ -10050,7 +10038,7 @@
       </c>
     </row>
     <row r="292">
-      <c r="A292" s="2" t="n">
+      <c r="A292" s="1" t="n">
         <v>44564</v>
       </c>
       <c r="B292" t="inlineStr">
@@ -10059,7 +10047,7 @@
         </is>
       </c>
       <c r="C292" t="n">
-        <v>24699.23777600611</v>
+        <v>24699.23777600606</v>
       </c>
       <c r="D292" t="n">
         <v>5</v>
@@ -10068,10 +10056,10 @@
         <v>10809.56140739083</v>
       </c>
       <c r="F292" t="n">
-        <v>13884.67636861528</v>
+        <v>13884.67636861523</v>
       </c>
       <c r="G292" t="n">
-        <v>3447.069346959262</v>
+        <v>3447.069346959249</v>
       </c>
       <c r="H292" t="n">
         <v>0</v>
@@ -10083,7 +10071,7 @@
       </c>
     </row>
     <row r="293">
-      <c r="A293" s="2" t="n">
+      <c r="A293" s="1" t="n">
         <v>44564</v>
       </c>
       <c r="B293" t="inlineStr">
@@ -10092,19 +10080,19 @@
         </is>
       </c>
       <c r="C293" t="n">
-        <v>7685.648373564019</v>
+        <v>7685.648373564013</v>
       </c>
       <c r="D293" t="n">
         <v>5</v>
       </c>
       <c r="E293" t="n">
-        <v>6336.65171364164</v>
+        <v>6336.651713641632</v>
       </c>
       <c r="F293" t="n">
-        <v>1343.99665992238</v>
+        <v>1343.996659922381</v>
       </c>
       <c r="G293" t="n">
-        <v>349.4391315798188</v>
+        <v>349.439131579819</v>
       </c>
       <c r="H293" t="n">
         <v>0</v>
@@ -10116,7 +10104,7 @@
       </c>
     </row>
     <row r="294">
-      <c r="A294" s="2" t="n">
+      <c r="A294" s="1" t="n">
         <v>44564</v>
       </c>
       <c r="B294" t="inlineStr">
@@ -10125,13 +10113,13 @@
         </is>
       </c>
       <c r="C294" t="n">
-        <v>6591.074966098468</v>
+        <v>6591.074966098464</v>
       </c>
       <c r="D294" t="n">
         <v>5</v>
       </c>
       <c r="E294" t="n">
-        <v>4555.904767055674</v>
+        <v>4555.904767055669</v>
       </c>
       <c r="F294" t="n">
         <v>2030.170199042795</v>
@@ -10149,7 +10137,7 @@
       </c>
     </row>
     <row r="295">
-      <c r="A295" s="2" t="n">
+      <c r="A295" s="1" t="n">
         <v>44928</v>
       </c>
       <c r="B295" t="inlineStr">
@@ -10158,19 +10146,19 @@
         </is>
       </c>
       <c r="C295" t="n">
-        <v>1860.500280366992</v>
+        <v>1860.500280366978</v>
       </c>
       <c r="D295" t="n">
         <v>5</v>
       </c>
       <c r="E295" t="n">
-        <v>1811.421087673685</v>
+        <v>1811.421087673672</v>
       </c>
       <c r="F295" t="n">
-        <v>44.07919269330705</v>
+        <v>44.07919269330569</v>
       </c>
       <c r="G295" t="n">
-        <v>11.46059010025983</v>
+        <v>11.46059010025948</v>
       </c>
       <c r="H295" t="n">
         <v>0</v>
@@ -10182,7 +10170,7 @@
       </c>
     </row>
     <row r="296">
-      <c r="A296" s="2" t="n">
+      <c r="A296" s="1" t="n">
         <v>44928</v>
       </c>
       <c r="B296" t="inlineStr">
@@ -10191,19 +10179,19 @@
         </is>
       </c>
       <c r="C296" t="n">
-        <v>1211.346608371518</v>
+        <v>1211.346608371521</v>
       </c>
       <c r="D296" t="n">
         <v>5</v>
       </c>
       <c r="E296" t="n">
-        <v>1064.922741072322</v>
+        <v>1064.922741072328</v>
       </c>
       <c r="F296" t="n">
-        <v>141.4238672991951</v>
+        <v>141.4238672991933</v>
       </c>
       <c r="G296" t="n">
-        <v>36.77020549779072</v>
+        <v>36.77020549779025</v>
       </c>
       <c r="H296" t="n">
         <v>0</v>
@@ -10215,7 +10203,7 @@
       </c>
     </row>
     <row r="297">
-      <c r="A297" s="2" t="n">
+      <c r="A297" s="1" t="n">
         <v>44928</v>
       </c>
       <c r="B297" t="inlineStr">
@@ -10224,19 +10212,19 @@
         </is>
       </c>
       <c r="C297" t="n">
-        <v>7942.940245275502</v>
+        <v>7942.940245275489</v>
       </c>
       <c r="D297" t="n">
         <v>5</v>
       </c>
       <c r="E297" t="n">
-        <v>5092.253690800395</v>
+        <v>5092.253690800386</v>
       </c>
       <c r="F297" t="n">
-        <v>2845.686554475107</v>
+        <v>2845.686554475104</v>
       </c>
       <c r="G297" t="n">
-        <v>739.8785041635279</v>
+        <v>739.8785041635269</v>
       </c>
       <c r="H297" t="n">
         <v>0</v>
@@ -10248,7 +10236,7 @@
       </c>
     </row>
     <row r="298">
-      <c r="A298" s="2" t="n">
+      <c r="A298" s="1" t="n">
         <v>44928</v>
       </c>
       <c r="B298" t="inlineStr">
@@ -10257,19 +10245,19 @@
         </is>
       </c>
       <c r="C298" t="n">
-        <v>755.0579250595256</v>
+        <v>755.057925059511</v>
       </c>
       <c r="D298" t="n">
         <v>5</v>
       </c>
       <c r="E298" t="n">
-        <v>590.476135972986</v>
+        <v>590.4761359729744</v>
       </c>
       <c r="F298" t="n">
-        <v>159.5817890865396</v>
+        <v>159.5817890865367</v>
       </c>
       <c r="G298" t="n">
-        <v>41.49126516250031</v>
+        <v>41.49126516249954</v>
       </c>
       <c r="H298" t="n">
         <v>0</v>
@@ -10281,7 +10269,7 @@
       </c>
     </row>
     <row r="299">
-      <c r="A299" s="2" t="n">
+      <c r="A299" s="1" t="n">
         <v>44928</v>
       </c>
       <c r="B299" t="inlineStr">
@@ -10290,19 +10278,19 @@
         </is>
       </c>
       <c r="C299" t="n">
-        <v>631.3247044533218</v>
+        <v>631.3247044533291</v>
       </c>
       <c r="D299" t="n">
         <v>5</v>
       </c>
       <c r="E299" t="n">
-        <v>473.0203646736933</v>
+        <v>473.0203646736983</v>
       </c>
       <c r="F299" t="n">
-        <v>153.3043397796285</v>
+        <v>153.3043397796308</v>
       </c>
       <c r="G299" t="n">
-        <v>39.85912834270341</v>
+        <v>39.859128342704</v>
       </c>
       <c r="H299" t="n">
         <v>0</v>
@@ -10314,7 +10302,7 @@
       </c>
     </row>
     <row r="300">
-      <c r="A300" s="2" t="n">
+      <c r="A300" s="1" t="n">
         <v>44928</v>
       </c>
       <c r="B300" t="inlineStr">
@@ -10323,19 +10311,19 @@
         </is>
       </c>
       <c r="C300" t="n">
-        <v>377.6567842804707</v>
+        <v>377.6567842804716</v>
       </c>
       <c r="D300" t="n">
         <v>5</v>
       </c>
       <c r="E300" t="n">
-        <v>300.3856739567382</v>
+        <v>300.3856739567389</v>
       </c>
       <c r="F300" t="n">
-        <v>72.2711103237325</v>
+        <v>72.27111032373267</v>
       </c>
       <c r="G300" t="n">
-        <v>18.79048868417045</v>
+        <v>18.79048868417049</v>
       </c>
       <c r="H300" t="n">
         <v>0</v>
@@ -10347,7 +10335,7 @@
       </c>
     </row>
     <row r="301">
-      <c r="A301" s="2" t="n">
+      <c r="A301" s="1" t="n">
         <v>44928</v>
       </c>
       <c r="B301" t="inlineStr">
@@ -10356,19 +10344,19 @@
         </is>
       </c>
       <c r="C301" t="n">
-        <v>17200.28602684302</v>
+        <v>17200.286026843</v>
       </c>
       <c r="D301" t="n">
         <v>5</v>
       </c>
       <c r="E301" t="n">
-        <v>10941.546859478</v>
+        <v>10941.54685947799</v>
       </c>
       <c r="F301" t="n">
-        <v>6253.73916736502</v>
+        <v>6253.739167365009</v>
       </c>
       <c r="G301" t="n">
-        <v>1625.972183514905</v>
+        <v>1625.972183514902</v>
       </c>
       <c r="H301" t="n">
         <v>0</v>
@@ -10380,7 +10368,7 @@
       </c>
     </row>
     <row r="302">
-      <c r="A302" s="2" t="n">
+      <c r="A302" s="1" t="n">
         <v>44928</v>
       </c>
       <c r="B302" t="inlineStr">
@@ -10389,22 +10377,22 @@
         </is>
       </c>
       <c r="C302" t="n">
-        <v>4385.467684108447</v>
+        <v>4385.467684108444</v>
       </c>
       <c r="D302" t="n">
         <v>5</v>
       </c>
       <c r="E302" t="n">
-        <v>6226.750231018468</v>
+        <v>6226.750231018463</v>
       </c>
       <c r="F302" t="n">
-        <v>-1846.282546910021</v>
+        <v>-1846.282546910019</v>
       </c>
       <c r="G302" t="n">
         <v>0</v>
       </c>
       <c r="H302" t="n">
-        <v>1846.282546910021</v>
+        <v>1846.282546910019</v>
       </c>
       <c r="I302" t="inlineStr">
         <is>
@@ -10413,7 +10401,7 @@
       </c>
     </row>
     <row r="303">
-      <c r="A303" s="2" t="n">
+      <c r="A303" s="1" t="n">
         <v>44928</v>
       </c>
       <c r="B303" t="inlineStr">
@@ -10428,16 +10416,16 @@
         <v>5</v>
       </c>
       <c r="E303" t="n">
-        <v>2870.035903165504</v>
+        <v>2870.035903165501</v>
       </c>
       <c r="F303" t="n">
-        <v>-686.1667603653914</v>
+        <v>-686.1667603653887</v>
       </c>
       <c r="G303" t="n">
         <v>0</v>
       </c>
       <c r="H303" t="n">
-        <v>2532.449307275412</v>
+        <v>2532.449307275408</v>
       </c>
       <c r="I303" t="inlineStr">
         <is>
@@ -10446,7 +10434,7 @@
       </c>
     </row>
     <row r="304">
-      <c r="A304" s="2" t="n">
+      <c r="A304" s="1" t="n">
         <v>44928</v>
       </c>
       <c r="B304" t="inlineStr">
@@ -10455,22 +10443,22 @@
         </is>
       </c>
       <c r="C304" t="n">
-        <v>2404.124364578956</v>
+        <v>2404.124364578954</v>
       </c>
       <c r="D304" t="n">
         <v>5</v>
       </c>
       <c r="E304" t="n">
-        <v>2687.778071466045</v>
+        <v>2687.778071466043</v>
       </c>
       <c r="F304" t="n">
-        <v>-288.6537068870884</v>
+        <v>-288.6537068870889</v>
       </c>
       <c r="G304" t="n">
         <v>0</v>
       </c>
       <c r="H304" t="n">
-        <v>2821.103014162501</v>
+        <v>2821.103014162496</v>
       </c>
       <c r="I304" t="inlineStr">
         <is>
@@ -10479,7 +10467,7 @@
       </c>
     </row>
     <row r="305">
-      <c r="A305" s="2" t="n">
+      <c r="A305" s="1" t="n">
         <v>45293</v>
       </c>
       <c r="B305" t="inlineStr">
@@ -10488,19 +10476,19 @@
         </is>
       </c>
       <c r="C305" t="n">
-        <v>41762.39624861949</v>
+        <v>41762.39624861947</v>
       </c>
       <c r="D305" t="n">
         <v>5</v>
       </c>
       <c r="E305" t="n">
-        <v>25643.76809619932</v>
+        <v>25643.76809619935</v>
       </c>
       <c r="F305" t="n">
-        <v>16113.62815242018</v>
+        <v>16113.62815242011</v>
       </c>
       <c r="G305" t="n">
-        <v>3456.056535946996</v>
+        <v>3456.056535946981</v>
       </c>
       <c r="H305" t="n">
         <v>0</v>
@@ -10512,7 +10500,7 @@
       </c>
     </row>
     <row r="306">
-      <c r="A306" s="2" t="n">
+      <c r="A306" s="1" t="n">
         <v>45293</v>
       </c>
       <c r="B306" t="inlineStr">
@@ -10521,19 +10509,19 @@
         </is>
       </c>
       <c r="C306" t="n">
-        <v>33363.47375859196</v>
+        <v>33363.47375859192</v>
       </c>
       <c r="D306" t="n">
         <v>5</v>
       </c>
       <c r="E306" t="n">
-        <v>21155.63567003812</v>
+        <v>21155.63567003809</v>
       </c>
       <c r="F306" t="n">
-        <v>12202.83808855385</v>
+        <v>12202.83808855383</v>
       </c>
       <c r="G306" t="n">
-        <v>3172.737903024</v>
+        <v>3172.737903023995</v>
       </c>
       <c r="H306" t="n">
         <v>0</v>
@@ -10545,7 +10533,7 @@
       </c>
     </row>
     <row r="307">
-      <c r="A307" s="2" t="n">
+      <c r="A307" s="1" t="n">
         <v>45293</v>
       </c>
       <c r="B307" t="inlineStr">
@@ -10554,19 +10542,19 @@
         </is>
       </c>
       <c r="C307" t="n">
-        <v>5668.422431759614</v>
+        <v>5668.422431759611</v>
       </c>
       <c r="D307" t="n">
         <v>5</v>
       </c>
       <c r="E307" t="n">
-        <v>3352.9950511624</v>
+        <v>3352.995051162398</v>
       </c>
       <c r="F307" t="n">
-        <v>2310.427380597214</v>
+        <v>2310.427380597213</v>
       </c>
       <c r="G307" t="n">
-        <v>600.7111189552758</v>
+        <v>600.7111189552754</v>
       </c>
       <c r="H307" t="n">
         <v>0</v>
@@ -10578,7 +10566,7 @@
       </c>
     </row>
     <row r="308">
-      <c r="A308" s="2" t="n">
+      <c r="A308" s="1" t="n">
         <v>45293</v>
       </c>
       <c r="B308" t="inlineStr">
@@ -10587,13 +10575,13 @@
         </is>
       </c>
       <c r="C308" t="n">
-        <v>29393.39292902277</v>
+        <v>29393.39292902274</v>
       </c>
       <c r="D308" t="n">
         <v>5</v>
       </c>
       <c r="E308" t="n">
-        <v>19149.82832160663</v>
+        <v>19149.8283216066</v>
       </c>
       <c r="F308" t="n">
         <v>10238.56460741614</v>
@@ -10611,7 +10599,7 @@
       </c>
     </row>
     <row r="309">
-      <c r="A309" s="2" t="n">
+      <c r="A309" s="1" t="n">
         <v>45293</v>
       </c>
       <c r="B309" t="inlineStr">
@@ -10620,19 +10608,19 @@
         </is>
       </c>
       <c r="C309" t="n">
-        <v>1844.466533219407</v>
+        <v>1844.466533219403</v>
       </c>
       <c r="D309" t="n">
         <v>5</v>
       </c>
       <c r="E309" t="n">
-        <v>1535.143829182103</v>
+        <v>1535.143829182101</v>
       </c>
       <c r="F309" t="n">
-        <v>304.3227040373033</v>
+        <v>304.3227040373022</v>
       </c>
       <c r="G309" t="n">
-        <v>79.12390304969887</v>
+        <v>79.12390304969857</v>
       </c>
       <c r="H309" t="n">
         <v>0</v>
@@ -10644,7 +10632,7 @@
       </c>
     </row>
     <row r="310">
-      <c r="A310" s="2" t="n">
+      <c r="A310" s="1" t="n">
         <v>43467</v>
       </c>
       <c r="B310" t="inlineStr">
@@ -10653,22 +10641,22 @@
         </is>
       </c>
       <c r="C310" t="n">
-        <v>97.57984005551043</v>
+        <v>97.57984005550134</v>
       </c>
       <c r="D310" t="n">
         <v>5</v>
       </c>
       <c r="E310" t="n">
-        <v>94.69192768437985</v>
+        <v>94.69192768437107</v>
       </c>
       <c r="F310" t="n">
-        <v>-2.112087628869418</v>
+        <v>-2.11208762886973</v>
       </c>
       <c r="G310" t="n">
         <v>0</v>
       </c>
       <c r="H310" t="n">
-        <v>2.112087628869418</v>
+        <v>2.11208762886973</v>
       </c>
       <c r="I310" t="inlineStr">
         <is>
@@ -10677,7 +10665,7 @@
       </c>
     </row>
     <row r="311">
-      <c r="A311" s="2" t="n">
+      <c r="A311" s="1" t="n">
         <v>43467</v>
       </c>
       <c r="B311" t="inlineStr">
@@ -10692,13 +10680,13 @@
         <v>5</v>
       </c>
       <c r="E311" t="n">
-        <v>308.6229459303919</v>
+        <v>308.6229459303918</v>
       </c>
       <c r="F311" t="n">
-        <v>9.589846505232629</v>
+        <v>9.589846505232742</v>
       </c>
       <c r="G311" t="n">
-        <v>1.944217307854435</v>
+        <v>1.944217307854383</v>
       </c>
       <c r="H311" t="n">
         <v>0</v>
@@ -10710,7 +10698,7 @@
       </c>
     </row>
     <row r="312">
-      <c r="A312" s="2" t="n">
+      <c r="A312" s="1" t="n">
         <v>43467</v>
       </c>
       <c r="B312" t="inlineStr">
@@ -10728,13 +10716,13 @@
         <v>112.4720817854447</v>
       </c>
       <c r="F312" t="n">
-        <v>-32.99014605438944</v>
+        <v>-32.99014605438943</v>
       </c>
       <c r="G312" t="n">
         <v>0</v>
       </c>
       <c r="H312" t="n">
-        <v>32.99014605438944</v>
+        <v>32.99014605438943</v>
       </c>
       <c r="I312" t="inlineStr">
         <is>
@@ -10743,7 +10731,7 @@
       </c>
     </row>
     <row r="313">
-      <c r="A313" s="2" t="n">
+      <c r="A313" s="1" t="n">
         <v>43467</v>
       </c>
       <c r="B313" t="inlineStr">
@@ -10758,16 +10746,16 @@
         <v>5</v>
       </c>
       <c r="E313" t="n">
-        <v>86.10405864674787</v>
+        <v>86.10405864674786</v>
       </c>
       <c r="F313" t="n">
-        <v>-35.47786742707824</v>
+        <v>-35.47786742707822</v>
       </c>
       <c r="G313" t="n">
         <v>0</v>
       </c>
       <c r="H313" t="n">
-        <v>68.46801348146768</v>
+        <v>68.46801348146765</v>
       </c>
       <c r="I313" t="inlineStr">
         <is>
@@ -10776,7 +10764,7 @@
       </c>
     </row>
     <row r="314">
-      <c r="A314" s="2" t="n">
+      <c r="A314" s="1" t="n">
         <v>43467</v>
       </c>
       <c r="B314" t="inlineStr">
@@ -10794,13 +10782,13 @@
         <v>135.8086767199117</v>
       </c>
       <c r="F314" t="n">
-        <v>-3.221893679079301</v>
+        <v>-3.221893679079272</v>
       </c>
       <c r="G314" t="n">
         <v>0</v>
       </c>
       <c r="H314" t="n">
-        <v>71.68990716054698</v>
+        <v>71.68990716054692</v>
       </c>
       <c r="I314" t="inlineStr">
         <is>
@@ -10809,7 +10797,7 @@
       </c>
     </row>
     <row r="315">
-      <c r="A315" s="2" t="n">
+      <c r="A315" s="1" t="n">
         <v>43467</v>
       </c>
       <c r="B315" t="inlineStr">
@@ -10824,16 +10812,16 @@
         <v>5</v>
       </c>
       <c r="E315" t="n">
-        <v>54.74121164452554</v>
+        <v>54.74121164452553</v>
       </c>
       <c r="F315" t="n">
-        <v>-5.09023850621616</v>
+        <v>-5.090238506216146</v>
       </c>
       <c r="G315" t="n">
         <v>0</v>
       </c>
       <c r="H315" t="n">
-        <v>76.78014566676313</v>
+        <v>76.78014566676308</v>
       </c>
       <c r="I315" t="inlineStr">
         <is>
@@ -10842,7 +10830,7 @@
       </c>
     </row>
     <row r="316">
-      <c r="A316" s="2" t="n">
+      <c r="A316" s="1" t="n">
         <v>43467</v>
       </c>
       <c r="B316" t="inlineStr">
@@ -10857,16 +10845,16 @@
         <v>5</v>
       </c>
       <c r="E316" t="n">
-        <v>4116.330911384407</v>
+        <v>4116.330911384406</v>
       </c>
       <c r="F316" t="n">
-        <v>-1363.515155274842</v>
+        <v>-1363.515155274841</v>
       </c>
       <c r="G316" t="n">
         <v>0</v>
       </c>
       <c r="H316" t="n">
-        <v>1440.295300941605</v>
+        <v>1440.295300941604</v>
       </c>
       <c r="I316" t="inlineStr">
         <is>
@@ -10875,7 +10863,7 @@
       </c>
     </row>
     <row r="317">
-      <c r="A317" s="2" t="n">
+      <c r="A317" s="1" t="n">
         <v>43467</v>
       </c>
       <c r="B317" t="inlineStr">
@@ -10884,22 +10872,22 @@
         </is>
       </c>
       <c r="C317" t="n">
-        <v>42.25472630284094</v>
+        <v>42.25472630284048</v>
       </c>
       <c r="D317" t="n">
         <v>5</v>
       </c>
       <c r="E317" t="n">
-        <v>42.6521959570013</v>
+        <v>42.65219595700083</v>
       </c>
       <c r="F317" t="n">
-        <v>-5.397469654160361</v>
+        <v>-5.397469654160354</v>
       </c>
       <c r="G317" t="n">
         <v>0</v>
       </c>
       <c r="H317" t="n">
-        <v>1445.692770595765</v>
+        <v>1445.692770595764</v>
       </c>
       <c r="I317" t="inlineStr">
         <is>
@@ -10908,7 +10896,7 @@
       </c>
     </row>
     <row r="318">
-      <c r="A318" s="2" t="n">
+      <c r="A318" s="1" t="n">
         <v>43832</v>
       </c>
       <c r="B318" t="inlineStr">
@@ -10917,22 +10905,22 @@
         </is>
       </c>
       <c r="C318" t="n">
-        <v>123.1652080884123</v>
+        <v>123.1652080884105</v>
       </c>
       <c r="D318" t="n">
         <v>5</v>
       </c>
       <c r="E318" t="n">
-        <v>339.945246705524</v>
+        <v>339.9452467055189</v>
       </c>
       <c r="F318" t="n">
-        <v>-221.7800386171117</v>
+        <v>-221.7800386171083</v>
       </c>
       <c r="G318" t="n">
         <v>0</v>
       </c>
       <c r="H318" t="n">
-        <v>1667.472809212877</v>
+        <v>1667.472809212873</v>
       </c>
       <c r="I318" t="inlineStr">
         <is>
@@ -10941,7 +10929,7 @@
       </c>
     </row>
     <row r="319">
-      <c r="A319" s="2" t="n">
+      <c r="A319" s="1" t="n">
         <v>43832</v>
       </c>
       <c r="B319" t="inlineStr">
@@ -10950,22 +10938,22 @@
         </is>
       </c>
       <c r="C319" t="n">
-        <v>828.0906065932031</v>
+        <v>828.0906065931958</v>
       </c>
       <c r="D319" t="n">
         <v>5</v>
       </c>
       <c r="E319" t="n">
-        <v>545.8947888092523</v>
+        <v>545.8947888092476</v>
       </c>
       <c r="F319" t="n">
-        <v>277.1958177839508</v>
+        <v>277.1958177839482</v>
       </c>
       <c r="G319" t="n">
         <v>0</v>
       </c>
       <c r="H319" t="n">
-        <v>1390.276991428926</v>
+        <v>1390.276991428924</v>
       </c>
       <c r="I319" t="inlineStr">
         <is>
@@ -10974,7 +10962,7 @@
       </c>
     </row>
     <row r="320">
-      <c r="A320" s="2" t="n">
+      <c r="A320" s="1" t="n">
         <v>43832</v>
       </c>
       <c r="B320" t="inlineStr">
@@ -10983,22 +10971,22 @@
         </is>
       </c>
       <c r="C320" t="n">
-        <v>612.4818191016657</v>
+        <v>612.4818191016602</v>
       </c>
       <c r="D320" t="n">
         <v>5</v>
       </c>
       <c r="E320" t="n">
-        <v>547.9724426378853</v>
+        <v>547.9724426378802</v>
       </c>
       <c r="F320" t="n">
-        <v>59.50937646378043</v>
+        <v>59.50937646377997</v>
       </c>
       <c r="G320" t="n">
         <v>0</v>
       </c>
       <c r="H320" t="n">
-        <v>1330.767614965145</v>
+        <v>1330.767614965144</v>
       </c>
       <c r="I320" t="inlineStr">
         <is>
@@ -11007,7 +10995,7 @@
       </c>
     </row>
     <row r="321">
-      <c r="A321" s="2" t="n">
+      <c r="A321" s="1" t="n">
         <v>43832</v>
       </c>
       <c r="B321" t="inlineStr">
@@ -11016,22 +11004,22 @@
         </is>
       </c>
       <c r="C321" t="n">
-        <v>811.0608253573573</v>
+        <v>811.0608253573537</v>
       </c>
       <c r="D321" t="n">
         <v>5</v>
       </c>
       <c r="E321" t="n">
-        <v>811.0875272740102</v>
+        <v>811.0875272740064</v>
       </c>
       <c r="F321" t="n">
-        <v>-5.026701916652883</v>
+        <v>-5.026701916652769</v>
       </c>
       <c r="G321" t="n">
         <v>0</v>
       </c>
       <c r="H321" t="n">
-        <v>1335.794316881798</v>
+        <v>1335.794316881797</v>
       </c>
       <c r="I321" t="inlineStr">
         <is>
@@ -11040,7 +11028,7 @@
       </c>
     </row>
     <row r="322">
-      <c r="A322" s="2" t="n">
+      <c r="A322" s="1" t="n">
         <v>43832</v>
       </c>
       <c r="B322" t="inlineStr">
@@ -11049,22 +11037,22 @@
         </is>
       </c>
       <c r="C322" t="n">
-        <v>336.2506562673298</v>
+        <v>336.2506562673261</v>
       </c>
       <c r="D322" t="n">
         <v>5</v>
       </c>
       <c r="E322" t="n">
-        <v>249.6468912997751</v>
+        <v>249.6468912997724</v>
       </c>
       <c r="F322" t="n">
-        <v>81.60376496755467</v>
+        <v>81.60376496755376</v>
       </c>
       <c r="G322" t="n">
         <v>0</v>
       </c>
       <c r="H322" t="n">
-        <v>1254.190551914244</v>
+        <v>1254.190551914243</v>
       </c>
       <c r="I322" t="inlineStr">
         <is>
@@ -11073,7 +11061,7 @@
       </c>
     </row>
     <row r="323">
-      <c r="A323" s="2" t="n">
+      <c r="A323" s="1" t="n">
         <v>43832</v>
       </c>
       <c r="B323" t="inlineStr">
@@ -11082,22 +11070,22 @@
         </is>
       </c>
       <c r="C323" t="n">
-        <v>417.2036616205405</v>
+        <v>417.2036616205396</v>
       </c>
       <c r="D323" t="n">
         <v>5</v>
       </c>
       <c r="E323" t="n">
-        <v>326.1984172597276</v>
+        <v>326.198417259727</v>
       </c>
       <c r="F323" t="n">
-        <v>86.00524436081287</v>
+        <v>86.00524436081264</v>
       </c>
       <c r="G323" t="n">
         <v>0</v>
       </c>
       <c r="H323" t="n">
-        <v>1168.185307553431</v>
+        <v>1168.18530755343</v>
       </c>
       <c r="I323" t="inlineStr">
         <is>
@@ -11106,7 +11094,7 @@
       </c>
     </row>
     <row r="324">
-      <c r="A324" s="2" t="n">
+      <c r="A324" s="1" t="n">
         <v>43832</v>
       </c>
       <c r="B324" t="inlineStr">
@@ -11121,16 +11109,16 @@
         <v>5</v>
       </c>
       <c r="E324" t="n">
-        <v>2773.733822443665</v>
+        <v>2773.733822443663</v>
       </c>
       <c r="F324" t="n">
-        <v>929.6330014340479</v>
+        <v>929.6330014340501</v>
       </c>
       <c r="G324" t="n">
         <v>0</v>
       </c>
       <c r="H324" t="n">
-        <v>238.5523061193828</v>
+        <v>238.5523061193803</v>
       </c>
       <c r="I324" t="inlineStr">
         <is>
@@ -11139,7 +11127,7 @@
       </c>
     </row>
     <row r="325">
-      <c r="A325" s="2" t="n">
+      <c r="A325" s="1" t="n">
         <v>43832</v>
       </c>
       <c r="B325" t="inlineStr">
@@ -11148,22 +11136,22 @@
         </is>
       </c>
       <c r="C325" t="n">
-        <v>73.31381279130756</v>
+        <v>73.31381279131892</v>
       </c>
       <c r="D325" t="n">
         <v>5</v>
       </c>
       <c r="E325" t="n">
-        <v>66.87538510368938</v>
+        <v>66.8753851036997</v>
       </c>
       <c r="F325" t="n">
-        <v>1.438427687618173</v>
+        <v>1.438427687619225</v>
       </c>
       <c r="G325" t="n">
         <v>0</v>
       </c>
       <c r="H325" t="n">
-        <v>237.1138784317646</v>
+        <v>237.1138784317611</v>
       </c>
       <c r="I325" t="inlineStr">
         <is>
@@ -11172,7 +11160,7 @@
       </c>
     </row>
     <row r="326">
-      <c r="A326" s="2" t="n">
+      <c r="A326" s="1" t="n">
         <v>44200</v>
       </c>
       <c r="B326" t="inlineStr">
@@ -11181,22 +11169,22 @@
         </is>
       </c>
       <c r="C326" t="n">
-        <v>66.36037678886441</v>
+        <v>66.3603767888626</v>
       </c>
       <c r="D326" t="n">
         <v>5</v>
       </c>
       <c r="E326" t="n">
-        <v>245.5006369893429</v>
+        <v>245.5006369893361</v>
       </c>
       <c r="F326" t="n">
-        <v>-184.1402602004785</v>
+        <v>-184.1402602004735</v>
       </c>
       <c r="G326" t="n">
         <v>0</v>
       </c>
       <c r="H326" t="n">
-        <v>421.2541386322431</v>
+        <v>421.2541386322346</v>
       </c>
       <c r="I326" t="inlineStr">
         <is>
@@ -11205,7 +11193,7 @@
       </c>
     </row>
     <row r="327">
-      <c r="A327" s="2" t="n">
+      <c r="A327" s="1" t="n">
         <v>44200</v>
       </c>
       <c r="B327" t="inlineStr">
@@ -11214,22 +11202,22 @@
         </is>
       </c>
       <c r="C327" t="n">
-        <v>759.9734313290319</v>
+        <v>759.9734313290282</v>
       </c>
       <c r="D327" t="n">
         <v>5</v>
       </c>
       <c r="E327" t="n">
-        <v>411.014555714167</v>
+        <v>411.0145557141652</v>
       </c>
       <c r="F327" t="n">
-        <v>343.9588756148649</v>
+        <v>343.9588756148631</v>
       </c>
       <c r="G327" t="n">
         <v>0</v>
       </c>
       <c r="H327" t="n">
-        <v>77.2952630173782</v>
+        <v>77.2952630173715</v>
       </c>
       <c r="I327" t="inlineStr">
         <is>
@@ -11238,7 +11226,7 @@
       </c>
     </row>
     <row r="328">
-      <c r="A328" s="2" t="n">
+      <c r="A328" s="1" t="n">
         <v>44200</v>
       </c>
       <c r="B328" t="inlineStr">
@@ -11247,22 +11235,22 @@
         </is>
       </c>
       <c r="C328" t="n">
-        <v>972.5540397782461</v>
+        <v>972.5540397782443</v>
       </c>
       <c r="D328" t="n">
         <v>5</v>
       </c>
       <c r="E328" t="n">
-        <v>1319.931295156713</v>
+        <v>1319.93129515671</v>
       </c>
       <c r="F328" t="n">
-        <v>-352.3772553784668</v>
+        <v>-352.3772553784661</v>
       </c>
       <c r="G328" t="n">
         <v>0</v>
       </c>
       <c r="H328" t="n">
-        <v>429.672518395845</v>
+        <v>429.6725183958376</v>
       </c>
       <c r="I328" t="inlineStr">
         <is>
@@ -11271,7 +11259,7 @@
       </c>
     </row>
     <row r="329">
-      <c r="A329" s="2" t="n">
+      <c r="A329" s="1" t="n">
         <v>44200</v>
       </c>
       <c r="B329" t="inlineStr">
@@ -11280,22 +11268,22 @@
         </is>
       </c>
       <c r="C329" t="n">
-        <v>163.6201791829244</v>
+        <v>163.6201791829235</v>
       </c>
       <c r="D329" t="n">
         <v>5</v>
       </c>
       <c r="E329" t="n">
-        <v>319.5350882320018</v>
+        <v>319.535088232</v>
       </c>
       <c r="F329" t="n">
-        <v>-160.9149090490774</v>
+        <v>-160.9149090490765</v>
       </c>
       <c r="G329" t="n">
         <v>0</v>
       </c>
       <c r="H329" t="n">
-        <v>590.5874274449225</v>
+        <v>590.5874274449141</v>
       </c>
       <c r="I329" t="inlineStr">
         <is>
@@ -11304,7 +11292,7 @@
       </c>
     </row>
     <row r="330">
-      <c r="A330" s="2" t="n">
+      <c r="A330" s="1" t="n">
         <v>44200</v>
       </c>
       <c r="B330" t="inlineStr">
@@ -11313,22 +11301,22 @@
         </is>
       </c>
       <c r="C330" t="n">
-        <v>330.8764710988862</v>
+        <v>330.8764710988899</v>
       </c>
       <c r="D330" t="n">
         <v>5</v>
       </c>
       <c r="E330" t="n">
-        <v>304.622158280448</v>
+        <v>304.6221582804512</v>
       </c>
       <c r="F330" t="n">
-        <v>21.25431281843817</v>
+        <v>21.25431281843862</v>
       </c>
       <c r="G330" t="n">
         <v>0</v>
       </c>
       <c r="H330" t="n">
-        <v>569.3331146264843</v>
+        <v>569.3331146264754</v>
       </c>
       <c r="I330" t="inlineStr">
         <is>
@@ -11337,7 +11325,7 @@
       </c>
     </row>
     <row r="331">
-      <c r="A331" s="2" t="n">
+      <c r="A331" s="1" t="n">
         <v>44200</v>
       </c>
       <c r="B331" t="inlineStr">
@@ -11346,22 +11334,22 @@
         </is>
       </c>
       <c r="C331" t="n">
-        <v>243.0613107331974</v>
+        <v>243.0613107331956</v>
       </c>
       <c r="D331" t="n">
         <v>5</v>
       </c>
       <c r="E331" t="n">
-        <v>130.4533889008519</v>
+        <v>130.4533889008509</v>
       </c>
       <c r="F331" t="n">
-        <v>107.6079218323455</v>
+        <v>107.6079218323447</v>
       </c>
       <c r="G331" t="n">
         <v>0</v>
       </c>
       <c r="H331" t="n">
-        <v>461.7251927941388</v>
+        <v>461.7251927941307</v>
       </c>
       <c r="I331" t="inlineStr">
         <is>
@@ -11370,7 +11358,7 @@
       </c>
     </row>
     <row r="332">
-      <c r="A332" s="2" t="n">
+      <c r="A332" s="1" t="n">
         <v>44200</v>
       </c>
       <c r="B332" t="inlineStr">
@@ -11379,22 +11367,22 @@
         </is>
       </c>
       <c r="C332" t="n">
-        <v>190.9843883932799</v>
+        <v>190.9843883932808</v>
       </c>
       <c r="D332" t="n">
         <v>5</v>
       </c>
       <c r="E332" t="n">
-        <v>144.4235122865531</v>
+        <v>144.4235122865538</v>
       </c>
       <c r="F332" t="n">
-        <v>41.56087610672677</v>
+        <v>41.56087610672702</v>
       </c>
       <c r="G332" t="n">
         <v>0</v>
       </c>
       <c r="H332" t="n">
-        <v>420.1643166874121</v>
+        <v>420.1643166874037</v>
       </c>
       <c r="I332" t="inlineStr">
         <is>
@@ -11403,7 +11391,7 @@
       </c>
     </row>
     <row r="333">
-      <c r="A333" s="2" t="n">
+      <c r="A333" s="1" t="n">
         <v>44200</v>
       </c>
       <c r="B333" t="inlineStr">
@@ -11418,16 +11406,16 @@
         <v>5</v>
       </c>
       <c r="E333" t="n">
-        <v>3163.223332952296</v>
+        <v>3163.223332952295</v>
       </c>
       <c r="F333" t="n">
-        <v>-861.2771666751382</v>
+        <v>-861.2771666751369</v>
       </c>
       <c r="G333" t="n">
         <v>0</v>
       </c>
       <c r="H333" t="n">
-        <v>1281.44148336255</v>
+        <v>1281.441483362541</v>
       </c>
       <c r="I333" t="inlineStr">
         <is>
@@ -11436,7 +11424,7 @@
       </c>
     </row>
     <row r="334">
-      <c r="A334" s="2" t="n">
+      <c r="A334" s="1" t="n">
         <v>44200</v>
       </c>
       <c r="B334" t="inlineStr">
@@ -11445,22 +11433,22 @@
         </is>
       </c>
       <c r="C334" t="n">
-        <v>3330.99853018378</v>
+        <v>3330.998530183775</v>
       </c>
       <c r="D334" t="n">
         <v>5</v>
       </c>
       <c r="E334" t="n">
-        <v>3835.1694456727</v>
+        <v>3835.169445672692</v>
       </c>
       <c r="F334" t="n">
-        <v>-509.1709154889195</v>
+        <v>-509.1709154889168</v>
       </c>
       <c r="G334" t="n">
         <v>0</v>
       </c>
       <c r="H334" t="n">
-        <v>1790.61239885147</v>
+        <v>1790.612398851457</v>
       </c>
       <c r="I334" t="inlineStr">
         <is>
@@ -11469,7 +11457,7 @@
       </c>
     </row>
     <row r="335">
-      <c r="A335" s="2" t="n">
+      <c r="A335" s="1" t="n">
         <v>44564</v>
       </c>
       <c r="B335" t="inlineStr">
@@ -11478,22 +11466,22 @@
         </is>
       </c>
       <c r="C335" t="n">
-        <v>445.831132532654</v>
+        <v>445.8311325326567</v>
       </c>
       <c r="D335" t="n">
         <v>5</v>
       </c>
       <c r="E335" t="n">
-        <v>1928.562223885923</v>
+        <v>1928.562223885933</v>
       </c>
       <c r="F335" t="n">
-        <v>-1487.731091353269</v>
+        <v>-1487.731091353276</v>
       </c>
       <c r="G335" t="n">
         <v>0</v>
       </c>
       <c r="H335" t="n">
-        <v>3278.343490204738</v>
+        <v>3278.343490204733</v>
       </c>
       <c r="I335" t="inlineStr">
         <is>
@@ -11502,7 +11490,7 @@
       </c>
     </row>
     <row r="336">
-      <c r="A336" s="2" t="n">
+      <c r="A336" s="1" t="n">
         <v>44564</v>
       </c>
       <c r="B336" t="inlineStr">
@@ -11511,22 +11499,22 @@
         </is>
       </c>
       <c r="C336" t="n">
-        <v>345.9093718636759</v>
+        <v>345.9093718636868</v>
       </c>
       <c r="D336" t="n">
         <v>5</v>
       </c>
       <c r="E336" t="n">
-        <v>210.284417839895</v>
+        <v>210.2844178399016</v>
       </c>
       <c r="F336" t="n">
-        <v>130.6249540237809</v>
+        <v>130.6249540237852</v>
       </c>
       <c r="G336" t="n">
         <v>0</v>
       </c>
       <c r="H336" t="n">
-        <v>3147.718536180957</v>
+        <v>3147.718536180948</v>
       </c>
       <c r="I336" t="inlineStr">
         <is>
@@ -11535,7 +11523,7 @@
       </c>
     </row>
     <row r="337">
-      <c r="A337" s="2" t="n">
+      <c r="A337" s="1" t="n">
         <v>44564</v>
       </c>
       <c r="B337" t="inlineStr">
@@ -11544,22 +11532,22 @@
         </is>
       </c>
       <c r="C337" t="n">
-        <v>116.1196320868639</v>
+        <v>116.1196320868621</v>
       </c>
       <c r="D337" t="n">
         <v>5</v>
       </c>
       <c r="E337" t="n">
-        <v>103.4130671769176</v>
+        <v>103.413067176916</v>
       </c>
       <c r="F337" t="n">
-        <v>7.70656490994638</v>
+        <v>7.706564909946138</v>
       </c>
       <c r="G337" t="n">
         <v>0</v>
       </c>
       <c r="H337" t="n">
-        <v>3140.011971271011</v>
+        <v>3140.011971271002</v>
       </c>
       <c r="I337" t="inlineStr">
         <is>
@@ -11568,7 +11556,7 @@
       </c>
     </row>
     <row r="338">
-      <c r="A338" s="2" t="n">
+      <c r="A338" s="1" t="n">
         <v>44564</v>
       </c>
       <c r="B338" t="inlineStr">
@@ -11577,22 +11565,22 @@
         </is>
       </c>
       <c r="C338" t="n">
-        <v>298.5354743909265</v>
+        <v>298.5354743909229</v>
       </c>
       <c r="D338" t="n">
         <v>5</v>
       </c>
       <c r="E338" t="n">
-        <v>278.6824140997134</v>
+        <v>278.6824140997099</v>
       </c>
       <c r="F338" t="n">
-        <v>14.85306029121318</v>
+        <v>14.85306029121296</v>
       </c>
       <c r="G338" t="n">
         <v>0</v>
       </c>
       <c r="H338" t="n">
-        <v>3125.158910979798</v>
+        <v>3125.158910979789</v>
       </c>
       <c r="I338" t="inlineStr">
         <is>
@@ -11601,7 +11589,7 @@
       </c>
     </row>
     <row r="339">
-      <c r="A339" s="2" t="n">
+      <c r="A339" s="1" t="n">
         <v>44564</v>
       </c>
       <c r="B339" t="inlineStr">
@@ -11610,22 +11598,22 @@
         </is>
       </c>
       <c r="C339" t="n">
-        <v>241.6110663688687</v>
+        <v>241.6110663688669</v>
       </c>
       <c r="D339" t="n">
         <v>5</v>
       </c>
       <c r="E339" t="n">
-        <v>156.743397371229</v>
+        <v>156.7433973712277</v>
       </c>
       <c r="F339" t="n">
-        <v>79.86766899763975</v>
+        <v>79.86766899763916</v>
       </c>
       <c r="G339" t="n">
         <v>0</v>
       </c>
       <c r="H339" t="n">
-        <v>3045.291241982158</v>
+        <v>3045.29124198215</v>
       </c>
       <c r="I339" t="inlineStr">
         <is>
@@ -11634,7 +11622,7 @@
       </c>
     </row>
     <row r="340">
-      <c r="A340" s="2" t="n">
+      <c r="A340" s="1" t="n">
         <v>44564</v>
       </c>
       <c r="B340" t="inlineStr">
@@ -11643,22 +11631,22 @@
         </is>
       </c>
       <c r="C340" t="n">
-        <v>73.04589772975669</v>
+        <v>73.04589772975487</v>
       </c>
       <c r="D340" t="n">
         <v>5</v>
       </c>
       <c r="E340" t="n">
-        <v>45.50638864708792</v>
+        <v>45.50638864708678</v>
       </c>
       <c r="F340" t="n">
-        <v>22.53950908266876</v>
+        <v>22.53950908266809</v>
       </c>
       <c r="G340" t="n">
         <v>0</v>
       </c>
       <c r="H340" t="n">
-        <v>3022.75173289949</v>
+        <v>3022.751732899481</v>
       </c>
       <c r="I340" t="inlineStr">
         <is>
@@ -11667,7 +11655,7 @@
       </c>
     </row>
     <row r="341">
-      <c r="A341" s="2" t="n">
+      <c r="A341" s="1" t="n">
         <v>44564</v>
       </c>
       <c r="B341" t="inlineStr">
@@ -11676,13 +11664,13 @@
         </is>
       </c>
       <c r="C341" t="n">
-        <v>4335.217843995461</v>
+        <v>4335.217843995458</v>
       </c>
       <c r="D341" t="n">
         <v>5</v>
       </c>
       <c r="E341" t="n">
-        <v>3654.695366840578</v>
+        <v>3654.695366840574</v>
       </c>
       <c r="F341" t="n">
         <v>675.5224771548833</v>
@@ -11691,7 +11679,7 @@
         <v>0</v>
       </c>
       <c r="H341" t="n">
-        <v>2347.229255744606</v>
+        <v>2347.229255744598</v>
       </c>
       <c r="I341" t="inlineStr">
         <is>
@@ -11700,7 +11688,7 @@
       </c>
     </row>
     <row r="342">
-      <c r="A342" s="2" t="n">
+      <c r="A342" s="1" t="n">
         <v>44928</v>
       </c>
       <c r="B342" t="inlineStr">
@@ -11715,16 +11703,16 @@
         <v>5</v>
       </c>
       <c r="E342" t="n">
-        <v>23900.16277580965</v>
+        <v>23900.16277580964</v>
       </c>
       <c r="F342" t="n">
-        <v>-23899.44170010375</v>
+        <v>-23899.44170010374</v>
       </c>
       <c r="G342" t="n">
         <v>0</v>
       </c>
       <c r="H342" t="n">
-        <v>26246.67095584835</v>
+        <v>26246.67095584834</v>
       </c>
       <c r="I342" t="inlineStr">
         <is>
@@ -11733,7 +11721,7 @@
       </c>
     </row>
     <row r="343">
-      <c r="A343" s="2" t="n">
+      <c r="A343" s="1" t="n">
         <v>44928</v>
       </c>
       <c r="B343" t="inlineStr">
@@ -11748,16 +11736,16 @@
         <v>5</v>
       </c>
       <c r="E343" t="n">
-        <v>389.7755841632736</v>
+        <v>389.7755841632738</v>
       </c>
       <c r="F343" t="n">
-        <v>94.20826735897913</v>
+        <v>94.20826735897896</v>
       </c>
       <c r="G343" t="n">
         <v>0</v>
       </c>
       <c r="H343" t="n">
-        <v>26152.46268848937</v>
+        <v>26152.46268848936</v>
       </c>
       <c r="I343" t="inlineStr">
         <is>
@@ -11766,7 +11754,7 @@
       </c>
     </row>
     <row r="344">
-      <c r="A344" s="2" t="n">
+      <c r="A344" s="1" t="n">
         <v>44928</v>
       </c>
       <c r="B344" t="inlineStr">
@@ -11775,22 +11763,22 @@
         </is>
       </c>
       <c r="C344" t="n">
-        <v>249.265582747923</v>
+        <v>249.2655827479284</v>
       </c>
       <c r="D344" t="n">
         <v>5</v>
       </c>
       <c r="E344" t="n">
-        <v>191.0387208134374</v>
+        <v>191.0387208134416</v>
       </c>
       <c r="F344" t="n">
-        <v>53.22686193448556</v>
+        <v>53.22686193448678</v>
       </c>
       <c r="G344" t="n">
         <v>0</v>
       </c>
       <c r="H344" t="n">
-        <v>26099.23582655489</v>
+        <v>26099.23582655487</v>
       </c>
       <c r="I344" t="inlineStr">
         <is>
@@ -11799,7 +11787,7 @@
       </c>
     </row>
     <row r="345">
-      <c r="A345" s="2" t="n">
+      <c r="A345" s="1" t="n">
         <v>44928</v>
       </c>
       <c r="B345" t="inlineStr">
@@ -11823,7 +11811,7 @@
         <v>0</v>
       </c>
       <c r="H345" t="n">
-        <v>26059.3001104377</v>
+        <v>26059.30011043769</v>
       </c>
       <c r="I345" t="inlineStr">
         <is>
@@ -11832,7 +11820,7 @@
       </c>
     </row>
     <row r="346">
-      <c r="A346" s="2" t="n">
+      <c r="A346" s="1" t="n">
         <v>44928</v>
       </c>
       <c r="B346" t="inlineStr">
@@ -11856,7 +11844,7 @@
         <v>0</v>
       </c>
       <c r="H346" t="n">
-        <v>26136.09350662937</v>
+        <v>26136.09350662935</v>
       </c>
       <c r="I346" t="inlineStr">
         <is>
@@ -11865,7 +11853,7 @@
       </c>
     </row>
     <row r="347">
-      <c r="A347" s="2" t="n">
+      <c r="A347" s="1" t="n">
         <v>44928</v>
       </c>
       <c r="B347" t="inlineStr">
@@ -11874,22 +11862,22 @@
         </is>
       </c>
       <c r="C347" t="n">
-        <v>258.1729720059193</v>
+        <v>258.1729720059229</v>
       </c>
       <c r="D347" t="n">
         <v>5</v>
       </c>
       <c r="E347" t="n">
-        <v>176.9381013424947</v>
+        <v>176.9381013424971</v>
       </c>
       <c r="F347" t="n">
-        <v>76.23487066342457</v>
+        <v>76.23487066342582</v>
       </c>
       <c r="G347" t="n">
         <v>0</v>
       </c>
       <c r="H347" t="n">
-        <v>26059.85863596594</v>
+        <v>26059.85863596593</v>
       </c>
       <c r="I347" t="inlineStr">
         <is>
@@ -11898,7 +11886,7 @@
       </c>
     </row>
     <row r="348">
-      <c r="A348" s="2" t="n">
+      <c r="A348" s="1" t="n">
         <v>44928</v>
       </c>
       <c r="B348" t="inlineStr">
@@ -11922,7 +11910,7 @@
         <v>0</v>
       </c>
       <c r="H348" t="n">
-        <v>24335.25270609233</v>
+        <v>24335.25270609232</v>
       </c>
       <c r="I348" t="inlineStr">
         <is>
@@ -11931,7 +11919,7 @@
       </c>
     </row>
     <row r="349">
-      <c r="A349" s="2" t="n">
+      <c r="A349" s="1" t="n">
         <v>44928</v>
       </c>
       <c r="B349" t="inlineStr">
@@ -11940,22 +11928,22 @@
         </is>
       </c>
       <c r="C349" t="n">
-        <v>3862.914621156058</v>
+        <v>3862.914621156057</v>
       </c>
       <c r="D349" t="n">
         <v>5</v>
       </c>
       <c r="E349" t="n">
-        <v>4572.115910315272</v>
+        <v>4572.115910315269</v>
       </c>
       <c r="F349" t="n">
-        <v>-714.2012891592144</v>
+        <v>-714.2012891592117</v>
       </c>
       <c r="G349" t="n">
         <v>0</v>
       </c>
       <c r="H349" t="n">
-        <v>25049.45399525155</v>
+        <v>25049.45399525153</v>
       </c>
       <c r="I349" t="inlineStr">
         <is>
@@ -11964,7 +11952,7 @@
       </c>
     </row>
     <row r="350">
-      <c r="A350" s="2" t="n">
+      <c r="A350" s="1" t="n">
         <v>45293</v>
       </c>
       <c r="B350" t="inlineStr">
@@ -11979,16 +11967,16 @@
         <v>5</v>
       </c>
       <c r="E350" t="n">
-        <v>2149.734235951086</v>
+        <v>2149.734235951087</v>
       </c>
       <c r="F350" t="n">
-        <v>1706.426679767688</v>
+        <v>1706.426679767687</v>
       </c>
       <c r="G350" t="n">
         <v>0</v>
       </c>
       <c r="H350" t="n">
-        <v>23343.02731548386</v>
+        <v>23343.02731548385</v>
       </c>
       <c r="I350" t="inlineStr">
         <is>
@@ -11997,7 +11985,7 @@
       </c>
     </row>
     <row r="351">
-      <c r="A351" s="2" t="n">
+      <c r="A351" s="1" t="n">
         <v>45293</v>
       </c>
       <c r="B351" t="inlineStr">
@@ -12012,16 +12000,16 @@
         <v>5</v>
       </c>
       <c r="E351" t="n">
-        <v>2688.340386514511</v>
+        <v>2688.340386514512</v>
       </c>
       <c r="F351" t="n">
-        <v>1632.718590574061</v>
+        <v>1632.71859057406</v>
       </c>
       <c r="G351" t="n">
         <v>0</v>
       </c>
       <c r="H351" t="n">
-        <v>21710.3087249098</v>
+        <v>21710.30872490979</v>
       </c>
       <c r="I351" t="inlineStr">
         <is>
@@ -12030,7 +12018,7 @@
       </c>
     </row>
     <row r="352">
-      <c r="A352" s="2" t="n">
+      <c r="A352" s="1" t="n">
         <v>45293</v>
       </c>
       <c r="B352" t="inlineStr">
@@ -12063,7 +12051,7 @@
       </c>
     </row>
     <row r="353">
-      <c r="A353" s="2" t="n">
+      <c r="A353" s="1" t="n">
         <v>45293</v>
       </c>
       <c r="B353" t="inlineStr">
@@ -12087,7 +12075,7 @@
         <v>0</v>
       </c>
       <c r="H353" t="n">
-        <v>19003.86250093391</v>
+        <v>19003.8625009339</v>
       </c>
       <c r="I353" t="inlineStr">
         <is>
@@ -12096,7 +12084,7 @@
       </c>
     </row>
     <row r="354">
-      <c r="A354" s="2" t="n">
+      <c r="A354" s="1" t="n">
         <v>45293</v>
       </c>
       <c r="B354" t="inlineStr">
@@ -12111,16 +12099,16 @@
         <v>5</v>
       </c>
       <c r="E354" t="n">
-        <v>832.6526680106168</v>
+        <v>832.6526680106163</v>
       </c>
       <c r="F354" t="n">
-        <v>649.16394990073</v>
+        <v>649.1639499007306</v>
       </c>
       <c r="G354" t="n">
         <v>0</v>
       </c>
       <c r="H354" t="n">
-        <v>18354.69855103318</v>
+        <v>18354.69855103317</v>
       </c>
       <c r="I354" t="inlineStr">
         <is>
@@ -12129,7 +12117,7 @@
       </c>
     </row>
     <row r="355">
-      <c r="A355" s="2" t="n">
+      <c r="A355" s="1" t="n">
         <v>45293</v>
       </c>
       <c r="B355" t="inlineStr">
@@ -12144,7 +12132,7 @@
         <v>5</v>
       </c>
       <c r="E355" t="n">
-        <v>586.8832440390964</v>
+        <v>586.8832440390963</v>
       </c>
       <c r="F355" t="n">
         <v>1146.99936533877</v>
@@ -12153,7 +12141,7 @@
         <v>0</v>
       </c>
       <c r="H355" t="n">
-        <v>17207.69918569442</v>
+        <v>17207.6991856944</v>
       </c>
       <c r="I355" t="inlineStr">
         <is>
@@ -12162,7 +12150,7 @@
       </c>
     </row>
     <row r="356">
-      <c r="A356" s="2" t="n">
+      <c r="A356" s="1" t="n">
         <v>45293</v>
       </c>
       <c r="B356" t="inlineStr">
@@ -12195,7 +12183,7 @@
       </c>
     </row>
     <row r="357">
-      <c r="A357" s="2" t="n">
+      <c r="A357" s="1" t="n">
         <v>45293</v>
       </c>
       <c r="B357" t="inlineStr">
@@ -12210,10 +12198,10 @@
         <v>5</v>
       </c>
       <c r="E357" t="n">
-        <v>4320.452268206559</v>
+        <v>4320.452268206558</v>
       </c>
       <c r="F357" t="n">
-        <v>522.4257900869079</v>
+        <v>522.4257900869088</v>
       </c>
       <c r="G357" t="n">
         <v>0</v>
@@ -12228,7 +12216,7 @@
       </c>
     </row>
     <row r="358">
-      <c r="A358" s="2" t="n">
+      <c r="A358" s="1" t="n">
         <v>45293</v>
       </c>
       <c r="B358" t="inlineStr">
@@ -12237,16 +12225,16 @@
         </is>
       </c>
       <c r="C358" t="n">
-        <v>849.0060946580925</v>
+        <v>849.0060946580952</v>
       </c>
       <c r="D358" t="n">
         <v>5</v>
       </c>
       <c r="E358" t="n">
-        <v>848.936932854983</v>
+        <v>848.9369328549859</v>
       </c>
       <c r="F358" t="n">
-        <v>-4.930838196890477</v>
+        <v>-4.930838196890704</v>
       </c>
       <c r="G358" t="n">
         <v>0</v>
@@ -12261,7 +12249,7 @@
       </c>
     </row>
     <row r="359">
-      <c r="A359" s="2" t="n">
+      <c r="A359" s="1" t="n">
         <v>45293</v>
       </c>
       <c r="B359" t="inlineStr">
@@ -12270,13 +12258,13 @@
         </is>
       </c>
       <c r="C359" t="n">
-        <v>5029.994581277249</v>
+        <v>5029.994581277253</v>
       </c>
       <c r="D359" t="n">
         <v>5</v>
       </c>
       <c r="E359" t="n">
-        <v>4412.192827506785</v>
+        <v>4412.192827506788</v>
       </c>
       <c r="F359" t="n">
         <v>612.8017537704645</v>
@@ -12285,7 +12273,7 @@
         <v>0</v>
       </c>
       <c r="H359" t="n">
-        <v>15785.62337300829</v>
+        <v>15785.62337300828</v>
       </c>
       <c r="I359" t="inlineStr">
         <is>
